--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="990" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{071680D5-ED3B-489B-8637-03FDAE99F1D6}"/>
+  <xr:revisionPtr revIDLastSave="1191" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12189F22-E748-47CA-A971-48C005002AA1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="536">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1490,9 +1491,6 @@
     <t>RUBEN DIAS</t>
   </si>
   <si>
-    <t>BRSTOL CITY</t>
-  </si>
-  <si>
     <t>MIKEL MERINO</t>
   </si>
   <si>
@@ -1526,9 +1524,6 @@
     <t>NATHANIEL MENDEZ-LAING</t>
   </si>
   <si>
-    <t>MILTON KEYNES</t>
-  </si>
-  <si>
     <t>(6 - 1)</t>
   </si>
   <si>
@@ -1638,6 +1633,21 @@
   </si>
   <si>
     <t>BURTON</t>
+  </si>
+  <si>
+    <t>MATEUS MANE</t>
+  </si>
+  <si>
+    <t>MARCUS BROWNE</t>
+  </si>
+  <si>
+    <t>ARIBIM PEPPLE</t>
+  </si>
+  <si>
+    <t>(3 - 1)</t>
+  </si>
+  <si>
+    <t>Qtr Final Replays</t>
   </si>
 </sst>
 </file>
@@ -3688,11 +3698,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="83"/>
       <c r="H5" s="84"/>
-      <c r="I5" s="85"/>
+      <c r="I5" s="85">
+        <v>1</v>
+      </c>
       <c r="J5" s="82"/>
       <c r="K5" s="16" t="str">
         <f>D2</f>
@@ -3704,15 +3716,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3743,11 +3755,11 @@
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3778,11 +3790,11 @@
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3818,11 +3830,11 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
@@ -3860,15 +3872,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3877,7 +3889,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="106" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D10" s="106" t="s">
         <v>24</v>
@@ -3906,15 +3918,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -3955,15 +3967,15 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -4004,15 +4016,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4048,15 +4060,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4095,15 +4107,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -4148,11 +4160,11 @@
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4188,15 +4200,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4230,15 +4242,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R17" s="119"/>
       <c r="S17" s="119"/>
@@ -4281,11 +4293,11 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
@@ -4341,13 +4353,15 @@
         <v>284</v>
       </c>
       <c r="F20" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="87">
         <v>45932</v>
       </c>
       <c r="H20" s="84"/>
-      <c r="I20" s="99"/>
+      <c r="I20" s="99">
+        <v>1</v>
+      </c>
       <c r="J20" s="76"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4400,7 +4414,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D22" s="28" t="s">
         <v>18</v>
@@ -4496,7 +4510,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D25" s="28" t="s">
         <v>74</v>
@@ -4533,7 +4547,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4649,23 +4663,27 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="79"/>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="111"/>
+      <c r="D32" s="110" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="112">
         <v>1</v>
       </c>
-      <c r="F32" s="15">
-        <v>40</v>
-      </c>
-      <c r="G32" s="80"/>
-      <c r="H32" s="94"/>
+      <c r="F32" s="113">
+        <v>44</v>
+      </c>
+      <c r="G32" s="80" t="s">
+        <v>285</v>
+      </c>
+      <c r="H32" s="94">
+        <v>46072</v>
+      </c>
       <c r="I32" s="95"/>
       <c r="J32" s="76"/>
       <c r="K32" s="1"/>
@@ -4676,14 +4694,26 @@
     </row>
     <row r="33" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="79"/>
-      <c r="B33" s="21"/>
+      <c r="B33" s="12" t="s">
+        <v>13</v>
+      </c>
       <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="86"/>
+      <c r="D33" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="F33" s="21">
+        <v>2</v>
+      </c>
+      <c r="G33" s="86">
+        <v>46072</v>
+      </c>
       <c r="H33" s="94"/>
-      <c r="I33" s="93"/>
+      <c r="I33" s="93">
+        <v>2</v>
+      </c>
       <c r="J33" s="76"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -4853,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="30">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4933,7 +4963,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D43" s="28" t="s">
         <v>132</v>
@@ -5082,10 +5112,10 @@
         <v>17</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E48" s="29" t="s">
         <v>284</v>
@@ -5173,22 +5203,24 @@
         <v>17</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E51" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F51" s="30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G51" s="91">
         <v>46051</v>
       </c>
       <c r="H51" s="91"/>
-      <c r="I51" s="89"/>
+      <c r="I51" s="89">
+        <v>3</v>
+      </c>
       <c r="J51" s="76"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -5358,11 +5390,13 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
-      <c r="I59" s="92"/>
+      <c r="I59" s="92">
+        <v>1</v>
+      </c>
       <c r="J59" s="76"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -5712,7 +5746,7 @@
         <v>284</v>
       </c>
       <c r="F73" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G73" s="87">
         <v>45897</v>
@@ -6220,7 +6254,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="106" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D94" s="106" t="s">
         <v>24</v>
@@ -6251,16 +6285,16 @@
         <v>16</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E95" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F95" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="91">
         <v>46065</v>
@@ -6289,11 +6323,13 @@
         <v>19</v>
       </c>
       <c r="F96" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G96" s="91"/>
       <c r="H96" s="91"/>
-      <c r="I96" s="90"/>
+      <c r="I96" s="90">
+        <v>2</v>
+      </c>
       <c r="J96" s="76"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -6382,7 +6418,7 @@
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D100" s="28" t="s">
         <v>97</v>
@@ -6457,9 +6493,7 @@
         <v>45918</v>
       </c>
       <c r="H102" s="91"/>
-      <c r="I102" s="90">
-        <v>1</v>
-      </c>
+      <c r="I102" s="90"/>
       <c r="J102" s="76"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -6562,7 +6596,7 @@
         <v>17</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D106" s="28" t="s">
         <v>179</v>
@@ -6577,9 +6611,7 @@
         <v>46002</v>
       </c>
       <c r="H106" s="91"/>
-      <c r="I106" s="92">
-        <v>1</v>
-      </c>
+      <c r="I106" s="92"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6598,7 +6630,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6722,11 +6754,13 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
-      <c r="I113" s="90"/>
+      <c r="I113" s="90">
+        <v>1</v>
+      </c>
       <c r="J113" s="76"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -6783,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G116" s="83"/>
       <c r="H116" s="91"/>
@@ -6939,13 +6973,15 @@
         <v>284</v>
       </c>
       <c r="F122" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G122" s="87">
         <v>45974</v>
       </c>
       <c r="H122" s="91"/>
-      <c r="I122" s="90"/>
+      <c r="I122" s="90">
+        <v>1</v>
+      </c>
       <c r="J122" s="76"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
@@ -7044,19 +7080,19 @@
     </row>
     <row r="126" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="79"/>
-      <c r="B126" s="28" t="s">
+      <c r="B126" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="28" t="s">
+      <c r="C126" s="106" t="s">
         <v>475</v>
       </c>
-      <c r="D126" s="28" t="s">
+      <c r="D126" s="106" t="s">
         <v>206</v>
       </c>
-      <c r="E126" s="29" t="s">
+      <c r="E126" s="107" t="s">
         <v>284</v>
       </c>
-      <c r="F126" s="30">
+      <c r="F126" s="108">
         <v>4</v>
       </c>
       <c r="G126" s="87">
@@ -7079,22 +7115,24 @@
         <v>17</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E127" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F127" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G127" s="87">
         <v>46023</v>
       </c>
       <c r="H127" s="91"/>
-      <c r="I127" s="90"/>
+      <c r="I127" s="90">
+        <v>2</v>
+      </c>
       <c r="J127" s="76"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
@@ -7179,13 +7217,15 @@
         <v>284</v>
       </c>
       <c r="F130" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" s="87">
         <v>46058</v>
       </c>
       <c r="H130" s="91"/>
-      <c r="I130" s="90"/>
+      <c r="I130" s="90">
+        <v>1</v>
+      </c>
       <c r="J130" s="76"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
@@ -7208,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="30">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G131" s="87"/>
       <c r="H131" s="91"/>
@@ -7266,7 +7306,7 @@
         <v>284</v>
       </c>
       <c r="F133" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G133" s="87">
         <v>45932</v>
@@ -7291,7 +7331,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7473,13 +7513,15 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
       </c>
       <c r="H142" s="92"/>
-      <c r="I142" s="118"/>
+      <c r="I142" s="118">
+        <v>2</v>
+      </c>
       <c r="J142" s="76"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1"/>
@@ -7658,13 +7700,15 @@
         <v>284</v>
       </c>
       <c r="F149" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G149" s="87">
         <v>45974</v>
       </c>
       <c r="H149" s="91"/>
-      <c r="I149" s="90"/>
+      <c r="I149" s="90">
+        <v>1</v>
+      </c>
       <c r="J149" s="76"/>
       <c r="K149" s="1"/>
       <c r="L149" s="1"/>
@@ -7674,13 +7718,27 @@
     </row>
     <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="79"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="28"/>
-      <c r="D150" s="28"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="87"/>
-      <c r="H150" s="91"/>
+      <c r="B150" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="106" t="s">
+        <v>150</v>
+      </c>
+      <c r="D150" s="106" t="s">
+        <v>68</v>
+      </c>
+      <c r="E150" s="107">
+        <v>1</v>
+      </c>
+      <c r="F150" s="108">
+        <v>5</v>
+      </c>
+      <c r="G150" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H150" s="91">
+        <v>46030</v>
+      </c>
       <c r="I150" s="90"/>
       <c r="J150" s="76"/>
       <c r="K150" s="1"/>
@@ -7691,28 +7749,28 @@
     </row>
     <row r="151" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="79"/>
-      <c r="B151" s="106" t="s">
+      <c r="B151" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C151" s="106" t="s">
-        <v>150</v>
-      </c>
-      <c r="D151" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="E151" s="107">
+      <c r="C151" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="D151" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E151" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F151" s="30">
+        <v>4</v>
+      </c>
+      <c r="G151" s="87">
+        <v>46030</v>
+      </c>
+      <c r="H151" s="91"/>
+      <c r="I151" s="90">
         <v>1</v>
       </c>
-      <c r="F151" s="108">
-        <v>5</v>
-      </c>
-      <c r="G151" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H151" s="91">
-        <v>46030</v>
-      </c>
-      <c r="I151" s="90"/>
       <c r="J151" s="76"/>
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
@@ -7722,25 +7780,27 @@
     </row>
     <row r="152" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="79"/>
-      <c r="B152" s="28" t="s">
+      <c r="B152" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C152" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="D152" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E152" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F152" s="30">
-        <v>3</v>
-      </c>
-      <c r="G152" s="87">
-        <v>46030</v>
-      </c>
-      <c r="H152" s="91"/>
+      <c r="C152" s="106" t="s">
+        <v>213</v>
+      </c>
+      <c r="D152" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="E152" s="107">
+        <v>18</v>
+      </c>
+      <c r="F152" s="108">
+        <v>10</v>
+      </c>
+      <c r="G152" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H152" s="91">
+        <v>46072</v>
+      </c>
       <c r="I152" s="90"/>
       <c r="J152" s="76"/>
       <c r="K152" s="1"/>
@@ -7755,20 +7815,24 @@
         <v>17</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>213</v>
+        <v>533</v>
       </c>
       <c r="D153" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="E153" s="29">
-        <v>18</v>
+        <v>425</v>
+      </c>
+      <c r="E153" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F153" s="30">
-        <v>10</v>
-      </c>
-      <c r="G153" s="83"/>
+        <v>2</v>
+      </c>
+      <c r="G153" s="87">
+        <v>46072</v>
+      </c>
       <c r="H153" s="91"/>
-      <c r="I153" s="90"/>
+      <c r="I153" s="90">
+        <v>2</v>
+      </c>
       <c r="J153" s="96"/>
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
@@ -7844,10 +7908,10 @@
         <v>17</v>
       </c>
       <c r="C156" s="106" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D156" s="106" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E156" s="107" t="s">
         <v>284</v>
@@ -7875,10 +7939,10 @@
         <v>17</v>
       </c>
       <c r="C157" s="28" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D157" s="28" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E157" s="29" t="s">
         <v>284</v>
@@ -7913,11 +7977,13 @@
         <v>25</v>
       </c>
       <c r="F158" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G158" s="87"/>
       <c r="H158" s="91"/>
-      <c r="I158" s="90"/>
+      <c r="I158" s="90">
+        <v>1</v>
+      </c>
       <c r="J158" s="76"/>
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
@@ -7962,7 +8028,7 @@
         <v>17</v>
       </c>
       <c r="C160" s="28" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D160" s="28" t="s">
         <v>20</v>
@@ -7996,7 +8062,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8149,7 +8215,7 @@
         <v>284</v>
       </c>
       <c r="F168" s="21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G168" s="86">
         <v>46318</v>
@@ -8266,11 +8332,13 @@
         <v>3</v>
       </c>
       <c r="F173" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G173" s="83"/>
       <c r="H173" s="91"/>
-      <c r="I173" s="90"/>
+      <c r="I173" s="90">
+        <v>1</v>
+      </c>
       <c r="J173" s="76"/>
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
@@ -8464,7 +8532,7 @@
         <v>17</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D180" s="28" t="s">
         <v>20</v>
@@ -8493,7 +8561,7 @@
         <v>17</v>
       </c>
       <c r="C181" s="28" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D181" s="28" t="s">
         <v>148</v>
@@ -8589,7 +8657,7 @@
         <v>284</v>
       </c>
       <c r="F184" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G184" s="87">
         <v>45953</v>
@@ -8705,7 +8773,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -8829,7 +8897,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -8961,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9087,13 +9155,13 @@
         <v>272</v>
       </c>
       <c r="D206" s="28" t="s">
-        <v>483</v>
+        <v>87</v>
       </c>
       <c r="E206" s="29">
         <v>1</v>
       </c>
       <c r="F206" s="30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G206" s="87"/>
       <c r="H206" s="90"/>
@@ -9174,11 +9242,13 @@
         <v>1</v>
       </c>
       <c r="F209" s="30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
-      <c r="I209" s="90"/>
+      <c r="I209" s="90">
+        <v>2</v>
+      </c>
       <c r="J209" s="76"/>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
@@ -9201,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="F210" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G210" s="87"/>
       <c r="H210" s="90"/>
@@ -9292,7 +9362,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9474,15 +9544,13 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
       </c>
       <c r="H223" s="92"/>
-      <c r="I223" s="93">
-        <v>3</v>
-      </c>
+      <c r="I223" s="93"/>
       <c r="J223" s="76"/>
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
@@ -9636,11 +9704,13 @@
         <v>5</v>
       </c>
       <c r="F229" s="30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G229" s="87"/>
       <c r="H229" s="91"/>
-      <c r="I229" s="89"/>
+      <c r="I229" s="89">
+        <v>1</v>
+      </c>
       <c r="J229" s="76"/>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -9754,7 +9824,7 @@
         <v>36</v>
       </c>
       <c r="F233" s="30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G233" s="87"/>
       <c r="H233" s="91"/>
@@ -9810,11 +9880,13 @@
         <v>8</v>
       </c>
       <c r="F235" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G235" s="83"/>
       <c r="H235" s="91"/>
-      <c r="I235" s="89"/>
+      <c r="I235" s="89">
+        <v>1</v>
+      </c>
       <c r="J235" s="76"/>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -9859,7 +9931,7 @@
         <v>17</v>
       </c>
       <c r="C237" s="28" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D237" s="28" t="s">
         <v>95</v>
@@ -9874,9 +9946,7 @@
         <v>46016</v>
       </c>
       <c r="H237" s="91"/>
-      <c r="I237" s="89">
-        <v>1</v>
-      </c>
+      <c r="I237" s="89"/>
       <c r="J237" s="76"/>
       <c r="K237" s="1"/>
       <c r="L237" s="1"/>
@@ -9930,13 +10000,15 @@
         <v>284</v>
       </c>
       <c r="F239" s="30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G239" s="87">
         <v>45911</v>
       </c>
       <c r="H239" s="91"/>
-      <c r="I239" s="89"/>
+      <c r="I239" s="89">
+        <v>2</v>
+      </c>
       <c r="J239" s="76"/>
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
@@ -9989,7 +10061,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10157,13 +10229,13 @@
       </c>
       <c r="C250" s="21"/>
       <c r="D250" s="21" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E250" s="22" t="s">
         <v>284</v>
       </c>
       <c r="F250" s="21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G250" s="86">
         <v>46037</v>
@@ -10263,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="F254" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G254" s="83"/>
       <c r="H254" s="91"/>
@@ -10343,10 +10415,10 @@
         <v>16</v>
       </c>
       <c r="C257" s="28" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D257" s="28" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E257" s="29" t="s">
         <v>284</v>
@@ -10510,13 +10582,15 @@
         <v>284</v>
       </c>
       <c r="F263" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G263" s="87">
         <v>45946</v>
       </c>
       <c r="H263" s="91"/>
-      <c r="I263" s="90"/>
+      <c r="I263" s="90">
+        <v>1</v>
+      </c>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1"/>
@@ -10652,10 +10726,10 @@
         <v>17</v>
       </c>
       <c r="C268" s="28" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D268" s="28" t="s">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="E268" s="29" t="s">
         <v>284</v>
@@ -10686,7 +10760,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -10839,13 +10913,15 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
       </c>
       <c r="H276" s="92"/>
-      <c r="I276" s="92"/>
+      <c r="I276" s="92">
+        <v>3</v>
+      </c>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
       <c r="L276" s="1"/>
@@ -11131,11 +11207,13 @@
         <v>1</v>
       </c>
       <c r="F288" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
-      <c r="I288" s="90"/>
+      <c r="I288" s="90">
+        <v>1</v>
+      </c>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
@@ -11189,7 +11267,7 @@
         <v>284</v>
       </c>
       <c r="F290" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G290" s="87">
         <v>45946</v>
@@ -11245,11 +11323,13 @@
         <v>1</v>
       </c>
       <c r="F292" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G292" s="87"/>
       <c r="H292" s="91"/>
-      <c r="I292" s="90"/>
+      <c r="I292" s="90">
+        <v>1</v>
+      </c>
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
@@ -11501,7 +11581,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -11524,7 +11604,7 @@
         <v>234</v>
       </c>
       <c r="D305" s="28" t="s">
-        <v>179</v>
+        <v>30</v>
       </c>
       <c r="E305" s="29">
         <v>2</v>
@@ -11623,7 +11703,7 @@
         <v>16</v>
       </c>
       <c r="C309" s="28" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D309" s="28" t="s">
         <v>64</v>
@@ -11743,7 +11823,7 @@
         <v>16</v>
       </c>
       <c r="C313" s="28" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D313" s="28" t="s">
         <v>86</v>
@@ -11839,13 +11919,15 @@
         <v>284</v>
       </c>
       <c r="F316" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G316" s="87">
         <v>45939</v>
       </c>
       <c r="H316" s="91"/>
-      <c r="I316" s="90"/>
+      <c r="I316" s="90">
+        <v>1</v>
+      </c>
       <c r="J316" s="1"/>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
@@ -11948,7 +12030,7 @@
         <v>17</v>
       </c>
       <c r="C320" s="28" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D320" s="28" t="s">
         <v>80</v>
@@ -12042,7 +12124,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12166,11 +12248,13 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
-      <c r="I329" s="90"/>
+      <c r="I329" s="90">
+        <v>1</v>
+      </c>
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
@@ -12320,7 +12404,7 @@
         <v>16</v>
       </c>
       <c r="C336" s="28" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D336" s="28" t="s">
         <v>19</v>
@@ -12345,23 +12429,27 @@
     </row>
     <row r="337" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="79"/>
-      <c r="B337" s="28" t="s">
+      <c r="B337" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C337" s="28" t="s">
+      <c r="C337" s="106" t="s">
         <v>180</v>
       </c>
-      <c r="D337" s="28" t="s">
+      <c r="D337" s="106" t="s">
         <v>160</v>
       </c>
-      <c r="E337" s="29">
+      <c r="E337" s="107">
         <v>1</v>
       </c>
-      <c r="F337" s="30">
+      <c r="F337" s="108">
         <v>2</v>
       </c>
-      <c r="G337" s="87"/>
-      <c r="H337" s="90"/>
+      <c r="G337" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H337" s="91">
+        <v>46072</v>
+      </c>
       <c r="I337" s="90"/>
       <c r="J337" s="1"/>
       <c r="K337" s="1"/>
@@ -12376,18 +12464,20 @@
         <v>16</v>
       </c>
       <c r="C338" s="28" t="s">
-        <v>279</v>
+        <v>531</v>
       </c>
       <c r="D338" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E338" s="29">
-        <v>1</v>
+        <v>103</v>
+      </c>
+      <c r="E338" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F338" s="30">
-        <v>3</v>
-      </c>
-      <c r="G338" s="83"/>
+        <v>0</v>
+      </c>
+      <c r="G338" s="87">
+        <v>46072</v>
+      </c>
       <c r="H338" s="91"/>
       <c r="I338" s="90"/>
       <c r="J338" s="1"/>
@@ -12399,11 +12489,21 @@
     </row>
     <row r="339" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="79"/>
-      <c r="B339" s="28"/>
-      <c r="C339" s="28"/>
-      <c r="D339" s="28"/>
-      <c r="E339" s="29"/>
-      <c r="F339" s="30"/>
+      <c r="B339" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C339" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="D339" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E339" s="29">
+        <v>1</v>
+      </c>
+      <c r="F339" s="30">
+        <v>3</v>
+      </c>
       <c r="G339" s="87"/>
       <c r="H339" s="91"/>
       <c r="I339" s="90"/>
@@ -12427,23 +12527,27 @@
     </row>
     <row r="341" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="79"/>
-      <c r="B341" s="28" t="s">
+      <c r="B341" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C341" s="28" t="s">
+      <c r="C341" s="106" t="s">
         <v>242</v>
       </c>
-      <c r="D341" s="28" t="s">
+      <c r="D341" s="106" t="s">
         <v>206</v>
       </c>
-      <c r="E341" s="29">
+      <c r="E341" s="107">
         <v>1</v>
       </c>
-      <c r="F341" s="30">
+      <c r="F341" s="108">
         <v>1</v>
       </c>
-      <c r="G341" s="83"/>
-      <c r="H341" s="91"/>
+      <c r="G341" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H341" s="91">
+        <v>46072</v>
+      </c>
       <c r="I341" s="90"/>
       <c r="J341" s="1"/>
       <c r="N341" s="1"/>
@@ -12455,20 +12559,24 @@
         <v>17</v>
       </c>
       <c r="C342" s="28" t="s">
-        <v>142</v>
+        <v>532</v>
       </c>
       <c r="D342" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E342" s="29">
+        <v>156</v>
+      </c>
+      <c r="E342" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F342" s="30">
         <v>1</v>
       </c>
-      <c r="F342" s="30">
-        <v>9</v>
-      </c>
-      <c r="G342" s="87"/>
+      <c r="G342" s="87">
+        <v>46072</v>
+      </c>
       <c r="H342" s="91"/>
-      <c r="I342" s="90"/>
+      <c r="I342" s="90">
+        <v>1</v>
+      </c>
       <c r="J342" s="1"/>
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
@@ -12479,43 +12587,49 @@
         <v>17</v>
       </c>
       <c r="C343" s="28" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D343" s="28" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="E343" s="29">
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
-      <c r="I343" s="90"/>
+      <c r="I343" s="90">
+        <v>1</v>
+      </c>
       <c r="J343" s="1"/>
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
     <row r="344" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="79"/>
-      <c r="B344" s="28" t="s">
+      <c r="B344" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C344" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="D344" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E344" s="29">
+      <c r="C344" s="106" t="s">
+        <v>127</v>
+      </c>
+      <c r="D344" s="106" t="s">
+        <v>121</v>
+      </c>
+      <c r="E344" s="107">
         <v>1</v>
       </c>
-      <c r="F344" s="30">
-        <v>10</v>
-      </c>
-      <c r="G344" s="83"/>
-      <c r="H344" s="91"/>
+      <c r="F344" s="108">
+        <v>3</v>
+      </c>
+      <c r="G344" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H344" s="91">
+        <v>46072</v>
+      </c>
       <c r="I344" s="90"/>
       <c r="J344" s="1"/>
       <c r="N344" s="1"/>
@@ -12523,28 +12637,28 @@
     </row>
     <row r="345" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="79"/>
-      <c r="B345" s="106" t="s">
+      <c r="B345" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C345" s="106" t="s">
-        <v>281</v>
-      </c>
-      <c r="D345" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="E345" s="107">
+      <c r="C345" s="28" t="s">
+        <v>430</v>
+      </c>
+      <c r="D345" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E345" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F345" s="30">
         <v>1</v>
       </c>
-      <c r="F345" s="108">
-        <v>0</v>
-      </c>
-      <c r="G345" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H345" s="91">
-        <v>45932</v>
-      </c>
-      <c r="I345" s="90"/>
+      <c r="G345" s="87">
+        <v>46072</v>
+      </c>
+      <c r="H345" s="91"/>
+      <c r="I345" s="90">
+        <v>1</v>
+      </c>
       <c r="J345" s="1"/>
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
@@ -12555,20 +12669,18 @@
         <v>17</v>
       </c>
       <c r="C346" s="28" t="s">
-        <v>456</v>
+        <v>280</v>
       </c>
       <c r="D346" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="E346" s="29" t="s">
-        <v>284</v>
+        <v>132</v>
+      </c>
+      <c r="E346" s="29">
+        <v>1</v>
       </c>
       <c r="F346" s="30">
-        <v>12</v>
-      </c>
-      <c r="G346" s="87">
-        <v>45932</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G346" s="83"/>
       <c r="H346" s="91"/>
       <c r="I346" s="90"/>
       <c r="J346" s="1"/>
@@ -12577,13 +12689,27 @@
     </row>
     <row r="347" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="79"/>
-      <c r="B347" s="28"/>
-      <c r="C347" s="28"/>
-      <c r="D347" s="28"/>
-      <c r="E347" s="29"/>
-      <c r="F347" s="30"/>
-      <c r="G347" s="87"/>
-      <c r="H347" s="91"/>
+      <c r="B347" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C347" s="106" t="s">
+        <v>281</v>
+      </c>
+      <c r="D347" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="E347" s="107">
+        <v>1</v>
+      </c>
+      <c r="F347" s="108">
+        <v>0</v>
+      </c>
+      <c r="G347" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H347" s="91">
+        <v>45932</v>
+      </c>
       <c r="I347" s="90"/>
       <c r="J347" s="1"/>
       <c r="N347" s="1"/>
@@ -12591,12 +12717,24 @@
     </row>
     <row r="348" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="79"/>
-      <c r="B348" s="28"/>
-      <c r="C348" s="28"/>
-      <c r="D348" s="28"/>
-      <c r="E348" s="29"/>
-      <c r="F348" s="30"/>
-      <c r="G348" s="87"/>
+      <c r="B348" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C348" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="D348" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E348" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F348" s="30">
+        <v>13</v>
+      </c>
+      <c r="G348" s="87">
+        <v>45932</v>
+      </c>
       <c r="H348" s="91"/>
       <c r="I348" s="90"/>
       <c r="J348" s="1"/>
@@ -12628,7 +12766,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -12753,7 +12891,7 @@
         <v>4</v>
       </c>
       <c r="F359" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
@@ -12806,7 +12944,7 @@
         <v>32</v>
       </c>
       <c r="F362" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" s="1"/>
@@ -12843,7 +12981,7 @@
         <v>16</v>
       </c>
       <c r="C364" s="28" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D364" s="28" t="s">
         <v>18</v>
@@ -12976,11 +13114,13 @@
         <v>5</v>
       </c>
       <c r="F370" s="30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G370" s="103"/>
       <c r="H370" s="1"/>
-      <c r="I370" s="1"/>
+      <c r="I370" s="1">
+        <v>2</v>
+      </c>
       <c r="J370" s="1"/>
     </row>
     <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -13013,7 +13153,7 @@
         <v>17</v>
       </c>
       <c r="C372" s="28" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D372" s="28" t="s">
         <v>288</v>
@@ -13125,7 +13265,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -13494,19 +13634,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="E7" s="25">
         <v>35</v>
       </c>
       <c r="F7" s="26">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G7" s="27">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13519,19 +13659,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="E8" s="25">
-        <v>31</v>
-      </c>
-      <c r="F8" s="26">
-        <v>64</v>
-      </c>
-      <c r="G8" s="27">
         <v>33</v>
+      </c>
+      <c r="F8" s="56">
+        <v>83</v>
+      </c>
+      <c r="G8" s="57">
+        <v>50</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13544,19 +13684,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>1</v>
+        <v>32</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>31</v>
       </c>
       <c r="E9" s="25">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" s="26">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G9" s="27">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13569,19 +13709,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="25">
         <v>31</v>
       </c>
-      <c r="E10" s="25">
-        <v>29</v>
-      </c>
       <c r="F10" s="26">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G10" s="27">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13594,19 +13734,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>203</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E11" s="25">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="26">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G11" s="27">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13619,19 +13759,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E12" s="25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" s="26">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G12" s="27">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13646,17 +13786,17 @@
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="24" t="s">
         <v>267</v>
       </c>
       <c r="E13" s="25">
-        <v>20</v>
-      </c>
-      <c r="F13" s="56">
-        <v>70</v>
-      </c>
-      <c r="G13" s="57">
-        <v>50</v>
+        <v>23</v>
+      </c>
+      <c r="F13" s="26">
+        <v>77</v>
+      </c>
+      <c r="G13" s="27">
+        <v>54</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -13671,17 +13811,17 @@
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="55" t="s">
         <v>188</v>
       </c>
       <c r="E14" s="25">
         <v>20</v>
       </c>
-      <c r="F14" s="26">
-        <v>60</v>
-      </c>
-      <c r="G14" s="27">
-        <v>40</v>
+      <c r="F14" s="56">
+        <v>66</v>
+      </c>
+      <c r="G14" s="57">
+        <v>46</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -13694,19 +13834,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>244</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E15" s="25">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F15" s="26">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G15" s="27">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -13719,19 +13859,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D16" s="55" t="s">
-        <v>245</v>
+        <v>66</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>243</v>
       </c>
       <c r="E16" s="25">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F16" s="26">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" s="27">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -13746,17 +13886,17 @@
       <c r="C17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="24" t="s">
         <v>140</v>
       </c>
       <c r="E17" s="25">
         <v>8</v>
       </c>
-      <c r="F17" s="56">
-        <v>54</v>
-      </c>
-      <c r="G17" s="57">
-        <v>46</v>
+      <c r="F17" s="26">
+        <v>58</v>
+      </c>
+      <c r="G17" s="27">
+        <v>50</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -13775,13 +13915,13 @@
         <v>222</v>
       </c>
       <c r="E18" s="25">
-        <v>5</v>
-      </c>
-      <c r="F18" s="56">
-        <v>60</v>
-      </c>
-      <c r="G18" s="57">
-        <v>55</v>
+        <v>4</v>
+      </c>
+      <c r="F18" s="26">
+        <v>62</v>
+      </c>
+      <c r="G18" s="27">
+        <v>58</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -13796,17 +13936,17 @@
       <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="25">
-        <v>3</v>
-      </c>
-      <c r="F19" s="26">
-        <v>45</v>
-      </c>
-      <c r="G19" s="27">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="F19" s="56">
+        <v>47</v>
+      </c>
+      <c r="G19" s="57">
+        <v>43</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -13825,13 +13965,13 @@
         <v>53</v>
       </c>
       <c r="E20" s="25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="26">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G20" s="27">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>
@@ -13884,7 +14024,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:IW29"/>
+  <dimension ref="A1:IW31"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33.296875" style="38" customWidth="1"/>
@@ -13946,10 +14086,10 @@
         <v>467</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -13963,7 +14103,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E5" s="68" t="s">
         <v>267</v>
@@ -13972,13 +14112,13 @@
         <v>3</v>
       </c>
       <c r="G5" s="64" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -14001,13 +14141,13 @@
         <v>3</v>
       </c>
       <c r="G6" s="64" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -14030,13 +14170,13 @@
         <v>-1</v>
       </c>
       <c r="G7" s="100" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I7" s="38" t="s">
         <v>40</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -14085,7 +14225,7 @@
         <v>467</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -14103,7 +14243,7 @@
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C11" s="68"/>
       <c r="D11" s="64"/>
@@ -14164,13 +14304,21 @@
       <c r="B15" s="65" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="64"/>
+      <c r="C15" s="68">
+        <v>1</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>433</v>
+      </c>
       <c r="E15" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="68"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="68">
+        <v>1</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
@@ -14179,28 +14327,44 @@
       <c r="B16" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="65" t="s">
-        <v>530</v>
-      </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="64"/>
+      <c r="C16" s="68">
+        <v>2</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="70" t="s">
+        <v>528</v>
+      </c>
+      <c r="F16" s="69">
+        <v>1</v>
+      </c>
+      <c r="G16" s="100" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="70" t="s">
         <v>243</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="64"/>
+      <c r="C17" s="69">
+        <v>2</v>
+      </c>
+      <c r="D17" s="100" t="s">
+        <v>534</v>
+      </c>
       <c r="E17" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="64"/>
+      <c r="F17" s="68">
+        <v>3</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="67" t="s">
@@ -14209,13 +14373,21 @@
       <c r="B18" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="65" t="s">
+      <c r="C18" s="68">
+        <v>0</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="E18" s="70" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="64"/>
+      <c r="F18" s="69">
+        <v>-1</v>
+      </c>
+      <c r="G18" s="100" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
@@ -14225,101 +14397,127 @@
       <c r="F19" s="66"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="65"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="40"/>
-    </row>
-    <row r="21" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="63" t="s">
+    <row r="20" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="67"/>
+      <c r="B20" s="63" t="s">
+        <v>535</v>
+      </c>
+      <c r="C20" s="68"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="64"/>
+    </row>
+    <row r="21" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+    </row>
+    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="65"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="40"/>
+    </row>
+    <row r="23" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="66"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="40"/>
-    </row>
-    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="67" t="s">
+      <c r="C23" s="66"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="40"/>
+    </row>
+    <row r="24" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="100"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="64"/>
-    </row>
-    <row r="23" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="67" t="s">
+      <c r="B24" s="70"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="64"/>
+    </row>
+    <row r="25" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="100"/>
-    </row>
-    <row r="24" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-    </row>
-    <row r="25" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="65"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="100"/>
+    </row>
+    <row r="26" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+    </row>
+    <row r="27" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-    </row>
-    <row r="26" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="67" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="65"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="100"/>
-    </row>
-    <row r="27" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="64"/>
-      <c r="E27" s="40"/>
+      <c r="E27" s="65"/>
       <c r="F27" s="40"/>
       <c r="G27" s="40"/>
     </row>
-    <row r="28" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="K28" s="98"/>
-    </row>
-    <row r="29" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="65"/>
+    <row r="28" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="67" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="65"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="100"/>
+    </row>
+    <row r="29" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="40"/>
       <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
+      <c r="D29" s="64"/>
       <c r="E29" s="40"/>
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
+    </row>
+    <row r="30" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="K30" s="98"/>
+    </row>
+    <row r="31" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="65"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15621,7 +15819,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="100" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E36" s="65" t="s">
         <v>233</v>
@@ -15630,7 +15828,7 @@
         <v>4</v>
       </c>
       <c r="G36" s="64" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H36" s="38"/>
       <c r="I36" s="38"/>
@@ -15713,7 +15911,7 @@
         <v>5</v>
       </c>
       <c r="D39" s="64" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E39" s="70" t="s">
         <v>233</v>
@@ -16438,7 +16636,7 @@
       </c>
       <c r="K6">
         <f>COUNTIF(Stats!D:D,'Player Count'!J6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="109"/>
       <c r="N6" s="67" t="s">
@@ -16495,7 +16693,7 @@
       </c>
       <c r="G8">
         <f>COUNTIF(Stats!D:D,'Player Count'!F8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="s">
         <v>345</v>
@@ -16534,7 +16732,7 @@
       </c>
       <c r="K9">
         <f>COUNTIF(Stats!D:D,'Player Count'!J9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" s="109"/>
       <c r="N9" t="s">
@@ -16926,7 +17124,7 @@
       </c>
       <c r="O21">
         <f>COUNTIF(Stats!D:D,'Player Count'!N21)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="109"/>
     </row>
@@ -16950,7 +17148,7 @@
       </c>
       <c r="K22">
         <f>COUNTIF(Stats!D:D,'Player Count'!J22)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="109"/>
       <c r="N22" s="67" t="s">
@@ -17032,7 +17230,7 @@
       </c>
       <c r="C25">
         <f>COUNTIF(Stats!D:D,'Player Count'!B25)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
         <v>338</v>
@@ -17064,7 +17262,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
         <v>339</v>
@@ -17146,21 +17344,21 @@
       </c>
       <c r="G29">
         <f>COUNTIF(Stats!D:D,'Player Count'!F29)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="67" t="s">
         <v>367</v>
       </c>
       <c r="K29">
         <f>COUNTIF(Stats!D:D,'Player Count'!J29)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29" t="s">
         <v>390</v>
       </c>
       <c r="O29">
         <f>COUNTIF(Stats!D:D,'Player Count'!N29)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.3">
@@ -17169,14 +17367,14 @@
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>317</v>
@@ -17192,28 +17390,28 @@
       </c>
       <c r="C38" s="114">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.37444933920704848</v>
+        <v>0.36752136752136755</v>
       </c>
       <c r="D38" s="114"/>
       <c r="E38" s="114"/>
       <c r="F38" s="114"/>
       <c r="G38" s="114">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.27312775330396477</v>
+        <v>0.27350427350427353</v>
       </c>
       <c r="H38" s="114"/>
       <c r="I38" s="114"/>
       <c r="J38" s="114"/>
       <c r="K38" s="114">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.1894273127753304</v>
+        <v>0.20085470085470086</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114"/>
       <c r="N38" s="114"/>
       <c r="O38" s="114">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.16299559471365638</v>
+        <v>0.15811965811965811</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1191" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12189F22-E748-47CA-A971-48C005002AA1}"/>
+  <xr:revisionPtr revIDLastSave="1246" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BF0BACC-3AC6-4588-93AB-A7C4040275F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,8 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="536">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -3698,13 +3697,11 @@
         <v>1</v>
       </c>
       <c r="F5" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="83"/>
       <c r="H5" s="84"/>
-      <c r="I5" s="85">
-        <v>1</v>
-      </c>
+      <c r="I5" s="85"/>
       <c r="J5" s="82"/>
       <c r="K5" s="16" t="str">
         <f>D2</f>
@@ -3716,7 +3713,7 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
@@ -3724,7 +3721,7 @@
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3751,15 +3748,15 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3786,15 +3783,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3830,15 +3827,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3872,15 +3869,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3918,7 +3915,7 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
@@ -3926,7 +3923,7 @@
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -3971,11 +3968,11 @@
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -4016,11 +4013,11 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
@@ -4060,15 +4057,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4111,11 +4108,11 @@
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -4156,15 +4153,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4200,11 +4197,11 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
@@ -4242,11 +4239,11 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
@@ -4297,11 +4294,11 @@
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4359,9 +4356,7 @@
         <v>45932</v>
       </c>
       <c r="H20" s="84"/>
-      <c r="I20" s="99">
-        <v>1</v>
-      </c>
+      <c r="I20" s="99"/>
       <c r="J20" s="76"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4547,7 +4542,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4705,15 +4700,13 @@
         <v>284</v>
       </c>
       <c r="F33" s="21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" s="86">
         <v>46072</v>
       </c>
       <c r="H33" s="94"/>
-      <c r="I33" s="93">
-        <v>2</v>
-      </c>
+      <c r="I33" s="93"/>
       <c r="J33" s="76"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -4780,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="91"/>
       <c r="H36" s="91"/>
@@ -5212,15 +5205,13 @@
         <v>284</v>
       </c>
       <c r="F51" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51" s="91">
         <v>46051</v>
       </c>
       <c r="H51" s="91"/>
-      <c r="I51" s="89">
-        <v>3</v>
-      </c>
+      <c r="I51" s="89"/>
       <c r="J51" s="76"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -5266,7 +5257,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5390,13 +5381,11 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
-      <c r="I59" s="92">
-        <v>1</v>
-      </c>
+      <c r="I59" s="92"/>
       <c r="J59" s="76"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -5524,7 +5513,7 @@
         <v>30</v>
       </c>
       <c r="F65" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65" s="83"/>
       <c r="H65" s="90"/>
@@ -5551,7 +5540,7 @@
         <v>5</v>
       </c>
       <c r="F66" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G66" s="83"/>
       <c r="H66" s="91"/>
@@ -5746,7 +5735,7 @@
         <v>284</v>
       </c>
       <c r="F73" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G73" s="87">
         <v>45897</v>
@@ -5775,7 +5764,7 @@
         <v>7</v>
       </c>
       <c r="F74" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G74" s="87"/>
       <c r="H74" s="91"/>
@@ -5949,7 +5938,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6073,7 +6062,7 @@
         <v>8</v>
       </c>
       <c r="F86" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -6327,9 +6316,7 @@
       </c>
       <c r="G96" s="91"/>
       <c r="H96" s="91"/>
-      <c r="I96" s="90">
-        <v>2</v>
-      </c>
+      <c r="I96" s="90"/>
       <c r="J96" s="76"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -6369,7 +6356,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G98" s="87"/>
       <c r="H98" s="91"/>
@@ -6516,7 +6503,7 @@
         <v>22</v>
       </c>
       <c r="F103" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G103" s="87"/>
       <c r="H103" s="91"/>
@@ -6630,7 +6617,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6754,13 +6741,11 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
-      <c r="I113" s="90">
-        <v>1</v>
-      </c>
+      <c r="I113" s="90"/>
       <c r="J113" s="76"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -6915,7 +6900,7 @@
         <v>20</v>
       </c>
       <c r="F120" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G120" s="87"/>
       <c r="H120" s="91"/>
@@ -6979,9 +6964,7 @@
         <v>45974</v>
       </c>
       <c r="H122" s="91"/>
-      <c r="I122" s="90">
-        <v>1</v>
-      </c>
+      <c r="I122" s="90"/>
       <c r="J122" s="76"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
@@ -7130,9 +7113,7 @@
         <v>46023</v>
       </c>
       <c r="H127" s="91"/>
-      <c r="I127" s="90">
-        <v>2</v>
-      </c>
+      <c r="I127" s="90"/>
       <c r="J127" s="76"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
@@ -7223,9 +7204,7 @@
         <v>46058</v>
       </c>
       <c r="H130" s="91"/>
-      <c r="I130" s="90">
-        <v>1</v>
-      </c>
+      <c r="I130" s="90"/>
       <c r="J130" s="76"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
@@ -7248,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="30">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G131" s="87"/>
       <c r="H131" s="91"/>
@@ -7331,7 +7310,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7513,15 +7492,13 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
       </c>
       <c r="H142" s="92"/>
-      <c r="I142" s="118">
-        <v>2</v>
-      </c>
+      <c r="I142" s="118"/>
       <c r="J142" s="76"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1"/>
@@ -7706,9 +7683,7 @@
         <v>45974</v>
       </c>
       <c r="H149" s="91"/>
-      <c r="I149" s="90">
-        <v>1</v>
-      </c>
+      <c r="I149" s="90"/>
       <c r="J149" s="76"/>
       <c r="K149" s="1"/>
       <c r="L149" s="1"/>
@@ -7768,9 +7743,7 @@
         <v>46030</v>
       </c>
       <c r="H151" s="91"/>
-      <c r="I151" s="90">
-        <v>1</v>
-      </c>
+      <c r="I151" s="90"/>
       <c r="J151" s="76"/>
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
@@ -7830,9 +7803,7 @@
         <v>46072</v>
       </c>
       <c r="H153" s="91"/>
-      <c r="I153" s="90">
-        <v>2</v>
-      </c>
+      <c r="I153" s="90"/>
       <c r="J153" s="96"/>
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
@@ -7981,9 +7952,7 @@
       </c>
       <c r="G158" s="87"/>
       <c r="H158" s="91"/>
-      <c r="I158" s="90">
-        <v>1</v>
-      </c>
+      <c r="I158" s="90"/>
       <c r="J158" s="76"/>
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
@@ -8062,7 +8031,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8215,7 +8184,7 @@
         <v>284</v>
       </c>
       <c r="F168" s="21">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G168" s="86">
         <v>46318</v>
@@ -8332,13 +8301,11 @@
         <v>3</v>
       </c>
       <c r="F173" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G173" s="83"/>
       <c r="H173" s="91"/>
-      <c r="I173" s="90">
-        <v>1</v>
-      </c>
+      <c r="I173" s="90"/>
       <c r="J173" s="76"/>
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
@@ -8423,7 +8390,7 @@
         <v>284</v>
       </c>
       <c r="F176" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G176" s="91">
         <v>45953</v>
@@ -8958,7 +8925,7 @@
         <v>1</v>
       </c>
       <c r="F197" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" s="83"/>
       <c r="H197" s="91"/>
@@ -9029,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9246,9 +9213,7 @@
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
-      <c r="I209" s="90">
-        <v>2</v>
-      </c>
+      <c r="I209" s="90"/>
       <c r="J209" s="76"/>
       <c r="K209" s="1"/>
       <c r="L209" s="1"/>
@@ -9362,7 +9327,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9544,7 +9509,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9708,9 +9673,7 @@
       </c>
       <c r="G229" s="87"/>
       <c r="H229" s="91"/>
-      <c r="I229" s="89">
-        <v>1</v>
-      </c>
+      <c r="I229" s="89"/>
       <c r="J229" s="76"/>
       <c r="K229" s="1"/>
       <c r="L229" s="1"/>
@@ -9828,9 +9791,7 @@
       </c>
       <c r="G233" s="87"/>
       <c r="H233" s="91"/>
-      <c r="I233" s="89">
-        <v>2</v>
-      </c>
+      <c r="I233" s="89"/>
       <c r="J233" s="1"/>
       <c r="K233" s="1"/>
       <c r="L233" s="1"/>
@@ -9853,7 +9814,7 @@
         <v>20</v>
       </c>
       <c r="F234" s="30">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G234" s="87"/>
       <c r="H234" s="91"/>
@@ -9884,9 +9845,7 @@
       </c>
       <c r="G235" s="83"/>
       <c r="H235" s="91"/>
-      <c r="I235" s="89">
-        <v>1</v>
-      </c>
+      <c r="I235" s="89"/>
       <c r="J235" s="76"/>
       <c r="K235" s="1"/>
       <c r="L235" s="1"/>
@@ -10006,9 +9965,7 @@
         <v>45911</v>
       </c>
       <c r="H239" s="91"/>
-      <c r="I239" s="89">
-        <v>2</v>
-      </c>
+      <c r="I239" s="89"/>
       <c r="J239" s="76"/>
       <c r="K239" s="1"/>
       <c r="L239" s="1"/>
@@ -10061,7 +10018,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10235,13 +10192,15 @@
         <v>284</v>
       </c>
       <c r="F250" s="21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G250" s="86">
         <v>46037</v>
       </c>
       <c r="H250" s="92"/>
-      <c r="I250" s="92"/>
+      <c r="I250" s="92">
+        <v>1</v>
+      </c>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
       <c r="L250" s="1"/>
@@ -10588,9 +10547,7 @@
         <v>45946</v>
       </c>
       <c r="H263" s="91"/>
-      <c r="I263" s="90">
-        <v>1</v>
-      </c>
+      <c r="I263" s="90"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
       <c r="L263" s="1"/>
@@ -10644,13 +10601,15 @@
         <v>284</v>
       </c>
       <c r="F265" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G265" s="87">
         <v>45953</v>
       </c>
       <c r="H265" s="91"/>
-      <c r="I265" s="90"/>
+      <c r="I265" s="90">
+        <v>1</v>
+      </c>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
       <c r="L265" s="1"/>
@@ -10913,15 +10872,13 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
       </c>
       <c r="H276" s="92"/>
-      <c r="I276" s="92">
-        <v>3</v>
-      </c>
+      <c r="I276" s="92"/>
       <c r="J276" s="1"/>
       <c r="K276" s="1"/>
       <c r="L276" s="1"/>
@@ -11207,13 +11164,11 @@
         <v>1</v>
       </c>
       <c r="F288" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
-      <c r="I288" s="90">
-        <v>1</v>
-      </c>
+      <c r="I288" s="90"/>
       <c r="J288" s="1"/>
       <c r="K288" s="1"/>
       <c r="L288" s="1"/>
@@ -11267,7 +11222,7 @@
         <v>284</v>
       </c>
       <c r="F290" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G290" s="87">
         <v>45946</v>
@@ -11323,13 +11278,11 @@
         <v>1</v>
       </c>
       <c r="F292" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G292" s="87"/>
       <c r="H292" s="91"/>
-      <c r="I292" s="90">
-        <v>1</v>
-      </c>
+      <c r="I292" s="90"/>
       <c r="J292" s="1"/>
       <c r="K292" s="1"/>
       <c r="L292" s="1"/>
@@ -11399,7 +11352,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11832,7 +11785,7 @@
         <v>284</v>
       </c>
       <c r="F313" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G313" s="87">
         <v>45961</v>
@@ -11925,9 +11878,7 @@
         <v>45939</v>
       </c>
       <c r="H316" s="91"/>
-      <c r="I316" s="90">
-        <v>1</v>
-      </c>
+      <c r="I316" s="90"/>
       <c r="J316" s="1"/>
       <c r="K316" s="1"/>
       <c r="L316" s="1"/>
@@ -12124,7 +12075,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12252,9 +12203,7 @@
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
-      <c r="I329" s="90">
-        <v>1</v>
-      </c>
+      <c r="I329" s="90"/>
       <c r="J329" s="1"/>
       <c r="K329" s="1"/>
       <c r="L329" s="1"/>
@@ -12540,7 +12489,7 @@
         <v>1</v>
       </c>
       <c r="F341" s="108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G341" s="83" t="s">
         <v>285</v>
@@ -12574,9 +12523,7 @@
         <v>46072</v>
       </c>
       <c r="H342" s="91"/>
-      <c r="I342" s="90">
-        <v>1</v>
-      </c>
+      <c r="I342" s="90"/>
       <c r="J342" s="1"/>
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
@@ -12600,9 +12547,7 @@
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
-      <c r="I343" s="90">
-        <v>1</v>
-      </c>
+      <c r="I343" s="90"/>
       <c r="J343" s="1"/>
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
@@ -12656,9 +12601,7 @@
         <v>46072</v>
       </c>
       <c r="H345" s="91"/>
-      <c r="I345" s="90">
-        <v>1</v>
-      </c>
+      <c r="I345" s="90"/>
       <c r="J345" s="1"/>
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
@@ -12766,7 +12709,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -12848,7 +12791,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -12891,7 +12834,7 @@
         <v>4</v>
       </c>
       <c r="F359" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
@@ -13118,9 +13061,7 @@
       </c>
       <c r="G370" s="103"/>
       <c r="H370" s="1"/>
-      <c r="I370" s="1">
-        <v>2</v>
-      </c>
+      <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
     <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -13640,13 +13581,13 @@
         <v>203</v>
       </c>
       <c r="E7" s="25">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" s="26">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" s="27">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13665,12 +13606,12 @@
         <v>233</v>
       </c>
       <c r="E8" s="25">
-        <v>33</v>
-      </c>
-      <c r="F8" s="56">
-        <v>83</v>
-      </c>
-      <c r="G8" s="57">
+        <v>34</v>
+      </c>
+      <c r="F8" s="26">
+        <v>84</v>
+      </c>
+      <c r="G8" s="27">
         <v>50</v>
       </c>
       <c r="H8" s="52"/>
@@ -13684,19 +13625,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>31</v>
+        <v>198</v>
       </c>
       <c r="E9" s="25">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="26">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G9" s="27">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13709,19 +13650,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="E10" s="25">
         <v>31</v>
       </c>
       <c r="F10" s="26">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G10" s="27">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13734,19 +13675,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E11" s="25">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="26">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G11" s="27">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13765,13 +13706,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" s="26">
         <v>57</v>
       </c>
       <c r="G12" s="27">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13790,13 +13731,13 @@
         <v>267</v>
       </c>
       <c r="E13" s="25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="26">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" s="27">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -13815,13 +13756,13 @@
         <v>188</v>
       </c>
       <c r="E14" s="25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="56">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G14" s="57">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -13834,19 +13775,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>245</v>
+        <v>66</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>243</v>
       </c>
       <c r="E15" s="25">
-        <v>14</v>
-      </c>
-      <c r="F15" s="26">
-        <v>53</v>
-      </c>
-      <c r="G15" s="27">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="F15" s="56">
+        <v>52</v>
+      </c>
+      <c r="G15" s="57">
+        <v>37</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -13859,19 +13800,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>66</v>
+        <v>244</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E16" s="25">
         <v>14</v>
       </c>
       <c r="F16" s="26">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G16" s="27">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -13890,13 +13831,13 @@
         <v>140</v>
       </c>
       <c r="E17" s="25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" s="26">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G17" s="27">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -13911,17 +13852,17 @@
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="24" t="s">
         <v>222</v>
       </c>
       <c r="E18" s="25">
         <v>4</v>
       </c>
       <c r="F18" s="26">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="27">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -13936,17 +13877,17 @@
       <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="24" t="s">
         <v>34</v>
       </c>
       <c r="E19" s="25">
         <v>4</v>
       </c>
-      <c r="F19" s="56">
-        <v>47</v>
-      </c>
-      <c r="G19" s="57">
-        <v>43</v>
+      <c r="F19" s="26">
+        <v>49</v>
+      </c>
+      <c r="G19" s="27">
+        <v>45</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -13961,16 +13902,16 @@
       <c r="C20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="55" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="25">
-        <v>0</v>
-      </c>
-      <c r="F20" s="26">
-        <v>45</v>
-      </c>
-      <c r="G20" s="27">
+        <v>3</v>
+      </c>
+      <c r="F20" s="56">
+        <v>48</v>
+      </c>
+      <c r="G20" s="57">
         <v>45</v>
       </c>
       <c r="H20" s="117"/>
@@ -14410,18 +14351,26 @@
     </row>
     <row r="21" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B21" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
+      <c r="C21" s="64">
+        <v>0</v>
+      </c>
+      <c r="D21" s="64" t="s">
+        <v>436</v>
+      </c>
       <c r="E21" s="68" t="s">
         <v>233</v>
       </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
+      <c r="F21" s="64">
+        <v>0</v>
+      </c>
+      <c r="G21" s="64" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="65"/>
@@ -14443,7 +14392,7 @@
     </row>
     <row r="24" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="70"/>
       <c r="C24" s="69"/>
@@ -14454,7 +14403,7 @@
     </row>
     <row r="25" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="B25" s="65"/>
       <c r="C25" s="68"/>
@@ -14483,7 +14432,7 @@
     </row>
     <row r="28" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="B28" s="65"/>
       <c r="C28" s="68"/>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1246" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BF0BACC-3AC6-4588-93AB-A7C4040275F4}"/>
+  <xr:revisionPtr revIDLastSave="1473" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC201A0E-6B28-4587-A2BF-F0DB5A37943A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="545">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1647,6 +1647,33 @@
   </si>
   <si>
     <t>Qtr Final Replays</t>
+  </si>
+  <si>
+    <t>DAVID MCGOLDRICK</t>
+  </si>
+  <si>
+    <t>BARNSLEY</t>
+  </si>
+  <si>
+    <t>DOMINIK SZOBOSZLAI</t>
+  </si>
+  <si>
+    <t>ROB STREET</t>
+  </si>
+  <si>
+    <t>EVANN GUESSAND</t>
+  </si>
+  <si>
+    <t>MARVIN DUCKSCH</t>
+  </si>
+  <si>
+    <t>ADAMA SIDIBEH</t>
+  </si>
+  <si>
+    <t>Semi Final Replay</t>
+  </si>
+  <si>
+    <t>BARROW</t>
   </si>
 </sst>
 </file>
@@ -3686,21 +3713,25 @@
     </row>
     <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="111"/>
+      <c r="D5" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="112">
         <v>1</v>
       </c>
-      <c r="F5" s="15">
-        <v>30</v>
-      </c>
-      <c r="G5" s="83"/>
-      <c r="H5" s="84"/>
+      <c r="F5" s="113">
+        <v>32</v>
+      </c>
+      <c r="G5" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H5" s="84">
+        <v>46093</v>
+      </c>
       <c r="I5" s="85"/>
       <c r="J5" s="82"/>
       <c r="K5" s="16" t="str">
@@ -3713,15 +3744,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3729,14 +3760,26 @@
     </row>
     <row r="6" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
-      <c r="B6" s="21"/>
+      <c r="B6" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="86"/>
+      <c r="D6" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="F6" s="21">
+        <v>3</v>
+      </c>
+      <c r="G6" s="86">
+        <v>46093</v>
+      </c>
       <c r="H6" s="84"/>
-      <c r="I6" s="81"/>
+      <c r="I6" s="81">
+        <v>1</v>
+      </c>
       <c r="J6" s="79"/>
       <c r="K6" s="23" t="str">
         <f>D29</f>
@@ -3748,15 +3791,15 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3783,15 +3826,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3827,15 +3870,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3869,15 +3912,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3915,15 +3958,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -3964,15 +4007,15 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -4013,15 +4056,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4039,13 +4082,15 @@
         <v>284</v>
       </c>
       <c r="F13" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="87">
         <v>45932</v>
       </c>
       <c r="H13" s="84"/>
-      <c r="I13" s="99"/>
+      <c r="I13" s="99">
+        <v>1</v>
+      </c>
       <c r="J13" s="82"/>
       <c r="K13" s="71" t="str">
         <f>D218</f>
@@ -4057,15 +4102,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4088,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="87"/>
       <c r="H14" s="84"/>
@@ -4104,15 +4149,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -4153,15 +4198,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4201,11 +4246,11 @@
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4239,7 +4284,7 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
@@ -4247,7 +4292,7 @@
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R17" s="119"/>
       <c r="S17" s="119"/>
@@ -4290,15 +4335,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4350,7 +4395,7 @@
         <v>284</v>
       </c>
       <c r="F20" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="87">
         <v>45932</v>
@@ -4542,7 +4587,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4700,7 +4745,7 @@
         <v>284</v>
       </c>
       <c r="F33" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G33" s="86">
         <v>46072</v>
@@ -4817,7 +4862,7 @@
         <v>32</v>
       </c>
       <c r="F38" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" s="83"/>
       <c r="H38" s="91"/>
@@ -4849,7 +4894,7 @@
         <v>12</v>
       </c>
       <c r="F39" s="30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -4876,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="30">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G40" s="87"/>
       <c r="H40" s="91"/>
@@ -4965,7 +5010,7 @@
         <v>284</v>
       </c>
       <c r="F43" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="87">
         <v>46051</v>
@@ -4994,7 +5039,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -5205,7 +5250,7 @@
         <v>284</v>
       </c>
       <c r="F51" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G51" s="91">
         <v>46051</v>
@@ -5234,7 +5279,7 @@
         <v>24</v>
       </c>
       <c r="F52" s="30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G52" s="87"/>
       <c r="H52" s="91"/>
@@ -5257,7 +5302,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5381,7 +5426,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -5540,7 +5585,7 @@
         <v>5</v>
       </c>
       <c r="F66" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G66" s="83"/>
       <c r="H66" s="91"/>
@@ -5675,7 +5720,7 @@
         <v>284</v>
       </c>
       <c r="F71" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" s="87">
         <v>46058</v>
@@ -5853,7 +5898,7 @@
         <v>284</v>
       </c>
       <c r="F77" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G77" s="87">
         <v>46044</v>
@@ -5938,7 +5983,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6062,11 +6107,13 @@
         <v>8</v>
       </c>
       <c r="F86" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
-      <c r="I86" s="93"/>
+      <c r="I86" s="93">
+        <v>1</v>
+      </c>
       <c r="J86" s="76"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -6283,7 +6330,7 @@
         <v>284</v>
       </c>
       <c r="F95" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" s="91">
         <v>46065</v>
@@ -6312,7 +6359,7 @@
         <v>19</v>
       </c>
       <c r="F96" s="30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G96" s="91"/>
       <c r="H96" s="91"/>
@@ -6326,11 +6373,21 @@
     </row>
     <row r="97" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="79"/>
-      <c r="B97" s="28"/>
-      <c r="C97" s="28"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="29"/>
-      <c r="F97" s="30"/>
+      <c r="B97" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E97" s="29">
+        <v>25</v>
+      </c>
+      <c r="F97" s="30">
+        <v>17</v>
+      </c>
       <c r="G97" s="87"/>
       <c r="H97" s="91"/>
       <c r="I97" s="90"/>
@@ -6343,23 +6400,27 @@
     </row>
     <row r="98" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="79"/>
-      <c r="B98" s="28" t="s">
+      <c r="B98" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="D98" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E98" s="29">
-        <v>25</v>
-      </c>
-      <c r="F98" s="30">
-        <v>16</v>
-      </c>
-      <c r="G98" s="87"/>
-      <c r="H98" s="91"/>
+      <c r="C98" s="106" t="s">
+        <v>154</v>
+      </c>
+      <c r="D98" s="106" t="s">
+        <v>153</v>
+      </c>
+      <c r="E98" s="107">
+        <v>10</v>
+      </c>
+      <c r="F98" s="108">
+        <v>3</v>
+      </c>
+      <c r="G98" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H98" s="91">
+        <v>45995</v>
+      </c>
       <c r="I98" s="90"/>
       <c r="J98" s="76"/>
       <c r="K98" s="1"/>
@@ -6374,22 +6435,22 @@
         <v>17</v>
       </c>
       <c r="C99" s="106" t="s">
-        <v>154</v>
+        <v>484</v>
       </c>
       <c r="D99" s="106" t="s">
-        <v>153</v>
-      </c>
-      <c r="E99" s="107">
-        <v>10</v>
+        <v>97</v>
+      </c>
+      <c r="E99" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F99" s="108">
         <v>3</v>
       </c>
-      <c r="G99" s="83" t="s">
-        <v>285</v>
+      <c r="G99" s="87">
+        <v>45995</v>
       </c>
       <c r="H99" s="91">
-        <v>45995</v>
+        <v>46086</v>
       </c>
       <c r="I99" s="90"/>
       <c r="J99" s="76"/>
@@ -6405,22 +6466,24 @@
         <v>17</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>97</v>
+        <v>537</v>
       </c>
       <c r="E100" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F100" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G100" s="87">
-        <v>45995</v>
+        <v>46086</v>
       </c>
       <c r="H100" s="91"/>
-      <c r="I100" s="90"/>
+      <c r="I100" s="90">
+        <v>1</v>
+      </c>
       <c r="J100" s="76"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -6474,7 +6537,7 @@
         <v>284</v>
       </c>
       <c r="F102" s="30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G102" s="87">
         <v>45918</v>
@@ -6503,7 +6566,7 @@
         <v>22</v>
       </c>
       <c r="F103" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G103" s="87"/>
       <c r="H103" s="91"/>
@@ -6617,7 +6680,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6741,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -7227,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G131" s="87"/>
       <c r="H131" s="91"/>
@@ -7310,7 +7373,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7492,13 +7555,15 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
       </c>
       <c r="H142" s="92"/>
-      <c r="I142" s="118"/>
+      <c r="I142" s="118">
+        <v>1</v>
+      </c>
       <c r="J142" s="76"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1"/>
@@ -7521,7 +7586,7 @@
         <v>3</v>
       </c>
       <c r="F143" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="83"/>
       <c r="H143" s="91"/>
@@ -7562,11 +7627,21 @@
     </row>
     <row r="145" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="79"/>
-      <c r="B145" s="28"/>
-      <c r="C145" s="28"/>
-      <c r="D145" s="28"/>
-      <c r="E145" s="29"/>
-      <c r="F145" s="30"/>
+      <c r="B145" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="D145" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E145" s="29">
+        <v>42</v>
+      </c>
+      <c r="F145" s="30">
+        <v>10</v>
+      </c>
       <c r="G145" s="87"/>
       <c r="H145" s="91"/>
       <c r="I145" s="90"/>
@@ -7583,16 +7658,16 @@
         <v>16</v>
       </c>
       <c r="C146" s="28" t="s">
-        <v>212</v>
+        <v>91</v>
       </c>
       <c r="D146" s="28" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E146" s="29">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F146" s="30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G146" s="87"/>
       <c r="H146" s="91"/>
@@ -7606,23 +7681,27 @@
     </row>
     <row r="147" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="79"/>
-      <c r="B147" s="28" t="s">
+      <c r="B147" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C147" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D147" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E147" s="29">
+      <c r="C147" s="106" t="s">
+        <v>101</v>
+      </c>
+      <c r="D147" s="106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="107">
         <v>1</v>
       </c>
-      <c r="F147" s="30">
-        <v>10</v>
-      </c>
-      <c r="G147" s="87"/>
-      <c r="H147" s="91"/>
+      <c r="F147" s="108">
+        <v>2</v>
+      </c>
+      <c r="G147" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H147" s="91">
+        <v>45974</v>
+      </c>
       <c r="I147" s="90"/>
       <c r="J147" s="96"/>
       <c r="K147" s="1"/>
@@ -7633,27 +7712,25 @@
     </row>
     <row r="148" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="79"/>
-      <c r="B148" s="106" t="s">
+      <c r="B148" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C148" s="106" t="s">
-        <v>101</v>
-      </c>
-      <c r="D148" s="106" t="s">
-        <v>69</v>
-      </c>
-      <c r="E148" s="107">
-        <v>1</v>
-      </c>
-      <c r="F148" s="108">
-        <v>2</v>
-      </c>
-      <c r="G148" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H148" s="91">
+      <c r="C148" s="28" t="s">
+        <v>476</v>
+      </c>
+      <c r="D148" s="28" t="s">
+        <v>454</v>
+      </c>
+      <c r="E148" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F148" s="30">
+        <v>6</v>
+      </c>
+      <c r="G148" s="87">
         <v>45974</v>
       </c>
+      <c r="H148" s="91"/>
       <c r="I148" s="90"/>
       <c r="J148" s="96"/>
       <c r="K148" s="1"/>
@@ -7664,25 +7741,27 @@
     </row>
     <row r="149" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="79"/>
-      <c r="B149" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" s="28" t="s">
-        <v>476</v>
-      </c>
-      <c r="D149" s="28" t="s">
-        <v>454</v>
-      </c>
-      <c r="E149" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F149" s="30">
-        <v>4</v>
-      </c>
-      <c r="G149" s="87">
-        <v>45974</v>
-      </c>
-      <c r="H149" s="91"/>
+      <c r="B149" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" s="106" t="s">
+        <v>150</v>
+      </c>
+      <c r="D149" s="106" t="s">
+        <v>68</v>
+      </c>
+      <c r="E149" s="107">
+        <v>1</v>
+      </c>
+      <c r="F149" s="108">
+        <v>5</v>
+      </c>
+      <c r="G149" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H149" s="91">
+        <v>46030</v>
+      </c>
       <c r="I149" s="90"/>
       <c r="J149" s="76"/>
       <c r="K149" s="1"/>
@@ -7693,28 +7772,28 @@
     </row>
     <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="79"/>
-      <c r="B150" s="106" t="s">
+      <c r="B150" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C150" s="106" t="s">
-        <v>150</v>
-      </c>
-      <c r="D150" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="E150" s="107">
+      <c r="C150" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="D150" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="E150" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F150" s="30">
+        <v>5</v>
+      </c>
+      <c r="G150" s="87">
+        <v>46030</v>
+      </c>
+      <c r="H150" s="91"/>
+      <c r="I150" s="90">
         <v>1</v>
       </c>
-      <c r="F150" s="108">
-        <v>5</v>
-      </c>
-      <c r="G150" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H150" s="91">
-        <v>46030</v>
-      </c>
-      <c r="I150" s="90"/>
       <c r="J150" s="76"/>
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
@@ -7724,25 +7803,27 @@
     </row>
     <row r="151" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="79"/>
-      <c r="B151" s="28" t="s">
+      <c r="B151" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C151" s="28" t="s">
-        <v>505</v>
-      </c>
-      <c r="D151" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E151" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F151" s="30">
-        <v>4</v>
-      </c>
-      <c r="G151" s="87">
-        <v>46030</v>
-      </c>
-      <c r="H151" s="91"/>
+      <c r="C151" s="106" t="s">
+        <v>213</v>
+      </c>
+      <c r="D151" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="E151" s="107">
+        <v>18</v>
+      </c>
+      <c r="F151" s="108">
+        <v>10</v>
+      </c>
+      <c r="G151" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H151" s="91">
+        <v>46072</v>
+      </c>
       <c r="I151" s="90"/>
       <c r="J151" s="76"/>
       <c r="K151" s="1"/>
@@ -7753,27 +7834,25 @@
     </row>
     <row r="152" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="79"/>
-      <c r="B152" s="106" t="s">
+      <c r="B152" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C152" s="106" t="s">
-        <v>213</v>
-      </c>
-      <c r="D152" s="106" t="s">
-        <v>83</v>
-      </c>
-      <c r="E152" s="107">
-        <v>18</v>
-      </c>
-      <c r="F152" s="108">
-        <v>10</v>
-      </c>
-      <c r="G152" s="83" t="s">
-        <v>285</v>
-      </c>
-      <c r="H152" s="91">
+      <c r="C152" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="D152" s="28" t="s">
+        <v>425</v>
+      </c>
+      <c r="E152" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F152" s="30">
+        <v>5</v>
+      </c>
+      <c r="G152" s="87">
         <v>46072</v>
       </c>
+      <c r="H152" s="91"/>
       <c r="I152" s="90"/>
       <c r="J152" s="76"/>
       <c r="K152" s="1"/>
@@ -7784,25 +7863,27 @@
     </row>
     <row r="153" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="79"/>
-      <c r="B153" s="28" t="s">
+      <c r="B153" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C153" s="28" t="s">
-        <v>533</v>
-      </c>
-      <c r="D153" s="28" t="s">
-        <v>425</v>
-      </c>
-      <c r="E153" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F153" s="30">
-        <v>2</v>
-      </c>
-      <c r="G153" s="87">
-        <v>46072</v>
-      </c>
-      <c r="H153" s="91"/>
+      <c r="C153" s="106" t="s">
+        <v>214</v>
+      </c>
+      <c r="D153" s="106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153" s="107">
+        <v>3</v>
+      </c>
+      <c r="F153" s="108">
+        <v>0</v>
+      </c>
+      <c r="G153" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H153" s="91">
+        <v>45911</v>
+      </c>
       <c r="I153" s="90"/>
       <c r="J153" s="96"/>
       <c r="K153" s="1"/>
@@ -7817,22 +7898,22 @@
         <v>17</v>
       </c>
       <c r="C154" s="106" t="s">
-        <v>214</v>
+        <v>478</v>
       </c>
       <c r="D154" s="106" t="s">
-        <v>19</v>
-      </c>
-      <c r="E154" s="107">
-        <v>3</v>
+        <v>138</v>
+      </c>
+      <c r="E154" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F154" s="108">
-        <v>0</v>
-      </c>
-      <c r="G154" s="87" t="s">
-        <v>285</v>
+        <v>2</v>
+      </c>
+      <c r="G154" s="87">
+        <v>45911</v>
       </c>
       <c r="H154" s="91">
-        <v>45911</v>
+        <v>45995</v>
       </c>
       <c r="I154" s="90"/>
       <c r="J154" s="96"/>
@@ -7848,22 +7929,22 @@
         <v>17</v>
       </c>
       <c r="C155" s="106" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D155" s="106" t="s">
-        <v>138</v>
+        <v>515</v>
       </c>
       <c r="E155" s="107" t="s">
         <v>284</v>
       </c>
       <c r="F155" s="108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G155" s="87">
-        <v>45911</v>
+        <v>45995</v>
       </c>
       <c r="H155" s="91">
-        <v>45995</v>
+        <v>46044</v>
       </c>
       <c r="I155" s="90"/>
       <c r="J155" s="76"/>
@@ -7875,27 +7956,25 @@
     </row>
     <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79"/>
-      <c r="B156" s="106" t="s">
+      <c r="B156" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C156" s="106" t="s">
-        <v>486</v>
-      </c>
-      <c r="D156" s="106" t="s">
-        <v>515</v>
-      </c>
-      <c r="E156" s="107" t="s">
+      <c r="C156" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="D156" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="E156" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F156" s="108">
-        <v>0</v>
+      <c r="F156" s="30">
+        <v>1</v>
       </c>
       <c r="G156" s="87">
-        <v>45995</v>
-      </c>
-      <c r="H156" s="91">
         <v>46044</v>
       </c>
+      <c r="H156" s="91"/>
       <c r="I156" s="90"/>
       <c r="J156" s="76"/>
       <c r="K156" s="1"/>
@@ -7910,20 +7989,18 @@
         <v>17</v>
       </c>
       <c r="C157" s="28" t="s">
-        <v>517</v>
+        <v>116</v>
       </c>
       <c r="D157" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="E157" s="29" t="s">
-        <v>284</v>
+        <v>19</v>
+      </c>
+      <c r="E157" s="29">
+        <v>25</v>
       </c>
       <c r="F157" s="30">
-        <v>1</v>
-      </c>
-      <c r="G157" s="87">
-        <v>46044</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G157" s="87"/>
       <c r="H157" s="91"/>
       <c r="I157" s="90"/>
       <c r="J157" s="76"/>
@@ -7935,23 +8012,27 @@
     </row>
     <row r="158" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="79"/>
-      <c r="B158" s="28" t="s">
+      <c r="B158" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C158" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D158" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E158" s="29">
-        <v>25</v>
-      </c>
-      <c r="F158" s="30">
-        <v>14</v>
-      </c>
-      <c r="G158" s="87"/>
-      <c r="H158" s="91"/>
+      <c r="C158" s="106" t="s">
+        <v>131</v>
+      </c>
+      <c r="D158" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="E158" s="107">
+        <v>4</v>
+      </c>
+      <c r="F158" s="108">
+        <v>11</v>
+      </c>
+      <c r="G158" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H158" s="91">
+        <v>46065</v>
+      </c>
       <c r="I158" s="90"/>
       <c r="J158" s="76"/>
       <c r="K158" s="1"/>
@@ -7966,22 +8047,22 @@
         <v>17</v>
       </c>
       <c r="C159" s="106" t="s">
-        <v>131</v>
+        <v>527</v>
       </c>
       <c r="D159" s="106" t="s">
-        <v>103</v>
-      </c>
-      <c r="E159" s="107">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="E159" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F159" s="108">
-        <v>11</v>
-      </c>
-      <c r="G159" s="87" t="s">
-        <v>285</v>
+        <v>1</v>
+      </c>
+      <c r="G159" s="87">
+        <v>46065</v>
       </c>
       <c r="H159" s="91">
-        <v>46065</v>
+        <v>46086</v>
       </c>
       <c r="I159" s="90"/>
       <c r="J159" s="76"/>
@@ -7997,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="C160" s="28" t="s">
-        <v>527</v>
+        <v>150</v>
       </c>
       <c r="D160" s="28" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E160" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F160" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" s="87">
-        <v>46065</v>
+        <v>46086</v>
       </c>
       <c r="H160" s="91"/>
       <c r="I160" s="92"/>
@@ -8031,7 +8112,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8184,7 +8265,7 @@
         <v>284</v>
       </c>
       <c r="F168" s="21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G168" s="86">
         <v>46318</v>
@@ -8257,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" s="87"/>
       <c r="H171" s="91"/>
@@ -8419,7 +8500,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G177" s="91"/>
       <c r="H177" s="91"/>
@@ -8537,7 +8618,7 @@
         <v>284</v>
       </c>
       <c r="F181" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G181" s="91">
         <v>46023</v>
@@ -8566,7 +8647,7 @@
         <v>7</v>
       </c>
       <c r="F182" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G182" s="87"/>
       <c r="H182" s="91"/>
@@ -8624,7 +8705,7 @@
         <v>284</v>
       </c>
       <c r="F184" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G184" s="87">
         <v>45953</v>
@@ -8715,7 +8796,7 @@
         <v>284</v>
       </c>
       <c r="F187" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G187" s="86">
         <v>45953</v>
@@ -8740,7 +8821,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -8864,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -8996,7 +9077,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9023,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="F201" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G201" s="83"/>
       <c r="H201" s="90"/>
@@ -9050,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="F202" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G202" s="83"/>
       <c r="H202" s="91"/>
@@ -9230,13 +9311,13 @@
         <v>275</v>
       </c>
       <c r="D210" s="28" t="s">
-        <v>276</v>
+        <v>544</v>
       </c>
       <c r="E210" s="29">
         <v>1</v>
       </c>
       <c r="F210" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G210" s="87"/>
       <c r="H210" s="90"/>
@@ -9327,7 +9408,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9509,7 +9590,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9640,7 +9721,7 @@
         <v>284</v>
       </c>
       <c r="F228" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G228" s="87">
         <v>45918</v>
@@ -9745,25 +9826,27 @@
     </row>
     <row r="232" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="79"/>
-      <c r="B232" s="28" t="s">
+      <c r="B232" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C232" s="28" t="s">
+      <c r="C232" s="106" t="s">
         <v>477</v>
       </c>
-      <c r="D232" s="28" t="s">
+      <c r="D232" s="106" t="s">
         <v>85</v>
       </c>
-      <c r="E232" s="29" t="s">
+      <c r="E232" s="107" t="s">
         <v>284</v>
       </c>
-      <c r="F232" s="30">
+      <c r="F232" s="108">
         <v>0</v>
       </c>
       <c r="G232" s="87">
         <v>45974</v>
       </c>
-      <c r="H232" s="91"/>
+      <c r="H232" s="91">
+        <v>46093</v>
+      </c>
       <c r="I232" s="89"/>
       <c r="J232" s="1"/>
       <c r="K232" s="1"/>
@@ -9775,21 +9858,23 @@
     <row r="233" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="79"/>
       <c r="B233" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C233" s="28" t="s">
-        <v>220</v>
+        <v>541</v>
       </c>
       <c r="D233" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E233" s="29">
-        <v>36</v>
+        <v>118</v>
+      </c>
+      <c r="E233" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F233" s="30">
-        <v>15</v>
-      </c>
-      <c r="G233" s="87"/>
+        <v>1</v>
+      </c>
+      <c r="G233" s="87">
+        <v>46093</v>
+      </c>
       <c r="H233" s="91"/>
       <c r="I233" s="89"/>
       <c r="J233" s="1"/>
@@ -9805,13 +9890,13 @@
         <v>17</v>
       </c>
       <c r="C234" s="28" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="D234" s="28" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="E234" s="29">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F234" s="30">
         <v>16</v>
@@ -9832,18 +9917,18 @@
         <v>17</v>
       </c>
       <c r="C235" s="28" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D235" s="28" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="E235" s="29">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F235" s="30">
-        <v>8</v>
-      </c>
-      <c r="G235" s="83"/>
+        <v>16</v>
+      </c>
+      <c r="G235" s="87"/>
       <c r="H235" s="91"/>
       <c r="I235" s="89"/>
       <c r="J235" s="76"/>
@@ -9855,27 +9940,23 @@
     </row>
     <row r="236" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="79"/>
-      <c r="B236" s="106" t="s">
+      <c r="B236" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C236" s="106" t="s">
-        <v>221</v>
-      </c>
-      <c r="D236" s="106" t="s">
-        <v>103</v>
-      </c>
-      <c r="E236" s="107">
-        <v>15</v>
-      </c>
-      <c r="F236" s="108">
-        <v>3</v>
-      </c>
-      <c r="G236" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H236" s="91">
-        <v>46016</v>
-      </c>
+      <c r="C236" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D236" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E236" s="29">
+        <v>8</v>
+      </c>
+      <c r="F236" s="30">
+        <v>8</v>
+      </c>
+      <c r="G236" s="83"/>
+      <c r="H236" s="91"/>
       <c r="I236" s="89"/>
       <c r="J236" s="76"/>
       <c r="K236" s="1"/>
@@ -9886,25 +9967,27 @@
     </row>
     <row r="237" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="79"/>
-      <c r="B237" s="28" t="s">
+      <c r="B237" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C237" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="D237" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E237" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F237" s="30">
-        <v>6</v>
-      </c>
-      <c r="G237" s="87">
+      <c r="C237" s="106" t="s">
+        <v>221</v>
+      </c>
+      <c r="D237" s="106" t="s">
+        <v>103</v>
+      </c>
+      <c r="E237" s="107">
+        <v>15</v>
+      </c>
+      <c r="F237" s="108">
+        <v>3</v>
+      </c>
+      <c r="G237" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H237" s="91">
         <v>46016</v>
       </c>
-      <c r="H237" s="91"/>
       <c r="I237" s="89"/>
       <c r="J237" s="76"/>
       <c r="K237" s="1"/>
@@ -9915,27 +9998,25 @@
     </row>
     <row r="238" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="79"/>
-      <c r="B238" s="106" t="s">
+      <c r="B238" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C238" s="106" t="s">
-        <v>266</v>
-      </c>
-      <c r="D238" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="E238" s="107">
-        <v>1</v>
-      </c>
-      <c r="F238" s="108">
-        <v>0</v>
-      </c>
-      <c r="G238" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H238" s="91">
-        <v>45911</v>
-      </c>
+      <c r="C238" s="28" t="s">
+        <v>496</v>
+      </c>
+      <c r="D238" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E238" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F238" s="30">
+        <v>8</v>
+      </c>
+      <c r="G238" s="87">
+        <v>46016</v>
+      </c>
+      <c r="H238" s="91"/>
       <c r="I238" s="89"/>
       <c r="J238" s="76"/>
       <c r="K238" s="1"/>
@@ -9946,25 +10027,27 @@
     </row>
     <row r="239" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="79"/>
-      <c r="B239" s="28" t="s">
+      <c r="B239" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C239" s="28" t="s">
-        <v>426</v>
-      </c>
-      <c r="D239" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E239" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F239" s="30">
-        <v>14</v>
-      </c>
-      <c r="G239" s="87">
+      <c r="C239" s="106" t="s">
+        <v>266</v>
+      </c>
+      <c r="D239" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="E239" s="107">
+        <v>1</v>
+      </c>
+      <c r="F239" s="108">
+        <v>0</v>
+      </c>
+      <c r="G239" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H239" s="91">
         <v>45911</v>
       </c>
-      <c r="H239" s="91"/>
       <c r="I239" s="89"/>
       <c r="J239" s="76"/>
       <c r="K239" s="1"/>
@@ -9975,12 +10058,24 @@
     </row>
     <row r="240" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="79"/>
-      <c r="B240" s="28"/>
-      <c r="C240" s="28"/>
-      <c r="D240" s="28"/>
-      <c r="E240" s="29"/>
-      <c r="F240" s="30"/>
-      <c r="G240" s="87"/>
+      <c r="B240" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C240" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="D240" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E240" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F240" s="30">
+        <v>15</v>
+      </c>
+      <c r="G240" s="87">
+        <v>45911</v>
+      </c>
       <c r="H240" s="91"/>
       <c r="I240" s="89"/>
       <c r="J240" s="76"/>
@@ -10018,7 +10113,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10192,15 +10287,13 @@
         <v>284</v>
       </c>
       <c r="F250" s="21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G250" s="86">
         <v>46037</v>
       </c>
       <c r="H250" s="92"/>
-      <c r="I250" s="92">
-        <v>1</v>
-      </c>
+      <c r="I250" s="92"/>
       <c r="J250" s="1"/>
       <c r="K250" s="1"/>
       <c r="L250" s="1"/>
@@ -10294,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="F254" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G254" s="83"/>
       <c r="H254" s="91"/>
@@ -10383,13 +10476,15 @@
         <v>284</v>
       </c>
       <c r="F257" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G257" s="87">
         <v>46030</v>
       </c>
       <c r="H257" s="91"/>
-      <c r="I257" s="90"/>
+      <c r="I257" s="90">
+        <v>1</v>
+      </c>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
       <c r="L257" s="1"/>
@@ -10483,7 +10578,7 @@
         <v>18</v>
       </c>
       <c r="F261" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G261" s="87"/>
       <c r="H261" s="91"/>
@@ -10541,7 +10636,7 @@
         <v>284</v>
       </c>
       <c r="F263" s="30">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G263" s="87">
         <v>45946</v>
@@ -10601,7 +10696,7 @@
         <v>284</v>
       </c>
       <c r="F265" s="30">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G265" s="87">
         <v>45953</v>
@@ -10719,7 +10814,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -10872,7 +10967,7 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
@@ -11164,7 +11259,7 @@
         <v>1</v>
       </c>
       <c r="F288" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G288" s="87"/>
       <c r="H288" s="91"/>
@@ -11222,7 +11317,7 @@
         <v>284</v>
       </c>
       <c r="F290" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G290" s="87">
         <v>45946</v>
@@ -11352,7 +11447,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11534,7 +11629,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -11604,13 +11699,27 @@
     </row>
     <row r="307" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="79"/>
-      <c r="B307" s="28"/>
-      <c r="C307" s="28"/>
-      <c r="D307" s="28"/>
-      <c r="E307" s="29"/>
-      <c r="F307" s="30"/>
-      <c r="G307" s="87"/>
-      <c r="H307" s="91"/>
+      <c r="B307" s="106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C307" s="106" t="s">
+        <v>174</v>
+      </c>
+      <c r="D307" s="106" t="s">
+        <v>121</v>
+      </c>
+      <c r="E307" s="107">
+        <v>4</v>
+      </c>
+      <c r="F307" s="108">
+        <v>4</v>
+      </c>
+      <c r="G307" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H307" s="91">
+        <v>46002</v>
+      </c>
       <c r="I307" s="90"/>
       <c r="J307" s="1"/>
       <c r="K307" s="1"/>
@@ -11621,27 +11730,25 @@
     </row>
     <row r="308" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="79"/>
-      <c r="B308" s="106" t="s">
+      <c r="B308" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C308" s="106" t="s">
-        <v>174</v>
-      </c>
-      <c r="D308" s="106" t="s">
-        <v>121</v>
-      </c>
-      <c r="E308" s="107">
+      <c r="C308" s="28" t="s">
+        <v>491</v>
+      </c>
+      <c r="D308" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E308" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F308" s="30">
         <v>4</v>
       </c>
-      <c r="F308" s="108">
-        <v>4</v>
-      </c>
-      <c r="G308" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H308" s="91">
+      <c r="G308" s="87">
         <v>46002</v>
       </c>
+      <c r="H308" s="91"/>
       <c r="I308" s="90"/>
       <c r="J308" s="1"/>
       <c r="K308" s="1"/>
@@ -11652,25 +11759,27 @@
     </row>
     <row r="309" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="79"/>
-      <c r="B309" s="28" t="s">
+      <c r="B309" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C309" s="28" t="s">
-        <v>491</v>
-      </c>
-      <c r="D309" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E309" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F309" s="30">
-        <v>4</v>
-      </c>
-      <c r="G309" s="87">
-        <v>46002</v>
-      </c>
-      <c r="H309" s="91"/>
+      <c r="C309" s="106" t="s">
+        <v>163</v>
+      </c>
+      <c r="D309" s="106" t="s">
+        <v>68</v>
+      </c>
+      <c r="E309" s="107">
+        <v>1</v>
+      </c>
+      <c r="F309" s="108">
+        <v>1</v>
+      </c>
+      <c r="G309" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H309" s="91">
+        <v>45911</v>
+      </c>
       <c r="I309" s="90"/>
       <c r="J309" s="1"/>
       <c r="K309" s="1"/>
@@ -11681,27 +11790,25 @@
     </row>
     <row r="310" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="79"/>
-      <c r="B310" s="106" t="s">
+      <c r="B310" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C310" s="106" t="s">
-        <v>163</v>
-      </c>
-      <c r="D310" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="E310" s="107">
-        <v>1</v>
-      </c>
-      <c r="F310" s="108">
-        <v>1</v>
-      </c>
-      <c r="G310" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H310" s="91">
+      <c r="C310" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D310" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E310" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F310" s="30">
+        <v>10</v>
+      </c>
+      <c r="G310" s="87">
         <v>45911</v>
       </c>
+      <c r="H310" s="91"/>
       <c r="I310" s="90"/>
       <c r="J310" s="1"/>
       <c r="K310" s="1"/>
@@ -11712,25 +11819,27 @@
     </row>
     <row r="311" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="79"/>
-      <c r="B311" s="28" t="s">
+      <c r="B311" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C311" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D311" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E311" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F311" s="30">
-        <v>10</v>
-      </c>
-      <c r="G311" s="87">
-        <v>45911</v>
-      </c>
-      <c r="H311" s="91"/>
+      <c r="C311" s="106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D311" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="E311" s="107">
+        <v>9</v>
+      </c>
+      <c r="F311" s="108">
+        <v>0</v>
+      </c>
+      <c r="G311" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H311" s="91">
+        <v>45961</v>
+      </c>
       <c r="I311" s="90"/>
       <c r="J311" s="1"/>
       <c r="K311" s="1"/>
@@ -11741,27 +11850,25 @@
     </row>
     <row r="312" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="79"/>
-      <c r="B312" s="106" t="s">
+      <c r="B312" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C312" s="106" t="s">
-        <v>102</v>
-      </c>
-      <c r="D312" s="106" t="s">
-        <v>132</v>
-      </c>
-      <c r="E312" s="107">
-        <v>9</v>
-      </c>
-      <c r="F312" s="108">
-        <v>0</v>
-      </c>
-      <c r="G312" s="83" t="s">
-        <v>285</v>
-      </c>
-      <c r="H312" s="91">
+      <c r="C312" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="D312" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E312" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F312" s="30">
+        <v>4</v>
+      </c>
+      <c r="G312" s="87">
         <v>45961</v>
       </c>
+      <c r="H312" s="91"/>
       <c r="I312" s="90"/>
       <c r="J312" s="1"/>
       <c r="K312" s="1"/>
@@ -11773,23 +11880,21 @@
     <row r="313" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="79"/>
       <c r="B313" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C313" s="28" t="s">
-        <v>516</v>
+        <v>71</v>
       </c>
       <c r="D313" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="E313" s="29" t="s">
-        <v>284</v>
+        <v>22</v>
+      </c>
+      <c r="E313" s="29">
+        <v>54</v>
       </c>
       <c r="F313" s="30">
-        <v>4</v>
-      </c>
-      <c r="G313" s="87">
-        <v>45961</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G313" s="87"/>
       <c r="H313" s="91"/>
       <c r="I313" s="90"/>
       <c r="J313" s="1"/>
@@ -11801,23 +11906,27 @@
     </row>
     <row r="314" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="79"/>
-      <c r="B314" s="28" t="s">
+      <c r="B314" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C314" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D314" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E314" s="29">
-        <v>54</v>
-      </c>
-      <c r="F314" s="30">
-        <v>29</v>
-      </c>
-      <c r="G314" s="87"/>
-      <c r="H314" s="91"/>
+      <c r="C314" s="106" t="s">
+        <v>236</v>
+      </c>
+      <c r="D314" s="106" t="s">
+        <v>122</v>
+      </c>
+      <c r="E314" s="107">
+        <v>8</v>
+      </c>
+      <c r="F314" s="108">
+        <v>1</v>
+      </c>
+      <c r="G314" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H314" s="91">
+        <v>45939</v>
+      </c>
       <c r="I314" s="90"/>
       <c r="J314" s="1"/>
       <c r="K314" s="1"/>
@@ -11828,27 +11937,25 @@
     </row>
     <row r="315" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="79"/>
-      <c r="B315" s="106" t="s">
+      <c r="B315" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C315" s="106" t="s">
-        <v>236</v>
-      </c>
-      <c r="D315" s="106" t="s">
-        <v>122</v>
-      </c>
-      <c r="E315" s="107">
-        <v>8</v>
-      </c>
-      <c r="F315" s="108">
-        <v>1</v>
-      </c>
-      <c r="G315" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H315" s="91">
+      <c r="C315" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="D315" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E315" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F315" s="30">
+        <v>4</v>
+      </c>
+      <c r="G315" s="87">
         <v>45939</v>
       </c>
+      <c r="H315" s="91"/>
       <c r="I315" s="90"/>
       <c r="J315" s="1"/>
       <c r="K315" s="1"/>
@@ -11859,25 +11966,27 @@
     </row>
     <row r="316" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="79"/>
-      <c r="B316" s="28" t="s">
+      <c r="B316" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C316" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="D316" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E316" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F316" s="30">
-        <v>3</v>
-      </c>
-      <c r="G316" s="87">
-        <v>45939</v>
-      </c>
-      <c r="H316" s="91"/>
+      <c r="C316" s="106" t="s">
+        <v>237</v>
+      </c>
+      <c r="D316" s="106" t="s">
+        <v>120</v>
+      </c>
+      <c r="E316" s="107">
+        <v>1</v>
+      </c>
+      <c r="F316" s="108">
+        <v>13</v>
+      </c>
+      <c r="G316" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H316" s="91">
+        <v>46093</v>
+      </c>
       <c r="I316" s="90"/>
       <c r="J316" s="1"/>
       <c r="K316" s="1"/>
@@ -11892,18 +12001,20 @@
         <v>17</v>
       </c>
       <c r="C317" s="28" t="s">
-        <v>237</v>
+        <v>542</v>
       </c>
       <c r="D317" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E317" s="29">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="E317" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F317" s="30">
-        <v>13</v>
-      </c>
-      <c r="G317" s="87"/>
+        <v>0</v>
+      </c>
+      <c r="G317" s="87">
+        <v>46093</v>
+      </c>
       <c r="H317" s="91"/>
       <c r="I317" s="90"/>
       <c r="J317" s="1"/>
@@ -12050,7 +12161,7 @@
         <v>284</v>
       </c>
       <c r="F322" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G322" s="87">
         <v>45890</v>
@@ -12199,7 +12310,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -12709,7 +12820,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -12791,7 +12902,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -12863,34 +12974,48 @@
       <c r="J360" s="1"/>
     </row>
     <row r="361" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B361" s="28"/>
-      <c r="C361" s="28"/>
-      <c r="D361" s="28"/>
-      <c r="E361" s="29"/>
-      <c r="F361" s="30"/>
+      <c r="B361" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C361" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="D361" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E361" s="29">
+        <v>32</v>
+      </c>
+      <c r="F361" s="30">
+        <v>9</v>
+      </c>
       <c r="G361" s="1"/>
       <c r="H361" s="1"/>
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
     </row>
     <row r="362" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B362" s="28" t="s">
+      <c r="B362" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C362" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="D362" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E362" s="29">
-        <v>32</v>
-      </c>
-      <c r="F362" s="30">
-        <v>8</v>
-      </c>
-      <c r="G362" s="1"/>
-      <c r="H362" s="1"/>
+      <c r="C362" s="106" t="s">
+        <v>248</v>
+      </c>
+      <c r="D362" s="106" t="s">
+        <v>56</v>
+      </c>
+      <c r="E362" s="107">
+        <v>4</v>
+      </c>
+      <c r="F362" s="108">
+        <v>1</v>
+      </c>
+      <c r="G362" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H362" s="103">
+        <v>45988</v>
+      </c>
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
     </row>
@@ -12899,22 +13024,22 @@
         <v>16</v>
       </c>
       <c r="C363" s="106" t="s">
-        <v>248</v>
+        <v>483</v>
       </c>
       <c r="D363" s="106" t="s">
-        <v>56</v>
-      </c>
-      <c r="E363" s="107">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="E363" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F363" s="108">
-        <v>1</v>
-      </c>
-      <c r="G363" s="1" t="s">
-        <v>285</v>
+        <v>3</v>
+      </c>
+      <c r="G363" s="103">
+        <v>45988</v>
       </c>
       <c r="H363" s="103">
-        <v>45988</v>
+        <v>46086</v>
       </c>
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
@@ -12924,19 +13049,19 @@
         <v>16</v>
       </c>
       <c r="C364" s="28" t="s">
-        <v>483</v>
+        <v>538</v>
       </c>
       <c r="D364" s="28" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E364" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F364" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G364" s="103">
-        <v>45988</v>
+        <v>46086</v>
       </c>
       <c r="H364" s="103"/>
       <c r="I364" s="1"/>
@@ -12991,13 +13116,27 @@
       <c r="J366" s="1"/>
     </row>
     <row r="367" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B367" s="28"/>
-      <c r="C367" s="28"/>
-      <c r="D367" s="28"/>
-      <c r="E367" s="29"/>
-      <c r="F367" s="30"/>
-      <c r="G367" s="1"/>
-      <c r="H367" s="103"/>
+      <c r="B367" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C367" s="106" t="s">
+        <v>92</v>
+      </c>
+      <c r="D367" s="106" t="s">
+        <v>114</v>
+      </c>
+      <c r="E367" s="107">
+        <v>27</v>
+      </c>
+      <c r="F367" s="108">
+        <v>5</v>
+      </c>
+      <c r="G367" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H367" s="103">
+        <v>46086</v>
+      </c>
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
     </row>
@@ -13006,18 +13145,20 @@
         <v>17</v>
       </c>
       <c r="C368" s="28" t="s">
-        <v>92</v>
+        <v>540</v>
       </c>
       <c r="D368" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E368" s="29">
-        <v>27</v>
+        <v>83</v>
+      </c>
+      <c r="E368" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F368" s="30">
-        <v>5</v>
-      </c>
-      <c r="G368" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="G368" s="103">
+        <v>46086</v>
+      </c>
       <c r="H368" s="103"/>
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
@@ -13090,50 +13231,50 @@
       <c r="J371" s="1"/>
     </row>
     <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B372" s="28" t="s">
+      <c r="B372" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C372" s="28" t="s">
+      <c r="C372" s="106" t="s">
         <v>495</v>
       </c>
-      <c r="D372" s="28" t="s">
+      <c r="D372" s="106" t="s">
         <v>288</v>
       </c>
-      <c r="E372" s="29" t="s">
+      <c r="E372" s="107" t="s">
         <v>284</v>
       </c>
-      <c r="F372" s="30">
+      <c r="F372" s="108">
         <v>0</v>
       </c>
       <c r="G372" s="103">
         <v>46009</v>
       </c>
-      <c r="H372" s="103"/>
+      <c r="H372" s="103">
+        <v>46086</v>
+      </c>
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
     <row r="373" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B373" s="106" t="s">
+      <c r="B373" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C373" s="106" t="s">
-        <v>145</v>
-      </c>
-      <c r="D373" s="106" t="s">
-        <v>83</v>
-      </c>
-      <c r="E373" s="107">
+      <c r="C373" s="28" t="s">
+        <v>539</v>
+      </c>
+      <c r="D373" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="E373" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F373" s="30">
         <v>1</v>
       </c>
-      <c r="F373" s="108">
-        <v>0</v>
-      </c>
-      <c r="G373" s="103" t="s">
-        <v>285</v>
-      </c>
-      <c r="H373" s="103">
-        <v>45890</v>
-      </c>
+      <c r="G373" s="103">
+        <v>46086</v>
+      </c>
+      <c r="H373" s="103"/>
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
@@ -13142,56 +13283,70 @@
         <v>17</v>
       </c>
       <c r="C374" s="106" t="s">
-        <v>401</v>
+        <v>145</v>
       </c>
       <c r="D374" s="106" t="s">
-        <v>158</v>
-      </c>
-      <c r="E374" s="107" t="s">
-        <v>284</v>
+        <v>83</v>
+      </c>
+      <c r="E374" s="107">
+        <v>1</v>
       </c>
       <c r="F374" s="108">
         <v>0</v>
       </c>
-      <c r="G374" s="103">
+      <c r="G374" s="103" t="s">
+        <v>285</v>
+      </c>
+      <c r="H374" s="103">
         <v>45890</v>
-      </c>
-      <c r="H374" s="103">
-        <v>45939</v>
       </c>
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
     </row>
     <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B375" s="28" t="s">
+      <c r="B375" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C375" s="28" t="s">
-        <v>457</v>
-      </c>
-      <c r="D375" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="E375" s="29" t="s">
+      <c r="C375" s="106" t="s">
+        <v>401</v>
+      </c>
+      <c r="D375" s="106" t="s">
+        <v>158</v>
+      </c>
+      <c r="E375" s="107" t="s">
         <v>284</v>
       </c>
-      <c r="F375" s="30">
-        <v>5</v>
+      <c r="F375" s="108">
+        <v>0</v>
       </c>
       <c r="G375" s="103">
+        <v>45890</v>
+      </c>
+      <c r="H375" s="103">
         <v>45939</v>
       </c>
-      <c r="H375" s="1"/>
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
     </row>
     <row r="376" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B376" s="28"/>
-      <c r="C376" s="28"/>
-      <c r="D376" s="28"/>
-      <c r="E376" s="29"/>
-      <c r="F376" s="30"/>
-      <c r="G376" s="103"/>
+      <c r="B376" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C376" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="D376" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E376" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F376" s="30">
+        <v>6</v>
+      </c>
+      <c r="G376" s="103">
+        <v>45939</v>
+      </c>
       <c r="H376" s="1"/>
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
@@ -13206,7 +13361,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -13575,19 +13730,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>203</v>
+        <v>31</v>
       </c>
       <c r="E7" s="25">
         <v>37</v>
       </c>
       <c r="F7" s="26">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G7" s="27">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13600,19 +13755,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>233</v>
+        <v>27</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="25">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" s="26">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G8" s="27">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13625,19 +13780,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>198</v>
+        <v>98</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>233</v>
       </c>
       <c r="E9" s="25">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" s="26">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="G9" s="27">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13650,19 +13805,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="25">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F10" s="26">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="27">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13675,19 +13830,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>31</v>
+        <v>51</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>203</v>
       </c>
       <c r="E11" s="25">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" s="26">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="27">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13700,19 +13855,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>188</v>
       </c>
       <c r="E12" s="25">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F12" s="26">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G12" s="27">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13727,17 +13882,17 @@
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="55" t="s">
         <v>267</v>
       </c>
       <c r="E13" s="25">
-        <v>24</v>
-      </c>
-      <c r="F13" s="26">
-        <v>79</v>
-      </c>
-      <c r="G13" s="27">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="F13" s="56">
+        <v>85</v>
+      </c>
+      <c r="G13" s="57">
+        <v>59</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -13750,19 +13905,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="55" t="s">
-        <v>188</v>
+        <v>2</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>1</v>
       </c>
       <c r="E14" s="25">
-        <v>21</v>
-      </c>
-      <c r="F14" s="56">
-        <v>68</v>
-      </c>
-      <c r="G14" s="57">
-        <v>47</v>
+        <v>25</v>
+      </c>
+      <c r="F14" s="26">
+        <v>60</v>
+      </c>
+      <c r="G14" s="27">
+        <v>35</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -13775,19 +13930,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>244</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E15" s="25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="56">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G15" s="57">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -13800,19 +13955,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>244</v>
+        <v>55</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E16" s="25">
         <v>14</v>
       </c>
       <c r="F16" s="26">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G16" s="27">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -13825,19 +13980,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>140</v>
+        <v>35</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>34</v>
       </c>
       <c r="E17" s="25">
         <v>10</v>
       </c>
       <c r="F17" s="26">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G17" s="27">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -13850,19 +14005,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c r="E18" s="25">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F18" s="26">
         <v>63</v>
       </c>
       <c r="G18" s="27">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -13875,19 +14030,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>34</v>
+        <v>52</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="E19" s="25">
-        <v>4</v>
-      </c>
-      <c r="F19" s="26">
-        <v>49</v>
-      </c>
-      <c r="G19" s="27">
-        <v>45</v>
+        <v>6</v>
+      </c>
+      <c r="F19" s="56">
+        <v>53</v>
+      </c>
+      <c r="G19" s="57">
+        <v>47</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -13900,19 +14055,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="25">
+        <v>6</v>
+      </c>
+      <c r="F20" s="26">
         <v>52</v>
       </c>
-      <c r="D20" s="55" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="25">
-        <v>3</v>
-      </c>
-      <c r="F20" s="56">
-        <v>48</v>
-      </c>
-      <c r="G20" s="57">
-        <v>45</v>
+      <c r="G20" s="27">
+        <v>46</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>
@@ -13965,7 +14120,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:IW31"/>
+  <dimension ref="A1:IW34"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="33.296875" style="38" customWidth="1"/>
@@ -14245,7 +14400,7 @@
       <c r="B15" s="65" t="s">
         <v>233</v>
       </c>
-      <c r="C15" s="68">
+      <c r="C15" s="64">
         <v>1</v>
       </c>
       <c r="D15" s="64" t="s">
@@ -14254,7 +14409,7 @@
       <c r="E15" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="68">
+      <c r="F15" s="64">
         <v>1</v>
       </c>
       <c r="G15" s="64" t="s">
@@ -14268,7 +14423,7 @@
       <c r="B16" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="68">
+      <c r="C16" s="64">
         <v>2</v>
       </c>
       <c r="D16" s="64" t="s">
@@ -14277,21 +14432,21 @@
       <c r="E16" s="70" t="s">
         <v>528</v>
       </c>
-      <c r="F16" s="69">
+      <c r="F16" s="100">
         <v>1</v>
       </c>
       <c r="G16" s="100" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="70" t="s">
         <v>243</v>
       </c>
-      <c r="C17" s="69">
+      <c r="C17" s="100">
         <v>2</v>
       </c>
       <c r="D17" s="100" t="s">
@@ -14300,21 +14455,21 @@
       <c r="E17" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="68">
+      <c r="F17" s="64">
         <v>3</v>
       </c>
       <c r="G17" s="64" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="67" t="s">
         <v>76</v>
       </c>
       <c r="B18" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="68">
+      <c r="C18" s="64">
         <v>0</v>
       </c>
       <c r="D18" s="64" t="s">
@@ -14323,14 +14478,14 @@
       <c r="E18" s="70" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="69">
+      <c r="F18" s="100">
         <v>-1</v>
       </c>
       <c r="G18" s="100" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
       <c r="C19" s="64"/>
       <c r="D19" s="64"/>
@@ -14338,7 +14493,7 @@
       <c r="F19" s="66"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
         <v>535</v>
@@ -14349,7 +14504,7 @@
       <c r="F20" s="68"/>
       <c r="G20" s="64"/>
     </row>
-    <row r="21" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
         <v>77</v>
       </c>
@@ -14362,17 +14517,17 @@
       <c r="D21" s="64" t="s">
         <v>436</v>
       </c>
-      <c r="E21" s="68" t="s">
+      <c r="E21" s="69" t="s">
         <v>233</v>
       </c>
-      <c r="F21" s="64">
-        <v>0</v>
-      </c>
-      <c r="G21" s="64" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F21" s="100">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="100" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="65"/>
       <c r="C22" s="64"/>
       <c r="D22" s="61"/>
@@ -14380,7 +14535,7 @@
       <c r="F22" s="66"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="63" t="s">
         <v>39</v>
       </c>
@@ -14390,83 +14545,144 @@
       <c r="F23" s="66"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="70"/>
-      <c r="C24" s="69"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="64"/>
-    </row>
-    <row r="25" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="C24" s="64">
+        <v>2</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>431</v>
+      </c>
+      <c r="E24" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="100">
+        <v>0</v>
+      </c>
+      <c r="G24" s="100" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="100"/>
-    </row>
-    <row r="26" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="64">
+        <v>0</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>436</v>
+      </c>
+      <c r="E25" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="64">
+        <v>0</v>
+      </c>
+      <c r="G25" s="64" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="67"/>
       <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
+      <c r="C26" s="68"/>
       <c r="D26" s="64"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-    </row>
-    <row r="27" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E26" s="70"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="100"/>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="65"/>
+        <v>543</v>
+      </c>
+      <c r="C27" s="68"/>
       <c r="D27" s="64"/>
       <c r="E27" s="65"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-    </row>
-    <row r="28" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F27" s="68"/>
+      <c r="G27" s="64"/>
+    </row>
+    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
         <v>255</v>
       </c>
-      <c r="B28" s="65"/>
-      <c r="C28" s="68"/>
+      <c r="B28" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="64"/>
       <c r="D28" s="64"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="69"/>
+      <c r="E28" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="100"/>
       <c r="G28" s="100"/>
     </row>
-    <row r="29" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
+    <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
       <c r="D29" s="64"/>
-      <c r="E29" s="40"/>
+      <c r="E29" s="65"/>
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
+        <v>40</v>
+      </c>
+      <c r="C30" s="65"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="65"/>
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
-      <c r="K30" s="98"/>
-    </row>
-    <row r="31" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="65"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="67" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="68"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="100"/>
+    </row>
+    <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+    </row>
+    <row r="33" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="K33" s="98"/>
+    </row>
+    <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="65"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16578,7 +16794,7 @@
       </c>
       <c r="G6">
         <f>COUNTIF(Stats!D:D,'Player Count'!F6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="67" t="s">
         <v>362</v>
@@ -16617,7 +16833,7 @@
       </c>
       <c r="K7">
         <f>COUNTIF(Stats!D:D,'Player Count'!J7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="109"/>
       <c r="N7" t="s">
@@ -16657,7 +16873,7 @@
       </c>
       <c r="O8">
         <f>COUNTIF(Stats!D:D,'Player Count'!N8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="109"/>
     </row>
@@ -16795,7 +17011,7 @@
       </c>
       <c r="C13">
         <f>COUNTIF(Stats!D:D,'Player Count'!B13)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>326</v>
@@ -16923,7 +17139,7 @@
       </c>
       <c r="C17">
         <f>COUNTIF(Stats!D:D,'Player Count'!B17)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>330</v>
@@ -16937,7 +17153,7 @@
       </c>
       <c r="K17">
         <f>COUNTIF(Stats!D:D,'Player Count'!J17)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" s="109"/>
       <c r="N17" s="67" t="s">
@@ -17009,7 +17225,7 @@
       </c>
       <c r="O19">
         <f>COUNTIF(Stats!D:D,'Player Count'!N19)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="109"/>
     </row>
@@ -17211,7 +17427,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F26" t="s">
         <v>339</v>
@@ -17250,7 +17466,7 @@
       </c>
       <c r="K27">
         <f>COUNTIF(Stats!D:D,'Player Count'!J27)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M27" s="109"/>
       <c r="N27" s="67" t="s">
@@ -17300,7 +17516,7 @@
       </c>
       <c r="K29">
         <f>COUNTIF(Stats!D:D,'Player Count'!J29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29" t="s">
         <v>390</v>
@@ -17316,14 +17532,14 @@
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>317</v>
@@ -17339,28 +17555,28 @@
       </c>
       <c r="C38" s="114">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.36752136752136755</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="D38" s="114"/>
       <c r="E38" s="114"/>
       <c r="F38" s="114"/>
       <c r="G38" s="114">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.27350427350427353</v>
+        <v>0.26859504132231404</v>
       </c>
       <c r="H38" s="114"/>
       <c r="I38" s="114"/>
       <c r="J38" s="114"/>
       <c r="K38" s="114">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.20085470085470086</v>
+        <v>0.21487603305785125</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114"/>
       <c r="N38" s="114"/>
       <c r="O38" s="114">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.15811965811965811</v>
+        <v>0.15289256198347106</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1473" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC201A0E-6B28-4587-A2BF-F0DB5A37943A}"/>
+  <xr:revisionPtr revIDLastSave="1530" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF8C3D2-E378-44AA-AD57-EAEAB798CB95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="547">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1674,6 +1674,12 @@
   </si>
   <si>
     <t>BARROW</t>
+  </si>
+  <si>
+    <t>JOE TAYLOR</t>
+  </si>
+  <si>
+    <t>ANDY COOK</t>
   </si>
 </sst>
 </file>
@@ -3744,11 +3750,11 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
@@ -3777,9 +3783,7 @@
         <v>46093</v>
       </c>
       <c r="H6" s="84"/>
-      <c r="I6" s="81">
-        <v>1</v>
-      </c>
+      <c r="I6" s="81"/>
       <c r="J6" s="79"/>
       <c r="K6" s="23" t="str">
         <f>D29</f>
@@ -3791,15 +3795,15 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3826,11 +3830,11 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
@@ -3870,7 +3874,7 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
@@ -3920,7 +3924,7 @@
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3958,15 +3962,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -3989,13 +3993,15 @@
         <v>284</v>
       </c>
       <c r="F11" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="87">
         <v>46009</v>
       </c>
       <c r="H11" s="84"/>
-      <c r="I11" s="99"/>
+      <c r="I11" s="99">
+        <v>1</v>
+      </c>
       <c r="J11" s="82"/>
       <c r="K11" s="23" t="str">
         <f>D164</f>
@@ -4007,11 +4013,11 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
@@ -4056,11 +4062,11 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
@@ -4088,9 +4094,7 @@
         <v>45932</v>
       </c>
       <c r="H13" s="84"/>
-      <c r="I13" s="99">
-        <v>1</v>
-      </c>
+      <c r="I13" s="99"/>
       <c r="J13" s="82"/>
       <c r="K13" s="71" t="str">
         <f>D218</f>
@@ -4102,15 +4106,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4149,11 +4153,11 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
@@ -4198,11 +4202,11 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
@@ -4242,11 +4246,11 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
@@ -4284,11 +4288,11 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
@@ -4335,15 +4339,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4587,7 +4591,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4745,7 +4749,7 @@
         <v>284</v>
       </c>
       <c r="F33" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" s="86">
         <v>46072</v>
@@ -4832,13 +4836,23 @@
     </row>
     <row r="37" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="79"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="86"/>
-      <c r="H37" s="94"/>
+      <c r="B37" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="29">
+        <v>32</v>
+      </c>
+      <c r="F37" s="30">
+        <v>10</v>
+      </c>
+      <c r="G37" s="83"/>
+      <c r="H37" s="91"/>
       <c r="I37" s="93"/>
       <c r="J37" s="76"/>
       <c r="K37" s="1"/>
@@ -4853,18 +4867,18 @@
         <v>16</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="E38" s="29">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F38" s="30">
         <v>10</v>
       </c>
-      <c r="G38" s="83"/>
+      <c r="G38" s="87"/>
       <c r="H38" s="91"/>
       <c r="I38" s="93"/>
       <c r="J38" s="76"/>
@@ -4885,16 +4899,16 @@
         <v>16</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>72</v>
+        <v>190</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E39" s="29">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F39" s="30">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -4908,23 +4922,27 @@
     </row>
     <row r="40" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="79"/>
-      <c r="B40" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="29">
-        <v>1</v>
-      </c>
-      <c r="F40" s="30">
-        <v>15</v>
-      </c>
-      <c r="G40" s="87"/>
-      <c r="H40" s="91"/>
+      <c r="B40" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="106" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="106" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="107">
+        <v>2</v>
+      </c>
+      <c r="F40" s="108">
+        <v>0</v>
+      </c>
+      <c r="G40" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H40" s="91">
+        <v>45876</v>
+      </c>
       <c r="I40" s="89"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -4939,22 +4957,22 @@
         <v>17</v>
       </c>
       <c r="C41" s="106" t="s">
-        <v>61</v>
+        <v>286</v>
       </c>
       <c r="D41" s="106" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="107">
-        <v>2</v>
+        <v>70</v>
+      </c>
+      <c r="E41" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F41" s="108">
-        <v>0</v>
-      </c>
-      <c r="G41" s="87" t="s">
-        <v>285</v>
+        <v>5</v>
+      </c>
+      <c r="G41" s="87">
+        <v>45876</v>
       </c>
       <c r="H41" s="91">
-        <v>45876</v>
+        <v>46051</v>
       </c>
       <c r="I41" s="89"/>
       <c r="J41" s="76"/>
@@ -4970,22 +4988,22 @@
         <v>17</v>
       </c>
       <c r="C42" s="106" t="s">
-        <v>286</v>
+        <v>520</v>
       </c>
       <c r="D42" s="106" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="E42" s="107" t="s">
         <v>284</v>
       </c>
       <c r="F42" s="108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G42" s="87">
-        <v>45876</v>
+        <v>46051</v>
       </c>
       <c r="H42" s="91">
-        <v>46051</v>
+        <v>46107</v>
       </c>
       <c r="I42" s="89"/>
       <c r="J42" s="76"/>
@@ -5001,19 +5019,19 @@
         <v>17</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="E43" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F43" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="87">
-        <v>46051</v>
+        <v>46107</v>
       </c>
       <c r="H43" s="91"/>
       <c r="I43" s="89"/>
@@ -5159,7 +5177,7 @@
         <v>284</v>
       </c>
       <c r="F48" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="91">
         <v>46065</v>
@@ -5302,7 +5320,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5558,7 +5576,7 @@
         <v>30</v>
       </c>
       <c r="F65" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G65" s="83"/>
       <c r="H65" s="90"/>
@@ -5983,7 +6001,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6107,12 +6125,12 @@
         <v>8</v>
       </c>
       <c r="F86" s="15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
       <c r="I86" s="93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" s="76"/>
       <c r="K86" s="1"/>
@@ -6211,12 +6229,22 @@
     </row>
     <row r="91" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="79"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="29"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="83"/>
+      <c r="B91" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="29">
+        <v>1</v>
+      </c>
+      <c r="F91" s="30">
+        <v>7</v>
+      </c>
+      <c r="G91" s="87"/>
       <c r="H91" s="91"/>
       <c r="I91" s="90"/>
       <c r="J91" s="76"/>
@@ -6228,23 +6256,27 @@
     </row>
     <row r="92" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="79"/>
-      <c r="B92" s="28" t="s">
+      <c r="B92" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C92" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="D92" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E92" s="29">
+      <c r="C92" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="106" t="s">
+        <v>136</v>
+      </c>
+      <c r="E92" s="107">
         <v>1</v>
       </c>
-      <c r="F92" s="30">
-        <v>7</v>
-      </c>
-      <c r="G92" s="87"/>
-      <c r="H92" s="91"/>
+      <c r="F92" s="108">
+        <v>0</v>
+      </c>
+      <c r="G92" s="91" t="s">
+        <v>285</v>
+      </c>
+      <c r="H92" s="91">
+        <v>45876</v>
+      </c>
       <c r="I92" s="90"/>
       <c r="J92" s="76"/>
       <c r="K92" s="1"/>
@@ -6259,22 +6291,22 @@
         <v>16</v>
       </c>
       <c r="C93" s="106" t="s">
-        <v>65</v>
+        <v>488</v>
       </c>
       <c r="D93" s="106" t="s">
-        <v>136</v>
-      </c>
-      <c r="E93" s="107">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="E93" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F93" s="108">
-        <v>0</v>
-      </c>
-      <c r="G93" s="91" t="s">
-        <v>285</v>
+        <v>2</v>
+      </c>
+      <c r="G93" s="91">
+        <v>45876</v>
       </c>
       <c r="H93" s="91">
-        <v>45876</v>
+        <v>46065</v>
       </c>
       <c r="I93" s="91"/>
       <c r="J93" s="76"/>
@@ -6286,27 +6318,25 @@
     </row>
     <row r="94" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="79"/>
-      <c r="B94" s="106" t="s">
+      <c r="B94" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C94" s="106" t="s">
-        <v>488</v>
-      </c>
-      <c r="D94" s="106" t="s">
-        <v>24</v>
-      </c>
-      <c r="E94" s="107" t="s">
+      <c r="C94" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="D94" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="E94" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F94" s="108">
+      <c r="F94" s="30">
         <v>2</v>
       </c>
       <c r="G94" s="91">
-        <v>45876</v>
-      </c>
-      <c r="H94" s="91">
         <v>46065</v>
       </c>
+      <c r="H94" s="91"/>
       <c r="I94" s="90"/>
       <c r="J94" s="76"/>
       <c r="K94" s="1"/>
@@ -6321,20 +6351,18 @@
         <v>16</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>526</v>
+        <v>137</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="E95" s="29" t="s">
-        <v>284</v>
+        <v>18</v>
+      </c>
+      <c r="E95" s="29">
+        <v>19</v>
       </c>
       <c r="F95" s="30">
-        <v>2</v>
-      </c>
-      <c r="G95" s="91">
-        <v>46065</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G95" s="91"/>
       <c r="H95" s="91"/>
       <c r="I95" s="90"/>
       <c r="J95" s="76"/>
@@ -6347,21 +6375,21 @@
     <row r="96" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="79"/>
       <c r="B96" s="28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E96" s="29">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F96" s="30">
-        <v>9</v>
-      </c>
-      <c r="G96" s="91"/>
+        <v>17</v>
+      </c>
+      <c r="G96" s="87"/>
       <c r="H96" s="91"/>
       <c r="I96" s="90"/>
       <c r="J96" s="76"/>
@@ -6373,23 +6401,27 @@
     </row>
     <row r="97" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="79"/>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C97" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="D97" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E97" s="29">
-        <v>25</v>
-      </c>
-      <c r="F97" s="30">
-        <v>17</v>
-      </c>
-      <c r="G97" s="87"/>
-      <c r="H97" s="91"/>
+      <c r="C97" s="106" t="s">
+        <v>154</v>
+      </c>
+      <c r="D97" s="106" t="s">
+        <v>153</v>
+      </c>
+      <c r="E97" s="107">
+        <v>10</v>
+      </c>
+      <c r="F97" s="108">
+        <v>3</v>
+      </c>
+      <c r="G97" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H97" s="91">
+        <v>45995</v>
+      </c>
       <c r="I97" s="90"/>
       <c r="J97" s="76"/>
       <c r="K97" s="1"/>
@@ -6404,22 +6436,22 @@
         <v>17</v>
       </c>
       <c r="C98" s="106" t="s">
-        <v>154</v>
+        <v>484</v>
       </c>
       <c r="D98" s="106" t="s">
-        <v>153</v>
-      </c>
-      <c r="E98" s="107">
-        <v>10</v>
+        <v>97</v>
+      </c>
+      <c r="E98" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F98" s="108">
         <v>3</v>
       </c>
-      <c r="G98" s="83" t="s">
-        <v>285</v>
+      <c r="G98" s="87">
+        <v>45995</v>
       </c>
       <c r="H98" s="91">
-        <v>45995</v>
+        <v>46086</v>
       </c>
       <c r="I98" s="90"/>
       <c r="J98" s="76"/>
@@ -6431,27 +6463,25 @@
     </row>
     <row r="99" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="79"/>
-      <c r="B99" s="106" t="s">
+      <c r="B99" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="106" t="s">
-        <v>484</v>
-      </c>
-      <c r="D99" s="106" t="s">
-        <v>97</v>
-      </c>
-      <c r="E99" s="107" t="s">
+      <c r="C99" s="28" t="s">
+        <v>536</v>
+      </c>
+      <c r="D99" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="E99" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F99" s="108">
-        <v>3</v>
+      <c r="F99" s="30">
+        <v>2</v>
       </c>
       <c r="G99" s="87">
-        <v>45995</v>
-      </c>
-      <c r="H99" s="91">
         <v>46086</v>
       </c>
+      <c r="H99" s="91"/>
       <c r="I99" s="90"/>
       <c r="J99" s="76"/>
       <c r="K99" s="1"/>
@@ -6462,28 +6492,28 @@
     </row>
     <row r="100" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="79"/>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C100" s="28" t="s">
-        <v>536</v>
-      </c>
-      <c r="D100" s="28" t="s">
-        <v>537</v>
-      </c>
-      <c r="E100" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F100" s="30">
-        <v>2</v>
-      </c>
-      <c r="G100" s="87">
-        <v>46086</v>
-      </c>
-      <c r="H100" s="91"/>
-      <c r="I100" s="90">
+      <c r="C100" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" s="106" t="s">
+        <v>148</v>
+      </c>
+      <c r="E100" s="107">
+        <v>6</v>
+      </c>
+      <c r="F100" s="108">
         <v>1</v>
       </c>
+      <c r="G100" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H100" s="91">
+        <v>45918</v>
+      </c>
+      <c r="I100" s="90"/>
       <c r="J100" s="76"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -6493,27 +6523,25 @@
     </row>
     <row r="101" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="79"/>
-      <c r="B101" s="106" t="s">
+      <c r="B101" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="106" t="s">
-        <v>60</v>
-      </c>
-      <c r="D101" s="106" t="s">
-        <v>148</v>
-      </c>
-      <c r="E101" s="107">
-        <v>6</v>
-      </c>
-      <c r="F101" s="108">
-        <v>1</v>
-      </c>
-      <c r="G101" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H101" s="91">
+      <c r="C101" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="D101" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E101" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F101" s="30">
+        <v>17</v>
+      </c>
+      <c r="G101" s="87">
         <v>45918</v>
       </c>
+      <c r="H101" s="91"/>
       <c r="I101" s="90"/>
       <c r="J101" s="76"/>
       <c r="K101" s="1"/>
@@ -6524,25 +6552,27 @@
     </row>
     <row r="102" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="79"/>
-      <c r="B102" s="28" t="s">
+      <c r="B102" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C102" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="D102" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="E102" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F102" s="30">
-        <v>17</v>
-      </c>
-      <c r="G102" s="87">
-        <v>45918</v>
-      </c>
-      <c r="H102" s="91"/>
+      <c r="C102" s="106" t="s">
+        <v>93</v>
+      </c>
+      <c r="D102" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="E102" s="107">
+        <v>22</v>
+      </c>
+      <c r="F102" s="108">
+        <v>5</v>
+      </c>
+      <c r="G102" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H102" s="91">
+        <v>46079</v>
+      </c>
       <c r="I102" s="90"/>
       <c r="J102" s="76"/>
       <c r="K102" s="1"/>
@@ -6557,20 +6587,24 @@
         <v>17</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>93</v>
+        <v>546</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E103" s="29">
-        <v>22</v>
+        <v>276</v>
+      </c>
+      <c r="E103" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F103" s="30">
-        <v>7</v>
-      </c>
-      <c r="G103" s="87"/>
+        <v>1</v>
+      </c>
+      <c r="G103" s="87">
+        <v>46079</v>
+      </c>
       <c r="H103" s="91"/>
-      <c r="I103" s="90"/>
+      <c r="I103" s="90">
+        <v>1</v>
+      </c>
       <c r="J103" s="76"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -6655,13 +6689,15 @@
         <v>284</v>
       </c>
       <c r="F106" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G106" s="87">
         <v>46002</v>
       </c>
       <c r="H106" s="91"/>
-      <c r="I106" s="92"/>
+      <c r="I106" s="92">
+        <v>1</v>
+      </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6680,7 +6716,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6804,7 +6840,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -7373,7 +7409,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7555,15 +7591,13 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
       </c>
       <c r="H142" s="92"/>
-      <c r="I142" s="118">
-        <v>1</v>
-      </c>
+      <c r="I142" s="118"/>
       <c r="J142" s="76"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1"/>
@@ -7791,9 +7825,7 @@
         <v>46030</v>
       </c>
       <c r="H150" s="91"/>
-      <c r="I150" s="90">
-        <v>1</v>
-      </c>
+      <c r="I150" s="90"/>
       <c r="J150" s="76"/>
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
@@ -7847,7 +7879,7 @@
         <v>284</v>
       </c>
       <c r="F152" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G152" s="87">
         <v>46072</v>
@@ -8112,7 +8144,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8796,7 +8828,7 @@
         <v>284</v>
       </c>
       <c r="F187" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G187" s="86">
         <v>45953</v>
@@ -8821,7 +8853,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -9077,7 +9109,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9290,7 +9322,7 @@
         <v>1</v>
       </c>
       <c r="F209" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G209" s="87"/>
       <c r="H209" s="91"/>
@@ -9408,7 +9440,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9590,7 +9622,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9953,7 +9985,7 @@
         <v>8</v>
       </c>
       <c r="F236" s="30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G236" s="83"/>
       <c r="H236" s="91"/>
@@ -10113,7 +10145,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10482,9 +10514,7 @@
         <v>46030</v>
       </c>
       <c r="H257" s="91"/>
-      <c r="I257" s="90">
-        <v>1</v>
-      </c>
+      <c r="I257" s="90"/>
       <c r="J257" s="1"/>
       <c r="K257" s="1"/>
       <c r="L257" s="1"/>
@@ -10578,7 +10608,7 @@
         <v>18</v>
       </c>
       <c r="F261" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G261" s="87"/>
       <c r="H261" s="91"/>
@@ -10702,9 +10732,7 @@
         <v>45953</v>
       </c>
       <c r="H265" s="91"/>
-      <c r="I265" s="90">
-        <v>1</v>
-      </c>
+      <c r="I265" s="90"/>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
       <c r="L265" s="1"/>
@@ -10814,7 +10842,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11373,7 +11401,7 @@
         <v>1</v>
       </c>
       <c r="F292" s="30">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G292" s="87"/>
       <c r="H292" s="91"/>
@@ -11447,7 +11475,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -12161,7 +12189,7 @@
         <v>284</v>
       </c>
       <c r="F322" s="30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G322" s="87">
         <v>45890</v>
@@ -12186,7 +12214,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12654,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
@@ -12820,7 +12848,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -12902,7 +12930,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -13106,7 +13134,7 @@
         <v>284</v>
       </c>
       <c r="F366" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G366" s="103">
         <v>45904</v>
@@ -13342,7 +13370,7 @@
         <v>284</v>
       </c>
       <c r="F376" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G376" s="103">
         <v>45939</v>
@@ -13361,7 +13389,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -13730,19 +13758,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="E7" s="25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" s="26">
         <v>89</v>
       </c>
       <c r="G7" s="27">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13755,19 +13783,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>31</v>
       </c>
       <c r="E8" s="25">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F8" s="26">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G8" s="27">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13780,19 +13808,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="E9" s="25">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F9" s="26">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G9" s="27">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13811,10 +13839,10 @@
         <v>198</v>
       </c>
       <c r="E10" s="25">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" s="26">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="27">
         <v>38</v>
@@ -13830,19 +13858,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>203</v>
+        <v>21</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>188</v>
       </c>
       <c r="E11" s="25">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" s="26">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G11" s="27">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13855,19 +13883,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E12" s="25">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="26">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G12" s="27">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13886,13 +13914,13 @@
         <v>267</v>
       </c>
       <c r="E13" s="25">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="56">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G13" s="57">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -13911,10 +13939,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="26">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" s="27">
         <v>35</v>
@@ -13930,19 +13958,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>245</v>
+        <v>55</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>222</v>
       </c>
       <c r="E15" s="25">
-        <v>16</v>
-      </c>
-      <c r="F15" s="56">
-        <v>59</v>
-      </c>
-      <c r="G15" s="57">
-        <v>43</v>
+        <v>15</v>
+      </c>
+      <c r="F15" s="26">
+        <v>75</v>
+      </c>
+      <c r="G15" s="27">
+        <v>60</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -13955,19 +13983,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>244</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E16" s="25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="26">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G16" s="27">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -13980,19 +14008,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="E17" s="25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="26">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G17" s="27">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -14005,19 +14033,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>140</v>
+        <v>35</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>34</v>
       </c>
       <c r="E18" s="25">
-        <v>9</v>
-      </c>
-      <c r="F18" s="26">
-        <v>63</v>
-      </c>
-      <c r="G18" s="27">
-        <v>54</v>
+        <v>11</v>
+      </c>
+      <c r="F18" s="56">
+        <v>58</v>
+      </c>
+      <c r="G18" s="57">
+        <v>47</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -14032,16 +14060,16 @@
       <c r="C19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="24" t="s">
         <v>53</v>
       </c>
       <c r="E19" s="25">
-        <v>6</v>
-      </c>
-      <c r="F19" s="56">
-        <v>53</v>
-      </c>
-      <c r="G19" s="57">
+        <v>8</v>
+      </c>
+      <c r="F19" s="26">
+        <v>55</v>
+      </c>
+      <c r="G19" s="27">
         <v>47</v>
       </c>
       <c r="H19" s="52"/>
@@ -14057,16 +14085,16 @@
       <c r="C20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="55" t="s">
         <v>243</v>
       </c>
       <c r="E20" s="25">
-        <v>6</v>
-      </c>
-      <c r="F20" s="26">
-        <v>52</v>
-      </c>
-      <c r="G20" s="27">
+        <v>7</v>
+      </c>
+      <c r="F20" s="56">
+        <v>53</v>
+      </c>
+      <c r="G20" s="57">
         <v>46</v>
       </c>
       <c r="H20" s="117"/>
@@ -14618,13 +14646,21 @@
       <c r="B28" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="68" t="s">
+      <c r="C28" s="64">
+        <v>1</v>
+      </c>
+      <c r="D28" s="64" t="s">
+        <v>433</v>
+      </c>
+      <c r="E28" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="100"/>
-      <c r="G28" s="100"/>
+      <c r="F28" s="100">
+        <v>0</v>
+      </c>
+      <c r="G28" s="100" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="65"/>
@@ -14653,7 +14689,9 @@
       </c>
       <c r="C31" s="68"/>
       <c r="D31" s="64"/>
-      <c r="E31" s="70"/>
+      <c r="E31" s="65" t="s">
+        <v>1</v>
+      </c>
       <c r="F31" s="69"/>
       <c r="G31" s="100"/>
     </row>
@@ -17225,7 +17263,7 @@
       </c>
       <c r="O19">
         <f>COUNTIF(Stats!D:D,'Player Count'!N19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="109"/>
     </row>
@@ -17491,7 +17529,7 @@
       </c>
       <c r="K28">
         <f>COUNTIF(Stats!D:D,'Player Count'!J28)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28" s="109"/>
       <c r="N28" s="67" t="s">
@@ -17539,14 +17577,14 @@
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -17555,28 +17593,28 @@
       </c>
       <c r="C38" s="114">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.36363636363636365</v>
+        <v>0.36065573770491804</v>
       </c>
       <c r="D38" s="114"/>
       <c r="E38" s="114"/>
       <c r="F38" s="114"/>
       <c r="G38" s="114">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.26859504132231404</v>
+        <v>0.26639344262295084</v>
       </c>
       <c r="H38" s="114"/>
       <c r="I38" s="114"/>
       <c r="J38" s="114"/>
       <c r="K38" s="114">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.21487603305785125</v>
+        <v>0.21721311475409835</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114"/>
       <c r="N38" s="114"/>
       <c r="O38" s="114">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.15289256198347106</v>
+        <v>0.15573770491803279</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1530" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF8C3D2-E378-44AA-AD57-EAEAB798CB95}"/>
+  <xr:revisionPtr revIDLastSave="1588" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A70F053-0421-421B-9B6E-466BCB556639}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="550">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1680,6 +1680,15 @@
   </si>
   <si>
     <t>ANDY COOK</t>
+  </si>
+  <si>
+    <t>CRYSENCIO SUMMERVILLE</t>
+  </si>
+  <si>
+    <t>MANCHESTER UTD</t>
+  </si>
+  <si>
+    <t>JACK MOYLAN</t>
   </si>
 </sst>
 </file>
@@ -3795,7 +3804,7 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
@@ -3803,7 +3812,7 @@
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3920,11 +3929,11 @@
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3999,9 +4008,7 @@
         <v>46009</v>
       </c>
       <c r="H11" s="84"/>
-      <c r="I11" s="99">
-        <v>1</v>
-      </c>
+      <c r="I11" s="99"/>
       <c r="J11" s="82"/>
       <c r="K11" s="23" t="str">
         <f>D164</f>
@@ -4062,11 +4069,11 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
@@ -4110,11 +4117,11 @@
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4153,7 +4160,7 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
@@ -4161,7 +4168,7 @@
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -4202,11 +4209,11 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
@@ -4339,7 +4346,7 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
@@ -4347,7 +4354,7 @@
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4707,9 +4714,9 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="79"/>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="115" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="111"/>
@@ -4738,23 +4745,25 @@
     </row>
     <row r="33" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="79"/>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21" t="s">
+      <c r="C33" s="115"/>
+      <c r="D33" s="115" t="s">
         <v>85</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="116" t="s">
         <v>284</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="115">
         <v>6</v>
       </c>
       <c r="G33" s="86">
         <v>46072</v>
       </c>
-      <c r="H33" s="94"/>
+      <c r="H33" s="94">
+        <v>46107</v>
+      </c>
       <c r="I33" s="93"/>
       <c r="J33" s="76"/>
       <c r="K33" s="1"/>
@@ -4765,12 +4774,22 @@
     </row>
     <row r="34" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="79"/>
-      <c r="B34" s="21"/>
+      <c r="B34" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="86"/>
+      <c r="D34" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="F34" s="21">
+        <v>2</v>
+      </c>
+      <c r="G34" s="86">
+        <v>46107</v>
+      </c>
       <c r="H34" s="92"/>
       <c r="I34" s="93"/>
       <c r="J34" s="76"/>
@@ -5320,7 +5339,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5677,13 +5696,27 @@
     </row>
     <row r="69" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="79"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="87"/>
-      <c r="H69" s="91"/>
+      <c r="B69" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" s="106" t="s">
+        <v>99</v>
+      </c>
+      <c r="D69" s="106" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="107">
+        <v>5</v>
+      </c>
+      <c r="F69" s="108">
+        <v>8</v>
+      </c>
+      <c r="G69" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H69" s="91">
+        <v>46058</v>
+      </c>
       <c r="I69" s="90"/>
       <c r="J69" s="76"/>
       <c r="K69" s="1"/>
@@ -5694,27 +5727,25 @@
     </row>
     <row r="70" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="79"/>
-      <c r="B70" s="106" t="s">
+      <c r="B70" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="106" t="s">
-        <v>99</v>
-      </c>
-      <c r="D70" s="106" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" s="107">
-        <v>5</v>
-      </c>
-      <c r="F70" s="108">
-        <v>8</v>
-      </c>
-      <c r="G70" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H70" s="91">
+      <c r="C70" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E70" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F70" s="30">
+        <v>3</v>
+      </c>
+      <c r="G70" s="87">
         <v>46058</v>
       </c>
+      <c r="H70" s="91"/>
       <c r="I70" s="90"/>
       <c r="J70" s="76"/>
       <c r="K70" s="1"/>
@@ -5725,25 +5756,27 @@
     </row>
     <row r="71" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="79"/>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C71" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="D71" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="E71" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F71" s="30">
-        <v>3</v>
-      </c>
-      <c r="G71" s="87">
-        <v>46058</v>
-      </c>
-      <c r="H71" s="91"/>
+      <c r="C71" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71" s="106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="107">
+        <v>7</v>
+      </c>
+      <c r="F71" s="108">
+        <v>0</v>
+      </c>
+      <c r="G71" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H71" s="91">
+        <v>45897</v>
+      </c>
       <c r="I71" s="90"/>
       <c r="J71" s="76"/>
       <c r="K71" s="1"/>
@@ -5754,27 +5787,25 @@
     </row>
     <row r="72" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="79"/>
-      <c r="B72" s="106" t="s">
+      <c r="B72" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C72" s="106" t="s">
-        <v>59</v>
-      </c>
-      <c r="D72" s="106" t="s">
-        <v>18</v>
-      </c>
-      <c r="E72" s="107">
+      <c r="C72" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E72" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F72" s="30">
         <v>7</v>
       </c>
-      <c r="F72" s="108">
-        <v>0</v>
-      </c>
-      <c r="G72" s="83" t="s">
-        <v>285</v>
-      </c>
-      <c r="H72" s="91">
+      <c r="G72" s="87">
         <v>45897</v>
       </c>
+      <c r="H72" s="91"/>
       <c r="I72" s="90"/>
       <c r="J72" s="76"/>
       <c r="K72" s="1"/>
@@ -5789,20 +5820,18 @@
         <v>17</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>405</v>
+        <v>195</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E73" s="29" t="s">
-        <v>284</v>
+        <v>160</v>
+      </c>
+      <c r="E73" s="29">
+        <v>7</v>
       </c>
       <c r="F73" s="30">
-        <v>7</v>
-      </c>
-      <c r="G73" s="87">
-        <v>45897</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G73" s="87"/>
       <c r="H73" s="91"/>
       <c r="I73" s="90"/>
       <c r="J73" s="96"/>
@@ -5814,23 +5843,27 @@
     </row>
     <row r="74" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="79"/>
-      <c r="B74" s="28" t="s">
+      <c r="B74" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C74" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="D74" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="E74" s="29">
-        <v>7</v>
-      </c>
-      <c r="F74" s="30">
-        <v>6</v>
-      </c>
-      <c r="G74" s="87"/>
-      <c r="H74" s="91"/>
+      <c r="C74" s="106" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" s="106" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="107">
+        <v>1</v>
+      </c>
+      <c r="F74" s="108">
+        <v>0</v>
+      </c>
+      <c r="G74" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H74" s="91">
+        <v>45890</v>
+      </c>
       <c r="I74" s="90"/>
       <c r="J74" s="76"/>
       <c r="K74" s="1"/>
@@ -5845,22 +5878,22 @@
         <v>17</v>
       </c>
       <c r="C75" s="106" t="s">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="D75" s="106" t="s">
-        <v>82</v>
-      </c>
-      <c r="E75" s="107">
-        <v>1</v>
+        <v>293</v>
+      </c>
+      <c r="E75" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F75" s="108">
-        <v>0</v>
-      </c>
-      <c r="G75" s="87" t="s">
-        <v>285</v>
+        <v>3</v>
+      </c>
+      <c r="G75" s="87">
+        <v>45890</v>
       </c>
       <c r="H75" s="91">
-        <v>45890</v>
+        <v>46044</v>
       </c>
       <c r="I75" s="90"/>
       <c r="J75" s="76"/>
@@ -5872,27 +5905,25 @@
     </row>
     <row r="76" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="79"/>
-      <c r="B76" s="106" t="s">
+      <c r="B76" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C76" s="106" t="s">
-        <v>292</v>
-      </c>
-      <c r="D76" s="106" t="s">
-        <v>293</v>
-      </c>
-      <c r="E76" s="107" t="s">
+      <c r="C76" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F76" s="108">
+      <c r="F76" s="30">
         <v>3</v>
       </c>
       <c r="G76" s="87">
-        <v>45890</v>
-      </c>
-      <c r="H76" s="91">
         <v>46044</v>
       </c>
+      <c r="H76" s="91"/>
       <c r="I76" s="90"/>
       <c r="J76" s="76"/>
       <c r="K76" s="1"/>
@@ -5903,25 +5934,27 @@
     </row>
     <row r="77" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="79"/>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C77" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D77" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F77" s="30">
-        <v>3</v>
-      </c>
-      <c r="G77" s="87">
-        <v>46044</v>
-      </c>
-      <c r="H77" s="91"/>
+      <c r="C77" s="106" t="s">
+        <v>197</v>
+      </c>
+      <c r="D77" s="106" t="s">
+        <v>100</v>
+      </c>
+      <c r="E77" s="107">
+        <v>1</v>
+      </c>
+      <c r="F77" s="108">
+        <v>1</v>
+      </c>
+      <c r="G77" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H77" s="91">
+        <v>45946</v>
+      </c>
       <c r="I77" s="90"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -5936,22 +5969,22 @@
         <v>17</v>
       </c>
       <c r="C78" s="106" t="s">
-        <v>197</v>
+        <v>458</v>
       </c>
       <c r="D78" s="106" t="s">
-        <v>100</v>
-      </c>
-      <c r="E78" s="107">
-        <v>1</v>
+        <v>459</v>
+      </c>
+      <c r="E78" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F78" s="108">
-        <v>1</v>
-      </c>
-      <c r="G78" s="87" t="s">
-        <v>285</v>
+        <v>4</v>
+      </c>
+      <c r="G78" s="87">
+        <v>45946</v>
       </c>
       <c r="H78" s="91">
-        <v>45946</v>
+        <v>46107</v>
       </c>
       <c r="I78" s="90"/>
       <c r="J78" s="76"/>
@@ -5967,19 +6000,19 @@
         <v>17</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>459</v>
+        <v>58</v>
       </c>
       <c r="E79" s="29" t="s">
         <v>284</v>
       </c>
       <c r="F79" s="30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G79" s="87">
-        <v>45946</v>
+        <v>46107</v>
       </c>
       <c r="H79" s="91"/>
       <c r="I79" s="92"/>
@@ -6129,9 +6162,7 @@
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
-      <c r="I86" s="93">
-        <v>2</v>
-      </c>
+      <c r="I86" s="93"/>
       <c r="J86" s="76"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -6602,9 +6633,7 @@
         <v>46079</v>
       </c>
       <c r="H103" s="91"/>
-      <c r="I103" s="90">
-        <v>1</v>
-      </c>
+      <c r="I103" s="90"/>
       <c r="J103" s="76"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -6695,9 +6724,7 @@
         <v>46002</v>
       </c>
       <c r="H106" s="91"/>
-      <c r="I106" s="92">
-        <v>1</v>
-      </c>
+      <c r="I106" s="92"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6840,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -6942,13 +6969,27 @@
     </row>
     <row r="118" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="79"/>
-      <c r="B118" s="28"/>
-      <c r="C118" s="28"/>
-      <c r="D118" s="28"/>
-      <c r="E118" s="29"/>
-      <c r="F118" s="30"/>
-      <c r="G118" s="87"/>
-      <c r="H118" s="91"/>
+      <c r="B118" s="106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" s="106" t="s">
+        <v>208</v>
+      </c>
+      <c r="D118" s="106" t="s">
+        <v>82</v>
+      </c>
+      <c r="E118" s="107">
+        <v>19</v>
+      </c>
+      <c r="F118" s="108">
+        <v>15</v>
+      </c>
+      <c r="G118" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H118" s="91">
+        <v>46079</v>
+      </c>
       <c r="I118" s="90"/>
       <c r="J118" s="76"/>
       <c r="K118" s="1"/>
@@ -6963,18 +7004,20 @@
         <v>16</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>208</v>
+        <v>549</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E119" s="29">
-        <v>19</v>
+        <v>404</v>
+      </c>
+      <c r="E119" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="F119" s="30">
-        <v>15</v>
-      </c>
-      <c r="G119" s="87"/>
+        <v>1</v>
+      </c>
+      <c r="G119" s="87">
+        <v>46079</v>
+      </c>
       <c r="H119" s="91"/>
       <c r="I119" s="90"/>
       <c r="J119" s="76"/>
@@ -9349,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="F210" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G210" s="87"/>
       <c r="H210" s="90"/>
@@ -9440,7 +9483,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9622,7 +9665,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -10103,7 +10146,7 @@
         <v>284</v>
       </c>
       <c r="F240" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G240" s="87">
         <v>45911</v>
@@ -10319,7 +10362,7 @@
         <v>284</v>
       </c>
       <c r="F250" s="21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G250" s="86">
         <v>46037</v>
@@ -10389,11 +10432,21 @@
     </row>
     <row r="253" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="79"/>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28"/>
-      <c r="D253" s="28"/>
-      <c r="E253" s="29"/>
-      <c r="F253" s="30"/>
+      <c r="B253" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C253" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D253" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="E253" s="29">
+        <v>1</v>
+      </c>
+      <c r="F253" s="30">
+        <v>10</v>
+      </c>
       <c r="G253" s="83"/>
       <c r="H253" s="91"/>
       <c r="I253" s="90"/>
@@ -10406,23 +10459,27 @@
     </row>
     <row r="254" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="79"/>
-      <c r="B254" s="28" t="s">
+      <c r="B254" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="C254" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="D254" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="E254" s="29">
-        <v>1</v>
-      </c>
-      <c r="F254" s="30">
-        <v>10</v>
-      </c>
-      <c r="G254" s="83"/>
-      <c r="H254" s="91"/>
+      <c r="C254" s="106" t="s">
+        <v>130</v>
+      </c>
+      <c r="D254" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E254" s="107">
+        <v>2</v>
+      </c>
+      <c r="F254" s="108">
+        <v>0</v>
+      </c>
+      <c r="G254" s="91" t="s">
+        <v>285</v>
+      </c>
+      <c r="H254" s="91">
+        <v>45890</v>
+      </c>
       <c r="I254" s="90"/>
       <c r="J254" s="1"/>
       <c r="K254" s="1"/>
@@ -10437,22 +10494,22 @@
         <v>16</v>
       </c>
       <c r="C255" s="106" t="s">
-        <v>130</v>
+        <v>294</v>
       </c>
       <c r="D255" s="106" t="s">
-        <v>24</v>
-      </c>
-      <c r="E255" s="107">
+        <v>288</v>
+      </c>
+      <c r="E255" s="107" t="s">
+        <v>284</v>
+      </c>
+      <c r="F255" s="108">
         <v>2</v>
       </c>
-      <c r="F255" s="108">
-        <v>0</v>
-      </c>
-      <c r="G255" s="91" t="s">
-        <v>285</v>
+      <c r="G255" s="87">
+        <v>45890</v>
       </c>
       <c r="H255" s="91">
-        <v>45890</v>
+        <v>46030</v>
       </c>
       <c r="I255" s="90"/>
       <c r="J255" s="1"/>
@@ -10464,27 +10521,25 @@
     </row>
     <row r="256" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="79"/>
-      <c r="B256" s="106" t="s">
+      <c r="B256" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C256" s="106" t="s">
-        <v>294</v>
-      </c>
-      <c r="D256" s="106" t="s">
-        <v>288</v>
-      </c>
-      <c r="E256" s="107" t="s">
+      <c r="C256" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="D256" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="E256" s="29" t="s">
         <v>284</v>
       </c>
-      <c r="F256" s="108">
+      <c r="F256" s="30">
         <v>2</v>
       </c>
       <c r="G256" s="87">
-        <v>45890</v>
-      </c>
-      <c r="H256" s="91">
         <v>46030</v>
       </c>
+      <c r="H256" s="91"/>
       <c r="I256" s="90"/>
       <c r="J256" s="1"/>
       <c r="K256" s="1"/>
@@ -10499,20 +10554,18 @@
         <v>16</v>
       </c>
       <c r="C257" s="28" t="s">
-        <v>502</v>
+        <v>224</v>
       </c>
       <c r="D257" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="E257" s="29" t="s">
-        <v>284</v>
+        <v>22</v>
+      </c>
+      <c r="E257" s="29">
+        <v>3</v>
       </c>
       <c r="F257" s="30">
-        <v>2</v>
-      </c>
-      <c r="G257" s="87">
-        <v>46030</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G257" s="87"/>
       <c r="H257" s="91"/>
       <c r="I257" s="90"/>
       <c r="J257" s="1"/>
@@ -10524,23 +10577,27 @@
     </row>
     <row r="258" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="79"/>
-      <c r="B258" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C258" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="D258" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E258" s="29">
+      <c r="B258" s="106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C258" s="106" t="s">
+        <v>225</v>
+      </c>
+      <c r="D258" s="106" t="s">
+        <v>118</v>
+      </c>
+      <c r="E258" s="107">
+        <v>20</v>
+      </c>
+      <c r="F258" s="108">
         <v>3</v>
       </c>
-      <c r="F258" s="30">
-        <v>9</v>
-      </c>
-      <c r="G258" s="87"/>
-      <c r="H258" s="91"/>
+      <c r="G258" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H258" s="91">
+        <v>46107</v>
+      </c>
       <c r="I258" s="90"/>
       <c r="J258" s="1"/>
       <c r="K258" s="1"/>
@@ -10551,12 +10608,24 @@
     </row>
     <row r="259" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="79"/>
-      <c r="B259" s="28"/>
-      <c r="C259" s="28"/>
-      <c r="D259" s="28"/>
-      <c r="E259" s="29"/>
-      <c r="F259" s="30"/>
-      <c r="G259" s="83"/>
+      <c r="B259" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C259" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="D259" s="28" t="s">
+        <v>548</v>
+      </c>
+      <c r="E259" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F259" s="30">
+        <v>0</v>
+      </c>
+      <c r="G259" s="87">
+        <v>46107</v>
+      </c>
       <c r="H259" s="91"/>
       <c r="I259" s="90"/>
       <c r="J259" s="1"/>
@@ -10572,16 +10641,16 @@
         <v>17</v>
       </c>
       <c r="C260" s="28" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="D260" s="28" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="E260" s="29">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F260" s="30">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -10595,23 +10664,27 @@
     </row>
     <row r="261" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="79"/>
-      <c r="B261" s="28" t="s">
+      <c r="B261" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C261" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="D261" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E261" s="29">
-        <v>18</v>
-      </c>
-      <c r="F261" s="30">
-        <v>10</v>
-      </c>
-      <c r="G261" s="87"/>
-      <c r="H261" s="91"/>
+      <c r="C261" s="106" t="s">
+        <v>106</v>
+      </c>
+      <c r="D261" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="E261" s="107">
+        <v>16</v>
+      </c>
+      <c r="F261" s="108">
+        <v>0</v>
+      </c>
+      <c r="G261" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H261" s="91">
+        <v>45946</v>
+      </c>
       <c r="I261" s="90"/>
       <c r="J261" s="1"/>
       <c r="K261" s="1"/>
@@ -10622,27 +10695,25 @@
     </row>
     <row r="262" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="79"/>
-      <c r="B262" s="106" t="s">
+      <c r="B262" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C262" s="106" t="s">
-        <v>106</v>
-      </c>
-      <c r="D262" s="106" t="s">
-        <v>24</v>
-      </c>
-      <c r="E262" s="107">
-        <v>16</v>
-      </c>
-      <c r="F262" s="108">
-        <v>0</v>
-      </c>
-      <c r="G262" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H262" s="91">
+      <c r="C262" s="28" t="s">
+        <v>460</v>
+      </c>
+      <c r="D262" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="E262" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F262" s="30">
+        <v>15</v>
+      </c>
+      <c r="G262" s="87">
         <v>45946</v>
       </c>
+      <c r="H262" s="91"/>
       <c r="I262" s="90"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
@@ -10653,25 +10724,27 @@
     </row>
     <row r="263" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="79"/>
-      <c r="B263" s="28" t="s">
+      <c r="B263" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C263" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="D263" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="E263" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F263" s="30">
-        <v>15</v>
-      </c>
-      <c r="G263" s="87">
-        <v>45946</v>
-      </c>
-      <c r="H263" s="91"/>
+      <c r="C263" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="D263" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="E263" s="107">
+        <v>14</v>
+      </c>
+      <c r="F263" s="108">
+        <v>0</v>
+      </c>
+      <c r="G263" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="H263" s="91">
+        <v>45953</v>
+      </c>
       <c r="I263" s="90"/>
       <c r="J263" s="1"/>
       <c r="K263" s="1"/>
@@ -10682,27 +10755,25 @@
     </row>
     <row r="264" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="79"/>
-      <c r="B264" s="106" t="s">
+      <c r="B264" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C264" s="106" t="s">
-        <v>139</v>
-      </c>
-      <c r="D264" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="E264" s="107">
-        <v>14</v>
-      </c>
-      <c r="F264" s="108">
-        <v>0</v>
-      </c>
-      <c r="G264" s="87" t="s">
-        <v>285</v>
-      </c>
-      <c r="H264" s="91">
+      <c r="C264" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="D264" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E264" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="F264" s="30">
+        <v>16</v>
+      </c>
+      <c r="G264" s="87">
         <v>45953</v>
       </c>
+      <c r="H264" s="91"/>
       <c r="I264" s="90"/>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
@@ -10713,25 +10784,27 @@
     </row>
     <row r="265" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="79"/>
-      <c r="B265" s="28" t="s">
+      <c r="B265" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C265" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="D265" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E265" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="F265" s="30">
-        <v>16</v>
-      </c>
-      <c r="G265" s="87">
-        <v>45953</v>
-      </c>
-      <c r="H265" s="91"/>
+      <c r="C265" s="106" t="s">
+        <v>141</v>
+      </c>
+      <c r="D265" s="106" t="s">
+        <v>288</v>
+      </c>
+      <c r="E265" s="107">
+        <v>14</v>
+      </c>
+      <c r="F265" s="108">
+        <v>0</v>
+      </c>
+      <c r="G265" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="H265" s="91">
+        <v>45897</v>
+      </c>
       <c r="I265" s="90"/>
       <c r="J265" s="1"/>
       <c r="K265" s="1"/>
@@ -10746,22 +10819,22 @@
         <v>17</v>
       </c>
       <c r="C266" s="106" t="s">
-        <v>141</v>
+        <v>406</v>
       </c>
       <c r="D266" s="106" t="s">
-        <v>288</v>
-      </c>
-      <c r="E266" s="107">
-        <v>14</v>
+        <v>73</v>
+      </c>
+      <c r="E266" s="107" t="s">
+        <v>284</v>
       </c>
       <c r="F266" s="108">
-        <v>0</v>
-      </c>
-      <c r="G266" s="83" t="s">
-        <v>285</v>
+        <v>7</v>
+      </c>
+      <c r="G266" s="87">
+        <v>45897</v>
       </c>
       <c r="H266" s="91">
-        <v>45897</v>
+        <v>46002</v>
       </c>
       <c r="I266" s="90"/>
       <c r="J266" s="1"/>
@@ -10777,22 +10850,22 @@
         <v>17</v>
       </c>
       <c r="C267" s="106" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="D267" s="106" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E267" s="107" t="s">
         <v>284</v>
       </c>
       <c r="F267" s="108">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G267" s="87">
-        <v>45897</v>
+        <v>46002</v>
       </c>
       <c r="H267" s="91">
-        <v>46002</v>
+        <v>46107</v>
       </c>
       <c r="I267" s="90"/>
       <c r="J267" s="1"/>
@@ -10808,10 +10881,10 @@
         <v>17</v>
       </c>
       <c r="C268" s="28" t="s">
-        <v>493</v>
+        <v>242</v>
       </c>
       <c r="D268" s="28" t="s">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="E268" s="29" t="s">
         <v>284</v>
@@ -10820,7 +10893,7 @@
         <v>0</v>
       </c>
       <c r="G268" s="87">
-        <v>46002</v>
+        <v>46107</v>
       </c>
       <c r="H268" s="90"/>
       <c r="I268" s="90"/>
@@ -10842,7 +10915,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11260,7 +11333,7 @@
         <v>12</v>
       </c>
       <c r="F287" s="30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G287" s="87"/>
       <c r="H287" s="91"/>
@@ -11475,7 +11548,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -12930,7 +13003,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -13389,7 +13462,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -13760,16 +13833,16 @@
       <c r="C7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="55" t="s">
         <v>233</v>
       </c>
       <c r="E7" s="25">
         <v>36</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="56">
         <v>89</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="57">
         <v>53</v>
       </c>
       <c r="H7" s="117"/>
@@ -13858,19 +13931,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="E11" s="25">
         <v>32</v>
       </c>
       <c r="F11" s="26">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G11" s="27">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13883,19 +13956,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E12" s="25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F12" s="26">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G12" s="27">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13910,17 +13983,17 @@
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="24" t="s">
         <v>267</v>
       </c>
       <c r="E13" s="25">
         <v>27</v>
       </c>
-      <c r="F13" s="56">
-        <v>87</v>
-      </c>
-      <c r="G13" s="57">
-        <v>60</v>
+      <c r="F13" s="26">
+        <v>88</v>
+      </c>
+      <c r="G13" s="27">
+        <v>61</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -13964,13 +14037,13 @@
         <v>222</v>
       </c>
       <c r="E15" s="25">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="26">
         <v>75</v>
       </c>
       <c r="G15" s="27">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -13985,17 +14058,17 @@
       <c r="C16" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="55" t="s">
         <v>245</v>
       </c>
       <c r="E16" s="25">
-        <v>15</v>
-      </c>
-      <c r="F16" s="26">
+        <v>14</v>
+      </c>
+      <c r="F16" s="56">
         <v>61</v>
       </c>
-      <c r="G16" s="27">
-        <v>46</v>
+      <c r="G16" s="57">
+        <v>47</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -14014,10 +14087,10 @@
         <v>140</v>
       </c>
       <c r="E17" s="25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" s="26">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G17" s="27">
         <v>54</v>
@@ -14064,10 +14137,10 @@
         <v>53</v>
       </c>
       <c r="E19" s="25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="26">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="27">
         <v>47</v>
@@ -14085,16 +14158,16 @@
       <c r="C20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="24" t="s">
         <v>243</v>
       </c>
       <c r="E20" s="25">
         <v>7</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="26">
         <v>53</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="27">
         <v>46</v>
       </c>
       <c r="H20" s="117"/>
@@ -16975,7 +17048,7 @@
       </c>
       <c r="O10">
         <f>COUNTIF(Stats!D:D,'Player Count'!N10)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="109"/>
     </row>
@@ -17191,7 +17264,7 @@
       </c>
       <c r="K17">
         <f>COUNTIF(Stats!D:D,'Player Count'!J17)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M17" s="109"/>
       <c r="N17" s="67" t="s">
@@ -17401,7 +17474,7 @@
       </c>
       <c r="C24">
         <f>COUNTIF(Stats!D:D,'Player Count'!B24)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
         <v>337</v>
@@ -17423,7 +17496,7 @@
       </c>
       <c r="O24">
         <f>COUNTIF(Stats!D:D,'Player Count'!N24)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="109"/>
     </row>
@@ -17465,7 +17538,7 @@
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
         <v>339</v>
@@ -17577,14 +17650,14 @@
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -17593,28 +17666,28 @@
       </c>
       <c r="C38" s="114">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.36065573770491804</v>
+        <v>0.3588709677419355</v>
       </c>
       <c r="D38" s="114"/>
       <c r="E38" s="114"/>
       <c r="F38" s="114"/>
       <c r="G38" s="114">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.26639344262295084</v>
+        <v>0.26209677419354838</v>
       </c>
       <c r="H38" s="114"/>
       <c r="I38" s="114"/>
       <c r="J38" s="114"/>
       <c r="K38" s="114">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.21721311475409835</v>
+        <v>0.21774193548387097</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114"/>
       <c r="N38" s="114"/>
       <c r="O38" s="114">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.15573770491803279</v>
+        <v>0.16129032258064516</v>
       </c>
     </row>
   </sheetData>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1588" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A70F053-0421-421B-9B6E-466BCB556639}"/>
+  <xr:revisionPtr revIDLastSave="1630" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F622B27-FA27-45B1-AFF7-3F76A6C49540}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3759,15 +3759,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3786,7 +3786,7 @@
         <v>284</v>
       </c>
       <c r="F6" s="21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="86">
         <v>46093</v>
@@ -3808,11 +3808,11 @@
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3839,11 +3839,11 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
@@ -3883,11 +3883,11 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
@@ -3925,15 +3925,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3971,15 +3971,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -4002,7 +4002,7 @@
         <v>284</v>
       </c>
       <c r="F11" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="87">
         <v>46009</v>
@@ -4024,11 +4024,11 @@
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -4069,11 +4069,11 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
@@ -4113,15 +4113,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4160,15 +4160,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -4209,11 +4209,11 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
@@ -4253,15 +4253,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4295,11 +4295,11 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
@@ -4346,15 +4346,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4406,7 +4406,7 @@
         <v>284</v>
       </c>
       <c r="F20" s="30">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G20" s="87">
         <v>45932</v>
@@ -4570,7 +4570,7 @@
         <v>284</v>
       </c>
       <c r="F25" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="87">
         <v>46023</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4785,7 +4785,7 @@
         <v>284</v>
       </c>
       <c r="F34" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" s="86">
         <v>46107</v>
@@ -5287,7 +5287,7 @@
         <v>284</v>
       </c>
       <c r="F51" s="30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G51" s="91">
         <v>46051</v>
@@ -5622,7 +5622,7 @@
         <v>5</v>
       </c>
       <c r="F66" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G66" s="83"/>
       <c r="H66" s="91"/>
@@ -5800,7 +5800,7 @@
         <v>284</v>
       </c>
       <c r="F72" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G72" s="87">
         <v>45897</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6507,7 +6507,7 @@
         <v>284</v>
       </c>
       <c r="F99" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G99" s="87">
         <v>46086</v>
@@ -6567,7 +6567,7 @@
         <v>284</v>
       </c>
       <c r="F101" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G101" s="87">
         <v>45918</v>
@@ -6718,7 +6718,7 @@
         <v>284</v>
       </c>
       <c r="F106" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G106" s="87">
         <v>46002</v>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6867,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -7013,7 +7013,7 @@
         <v>284</v>
       </c>
       <c r="F119" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" s="87">
         <v>46079</v>
@@ -7249,7 +7249,7 @@
         <v>284</v>
       </c>
       <c r="F127" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G127" s="87">
         <v>46023</v>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7634,7 +7634,7 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
@@ -8073,7 +8073,7 @@
         <v>25</v>
       </c>
       <c r="F157" s="30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G157" s="87"/>
       <c r="H157" s="91"/>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8340,7 +8340,7 @@
         <v>284</v>
       </c>
       <c r="F168" s="21">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G168" s="86">
         <v>46318</v>
@@ -8693,7 +8693,7 @@
         <v>284</v>
       </c>
       <c r="F181" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G181" s="91">
         <v>46023</v>
@@ -8722,7 +8722,7 @@
         <v>7</v>
       </c>
       <c r="F182" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G182" s="87"/>
       <c r="H182" s="91"/>
@@ -9338,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9665,7 +9665,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9974,7 +9974,7 @@
         <v>36</v>
       </c>
       <c r="F234" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G234" s="87"/>
       <c r="H234" s="91"/>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10362,7 +10362,7 @@
         <v>284</v>
       </c>
       <c r="F250" s="21">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G250" s="86">
         <v>46037</v>
@@ -10890,7 +10890,7 @@
         <v>284</v>
       </c>
       <c r="F268" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268" s="87">
         <v>46107</v>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11270,7 +11270,7 @@
         <v>284</v>
       </c>
       <c r="F284" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G284" s="87">
         <v>45876</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11730,7 +11730,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -11993,7 +11993,7 @@
         <v>54</v>
       </c>
       <c r="F313" s="30">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -12111,7 +12111,7 @@
         <v>284</v>
       </c>
       <c r="F317" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G317" s="87">
         <v>46093</v>
@@ -12262,7 +12262,7 @@
         <v>284</v>
       </c>
       <c r="F322" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G322" s="87">
         <v>45890</v>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12574,7 +12574,7 @@
         <v>284</v>
       </c>
       <c r="F336" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G336" s="87">
         <v>45995</v>
@@ -12755,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -13003,7 +13003,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -13046,7 +13046,7 @@
         <v>4</v>
       </c>
       <c r="F359" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
@@ -13299,7 +13299,7 @@
         <v>5</v>
       </c>
       <c r="F370" s="30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G370" s="103"/>
       <c r="H370" s="1"/>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -13837,13 +13837,13 @@
         <v>233</v>
       </c>
       <c r="E7" s="25">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7" s="56">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G7" s="57">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13856,19 +13856,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="25">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8" s="26">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G8" s="27">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13881,19 +13881,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>15</v>
+        <v>198</v>
       </c>
       <c r="E9" s="25">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F9" s="26">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G9" s="27">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13906,19 +13906,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>198</v>
+        <v>32</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>31</v>
       </c>
       <c r="E10" s="25">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" s="26">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G10" s="27">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13937,13 +13937,13 @@
         <v>203</v>
       </c>
       <c r="E11" s="25">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="26">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" s="27">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13965,10 +13965,10 @@
         <v>30</v>
       </c>
       <c r="F12" s="26">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G12" s="27">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13981,19 +13981,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>267</v>
+        <v>2</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>1</v>
       </c>
       <c r="E13" s="25">
-        <v>27</v>
-      </c>
-      <c r="F13" s="26">
-        <v>88</v>
-      </c>
-      <c r="G13" s="27">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F13" s="56">
+        <v>66</v>
+      </c>
+      <c r="G13" s="57">
+        <v>36</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -14006,19 +14006,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="E14" s="25">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F14" s="26">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G14" s="27">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -14031,19 +14031,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>244</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E15" s="25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="26">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G15" s="27">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -14056,19 +14056,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>244</v>
+        <v>117</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="E16" s="25">
         <v>14</v>
       </c>
-      <c r="F16" s="56">
-        <v>61</v>
-      </c>
-      <c r="G16" s="57">
-        <v>47</v>
+      <c r="F16" s="26">
+        <v>68</v>
+      </c>
+      <c r="G16" s="27">
+        <v>54</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -14081,19 +14081,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="E17" s="25">
         <v>13</v>
       </c>
-      <c r="F17" s="26">
-        <v>67</v>
-      </c>
-      <c r="G17" s="27">
-        <v>54</v>
+      <c r="F17" s="56">
+        <v>76</v>
+      </c>
+      <c r="G17" s="57">
+        <v>63</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -14108,17 +14108,17 @@
       <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="24" t="s">
         <v>34</v>
       </c>
       <c r="E18" s="25">
         <v>11</v>
       </c>
-      <c r="F18" s="56">
-        <v>58</v>
-      </c>
-      <c r="G18" s="57">
-        <v>47</v>
+      <c r="F18" s="26">
+        <v>60</v>
+      </c>
+      <c r="G18" s="27">
+        <v>49</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -14137,10 +14137,10 @@
         <v>53</v>
       </c>
       <c r="E19" s="25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="26">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" s="27">
         <v>47</v>
@@ -14162,10 +14162,10 @@
         <v>243</v>
       </c>
       <c r="E20" s="25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="26">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G20" s="27">
         <v>46</v>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1630" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F622B27-FA27-45B1-AFF7-3F76A6C49540}"/>
+  <xr:revisionPtr revIDLastSave="1669" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556B5891-80F8-40FE-A717-74A93E6B028E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3759,15 +3759,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3786,13 +3786,15 @@
         <v>284</v>
       </c>
       <c r="F6" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="86">
         <v>46093</v>
       </c>
       <c r="H6" s="84"/>
-      <c r="I6" s="81"/>
+      <c r="I6" s="81">
+        <v>1</v>
+      </c>
       <c r="J6" s="79"/>
       <c r="K6" s="23" t="str">
         <f>D29</f>
@@ -3808,11 +3810,11 @@
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3839,15 +3841,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3883,11 +3885,11 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
@@ -3925,11 +3927,11 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
@@ -3971,15 +3973,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -4069,7 +4071,7 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
@@ -4077,7 +4079,7 @@
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4095,13 +4097,15 @@
         <v>284</v>
       </c>
       <c r="F13" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="87">
         <v>45932</v>
       </c>
       <c r="H13" s="84"/>
-      <c r="I13" s="99"/>
+      <c r="I13" s="99">
+        <v>1</v>
+      </c>
       <c r="J13" s="82"/>
       <c r="K13" s="71" t="str">
         <f>D218</f>
@@ -4113,15 +4117,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4160,11 +4164,11 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
@@ -4209,11 +4213,11 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
@@ -4257,11 +4261,11 @@
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4295,11 +4299,11 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
@@ -4350,11 +4354,11 @@
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4406,13 +4410,15 @@
         <v>284</v>
       </c>
       <c r="F20" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" s="87">
         <v>45932</v>
       </c>
       <c r="H20" s="84"/>
-      <c r="I20" s="99"/>
+      <c r="I20" s="99">
+        <v>1</v>
+      </c>
       <c r="J20" s="76"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4598,7 +4604,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4785,7 +4791,7 @@
         <v>284</v>
       </c>
       <c r="F34" s="21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G34" s="86">
         <v>46107</v>
@@ -4927,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -5047,7 +5053,7 @@
         <v>284</v>
       </c>
       <c r="F43" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="87">
         <v>46107</v>
@@ -5287,7 +5293,7 @@
         <v>284</v>
       </c>
       <c r="F51" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G51" s="91">
         <v>46051</v>
@@ -5463,7 +5469,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -5918,7 +5924,7 @@
         <v>284</v>
       </c>
       <c r="F76" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" s="87">
         <v>46044</v>
@@ -6034,7 +6040,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6627,7 +6633,7 @@
         <v>284</v>
       </c>
       <c r="F103" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G103" s="87">
         <v>46079</v>
@@ -6743,7 +6749,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -7013,7 +7019,7 @@
         <v>284</v>
       </c>
       <c r="F119" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G119" s="87">
         <v>46079</v>
@@ -7427,7 +7433,7 @@
         <v>284</v>
       </c>
       <c r="F133" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G133" s="87">
         <v>45932</v>
@@ -7452,7 +7458,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7634,7 +7640,7 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
@@ -7717,7 +7723,7 @@
         <v>42</v>
       </c>
       <c r="F145" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G145" s="87"/>
       <c r="H145" s="91"/>
@@ -8162,7 +8168,7 @@
         <v>284</v>
       </c>
       <c r="F160" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G160" s="87">
         <v>46086</v>
@@ -8187,7 +8193,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -9020,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -9483,7 +9489,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9665,7 +9671,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9974,7 +9980,7 @@
         <v>36</v>
       </c>
       <c r="F234" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G234" s="87"/>
       <c r="H234" s="91"/>
@@ -10188,7 +10194,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10445,7 +10451,7 @@
         <v>1</v>
       </c>
       <c r="F253" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G253" s="83"/>
       <c r="H253" s="91"/>
@@ -10650,7 +10656,7 @@
         <v>18</v>
       </c>
       <c r="F260" s="30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -10708,13 +10714,15 @@
         <v>284</v>
       </c>
       <c r="F262" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G262" s="87">
         <v>45946</v>
       </c>
       <c r="H262" s="91"/>
-      <c r="I262" s="90"/>
+      <c r="I262" s="90">
+        <v>1</v>
+      </c>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
       <c r="L262" s="1"/>
@@ -10768,13 +10776,15 @@
         <v>284</v>
       </c>
       <c r="F264" s="30">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G264" s="87">
         <v>45953</v>
       </c>
       <c r="H264" s="91"/>
-      <c r="I264" s="90"/>
+      <c r="I264" s="90">
+        <v>2</v>
+      </c>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
       <c r="L264" s="1"/>
@@ -10915,7 +10925,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11270,7 +11280,7 @@
         <v>284</v>
       </c>
       <c r="F284" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G284" s="87">
         <v>45876</v>
@@ -11418,7 +11428,7 @@
         <v>284</v>
       </c>
       <c r="F290" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G290" s="87">
         <v>45946</v>
@@ -11548,7 +11558,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11730,7 +11740,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -12111,7 +12121,7 @@
         <v>284</v>
       </c>
       <c r="F317" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G317" s="87">
         <v>46093</v>
@@ -12755,7 +12765,7 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
@@ -12833,7 +12843,7 @@
         <v>1</v>
       </c>
       <c r="F346" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G346" s="83"/>
       <c r="H346" s="91"/>
@@ -12921,7 +12931,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -13003,7 +13013,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -13299,7 +13309,7 @@
         <v>5</v>
       </c>
       <c r="F370" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G370" s="103"/>
       <c r="H370" s="1"/>
@@ -13831,19 +13841,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>233</v>
+        <v>15</v>
       </c>
       <c r="E7" s="25">
-        <v>38</v>
-      </c>
-      <c r="F7" s="56">
-        <v>95</v>
-      </c>
-      <c r="G7" s="57">
-        <v>57</v>
+        <v>40</v>
+      </c>
+      <c r="F7" s="26">
+        <v>87</v>
+      </c>
+      <c r="G7" s="27">
+        <v>47</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13856,19 +13866,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>15</v>
+        <v>233</v>
       </c>
       <c r="E8" s="25">
         <v>38</v>
       </c>
       <c r="F8" s="26">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G8" s="27">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13881,19 +13891,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>198</v>
+        <v>32</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>31</v>
       </c>
       <c r="E9" s="25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" s="26">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="G9" s="27">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13906,19 +13916,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F10" s="26">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G10" s="27">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13937,10 +13947,10 @@
         <v>203</v>
       </c>
       <c r="E11" s="25">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11" s="26">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G11" s="27">
         <v>49</v>
@@ -13956,19 +13966,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>188</v>
+        <v>1</v>
       </c>
       <c r="E12" s="25">
-        <v>30</v>
-      </c>
-      <c r="F12" s="26">
-        <v>84</v>
-      </c>
-      <c r="G12" s="27">
-        <v>54</v>
+        <v>31</v>
+      </c>
+      <c r="F12" s="56">
+        <v>68</v>
+      </c>
+      <c r="G12" s="57">
+        <v>37</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13981,19 +13991,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>188</v>
       </c>
       <c r="E13" s="25">
         <v>30</v>
       </c>
-      <c r="F13" s="56">
-        <v>66</v>
-      </c>
-      <c r="G13" s="57">
-        <v>36</v>
+      <c r="F13" s="26">
+        <v>87</v>
+      </c>
+      <c r="G13" s="27">
+        <v>57</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -14012,13 +14022,13 @@
         <v>267</v>
       </c>
       <c r="E14" s="25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F14" s="26">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="27">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -14031,19 +14041,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>245</v>
+        <v>55</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>222</v>
       </c>
       <c r="E15" s="25">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F15" s="26">
+        <v>82</v>
+      </c>
+      <c r="G15" s="27">
         <v>63</v>
-      </c>
-      <c r="G15" s="27">
-        <v>48</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -14062,12 +14072,12 @@
         <v>140</v>
       </c>
       <c r="E16" s="25">
-        <v>14</v>
-      </c>
-      <c r="F16" s="26">
-        <v>68</v>
-      </c>
-      <c r="G16" s="27">
+        <v>16</v>
+      </c>
+      <c r="F16" s="56">
+        <v>70</v>
+      </c>
+      <c r="G16" s="57">
         <v>54</v>
       </c>
       <c r="H16" s="52"/>
@@ -14081,19 +14091,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="55" t="s">
-        <v>222</v>
+        <v>244</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>245</v>
       </c>
       <c r="E17" s="25">
-        <v>13</v>
-      </c>
-      <c r="F17" s="56">
-        <v>76</v>
-      </c>
-      <c r="G17" s="57">
-        <v>63</v>
+        <v>15</v>
+      </c>
+      <c r="F17" s="26">
+        <v>64</v>
+      </c>
+      <c r="G17" s="27">
+        <v>49</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -14108,16 +14118,16 @@
       <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E18" s="25">
         <v>11</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="56">
         <v>60</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="57">
         <v>49</v>
       </c>
       <c r="H18" s="52"/>
@@ -14131,19 +14141,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="E19" s="25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" s="26">
         <v>57</v>
       </c>
       <c r="G19" s="27">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -14156,19 +14166,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="E20" s="25">
         <v>9</v>
       </c>
       <c r="F20" s="26">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" s="27">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1669" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556B5891-80F8-40FE-A717-74A93E6B028E}"/>
+  <xr:revisionPtr revIDLastSave="1729" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8F773A2-655C-4A5F-9AFC-A78C2D41BB32}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="550">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -3763,11 +3763,11 @@
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3786,15 +3786,13 @@
         <v>284</v>
       </c>
       <c r="F6" s="21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" s="86">
         <v>46093</v>
       </c>
       <c r="H6" s="84"/>
-      <c r="I6" s="81">
-        <v>1</v>
-      </c>
+      <c r="I6" s="81"/>
       <c r="J6" s="79"/>
       <c r="K6" s="23" t="str">
         <f>D29</f>
@@ -3806,11 +3804,11 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
@@ -3841,15 +3839,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3889,11 +3887,11 @@
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3911,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="83"/>
       <c r="H9" s="75"/>
@@ -3927,15 +3925,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3973,15 +3971,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -4022,15 +4020,15 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -4071,11 +4069,11 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
@@ -4103,9 +4101,7 @@
         <v>45932</v>
       </c>
       <c r="H13" s="84"/>
-      <c r="I13" s="99">
-        <v>1</v>
-      </c>
+      <c r="I13" s="99"/>
       <c r="J13" s="82"/>
       <c r="K13" s="71" t="str">
         <f>D218</f>
@@ -4117,7 +4113,7 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
@@ -4125,7 +4121,7 @@
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4164,11 +4160,11 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
@@ -4213,7 +4209,7 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
@@ -4221,7 +4217,7 @@
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4257,15 +4253,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4303,11 +4299,11 @@
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R17" s="119"/>
       <c r="S17" s="119"/>
@@ -4354,11 +4350,11 @@
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4416,9 +4412,7 @@
         <v>45932</v>
       </c>
       <c r="H20" s="84"/>
-      <c r="I20" s="99">
-        <v>1</v>
-      </c>
+      <c r="I20" s="99"/>
       <c r="J20" s="76"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4576,7 +4570,7 @@
         <v>284</v>
       </c>
       <c r="F25" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="87">
         <v>46023</v>
@@ -4847,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="91"/>
       <c r="H36" s="91"/>
@@ -4933,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -5053,7 +5047,7 @@
         <v>284</v>
       </c>
       <c r="F43" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="87">
         <v>46107</v>
@@ -5082,7 +5076,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -5345,7 +5339,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5469,7 +5463,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -5924,7 +5918,7 @@
         <v>284</v>
       </c>
       <c r="F76" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G76" s="87">
         <v>46044</v>
@@ -6040,7 +6034,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6164,7 +6158,7 @@
         <v>8</v>
       </c>
       <c r="F86" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -6573,7 +6567,7 @@
         <v>284</v>
       </c>
       <c r="F101" s="30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G101" s="87">
         <v>45918</v>
@@ -6633,7 +6627,7 @@
         <v>284</v>
       </c>
       <c r="F103" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="87">
         <v>46079</v>
@@ -6873,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -7255,7 +7249,7 @@
         <v>284</v>
       </c>
       <c r="F127" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G127" s="87">
         <v>46023</v>
@@ -7458,7 +7452,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7640,7 +7634,7 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
@@ -7723,7 +7717,7 @@
         <v>42</v>
       </c>
       <c r="F145" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G145" s="87"/>
       <c r="H145" s="91"/>
@@ -7808,7 +7802,7 @@
         <v>284</v>
       </c>
       <c r="F148" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G148" s="87">
         <v>45974</v>
@@ -7868,7 +7862,7 @@
         <v>284</v>
       </c>
       <c r="F150" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G150" s="87">
         <v>46030</v>
@@ -7928,7 +7922,7 @@
         <v>284</v>
       </c>
       <c r="F152" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G152" s="87">
         <v>46072</v>
@@ -8050,7 +8044,7 @@
         <v>284</v>
       </c>
       <c r="F156" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" s="87">
         <v>46044</v>
@@ -8193,7 +8187,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8346,7 +8340,7 @@
         <v>284</v>
       </c>
       <c r="F168" s="21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G168" s="86">
         <v>46318</v>
@@ -8419,7 +8413,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G171" s="87"/>
       <c r="H171" s="91"/>
@@ -8581,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G177" s="91"/>
       <c r="H177" s="91"/>
@@ -8728,7 +8722,7 @@
         <v>7</v>
       </c>
       <c r="F182" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G182" s="87"/>
       <c r="H182" s="91"/>
@@ -8902,7 +8896,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -9158,7 +9152,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9344,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -9398,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="F210" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G210" s="87"/>
       <c r="H210" s="90"/>
@@ -9489,7 +9483,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9671,7 +9665,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -10194,7 +10188,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10569,7 +10563,7 @@
         <v>3</v>
       </c>
       <c r="F257" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G257" s="87"/>
       <c r="H257" s="91"/>
@@ -10656,7 +10650,7 @@
         <v>18</v>
       </c>
       <c r="F260" s="30">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -10925,7 +10919,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11078,7 +11072,7 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
@@ -11558,7 +11552,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11740,7 +11734,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -11914,7 +11908,7 @@
         <v>284</v>
       </c>
       <c r="F310" s="30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G310" s="87">
         <v>45911</v>
@@ -12003,7 +11997,7 @@
         <v>54</v>
       </c>
       <c r="F313" s="30">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -12061,7 +12055,7 @@
         <v>284</v>
       </c>
       <c r="F315" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G315" s="87">
         <v>45939</v>
@@ -12272,7 +12266,7 @@
         <v>284</v>
       </c>
       <c r="F322" s="30">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G322" s="87">
         <v>45890</v>
@@ -12297,7 +12291,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12421,7 +12415,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -12765,7 +12759,7 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G343" s="87"/>
       <c r="H343" s="91"/>
@@ -13013,7 +13007,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -13309,7 +13303,7 @@
         <v>5</v>
       </c>
       <c r="F370" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G370" s="103"/>
       <c r="H370" s="1"/>
@@ -13841,19 +13835,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>15</v>
+        <v>233</v>
       </c>
       <c r="E7" s="25">
-        <v>40</v>
-      </c>
-      <c r="F7" s="26">
-        <v>87</v>
-      </c>
-      <c r="G7" s="27">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="F7" s="56">
+        <v>102</v>
+      </c>
+      <c r="G7" s="57">
+        <v>60</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13866,19 +13860,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>233</v>
+        <v>32</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>31</v>
       </c>
       <c r="E8" s="25">
-        <v>38</v>
-      </c>
-      <c r="F8" s="26">
-        <v>96</v>
-      </c>
-      <c r="G8" s="27">
-        <v>58</v>
+        <v>40</v>
+      </c>
+      <c r="F8" s="56">
+        <v>100</v>
+      </c>
+      <c r="G8" s="57">
+        <v>60</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13891,19 +13885,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="25">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F9" s="26">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G9" s="27">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13918,17 +13912,17 @@
       <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="55" t="s">
         <v>198</v>
       </c>
       <c r="E10" s="25">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="26">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13941,19 +13935,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E11" s="25">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="26">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G11" s="27">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13966,19 +13960,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>203</v>
       </c>
       <c r="E12" s="25">
-        <v>31</v>
-      </c>
-      <c r="F12" s="56">
-        <v>68</v>
-      </c>
-      <c r="G12" s="57">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="F12" s="26">
+        <v>83</v>
+      </c>
+      <c r="G12" s="27">
+        <v>51</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13991,19 +13985,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>188</v>
+        <v>2</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>1</v>
       </c>
       <c r="E13" s="25">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" s="26">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="G13" s="27">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -14016,19 +14010,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>267</v>
+        <v>55</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>222</v>
       </c>
       <c r="E14" s="25">
-        <v>21</v>
-      </c>
-      <c r="F14" s="26">
-        <v>90</v>
-      </c>
-      <c r="G14" s="27">
-        <v>69</v>
+        <v>23</v>
+      </c>
+      <c r="F14" s="56">
+        <v>86</v>
+      </c>
+      <c r="G14" s="57">
+        <v>63</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -14041,19 +14035,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="E15" s="25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15" s="26">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G15" s="27">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -14066,19 +14060,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="55" t="s">
-        <v>140</v>
+        <v>244</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>245</v>
       </c>
       <c r="E16" s="25">
-        <v>16</v>
-      </c>
-      <c r="F16" s="56">
-        <v>70</v>
-      </c>
-      <c r="G16" s="57">
-        <v>54</v>
+        <v>15</v>
+      </c>
+      <c r="F16" s="26">
+        <v>65</v>
+      </c>
+      <c r="G16" s="27">
+        <v>50</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -14091,19 +14085,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>244</v>
+        <v>52</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="E17" s="25">
         <v>15</v>
       </c>
       <c r="F17" s="26">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G17" s="27">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -14118,17 +14112,17 @@
       <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="24" t="s">
         <v>34</v>
       </c>
       <c r="E18" s="25">
-        <v>11</v>
-      </c>
-      <c r="F18" s="56">
-        <v>60</v>
-      </c>
-      <c r="G18" s="57">
-        <v>49</v>
+        <v>13</v>
+      </c>
+      <c r="F18" s="26">
+        <v>63</v>
+      </c>
+      <c r="G18" s="27">
+        <v>50</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -14150,10 +14144,10 @@
         <v>11</v>
       </c>
       <c r="F19" s="26">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" s="27">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -14166,19 +14160,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="E20" s="25">
         <v>9</v>
       </c>
       <c r="F20" s="26">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G20" s="27">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>
@@ -14770,13 +14764,21 @@
       <c r="B31" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="C31" s="68"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="65" t="s">
+      <c r="C31" s="64">
+        <v>3</v>
+      </c>
+      <c r="D31" s="64" t="s">
+        <v>524</v>
+      </c>
+      <c r="E31" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="F31" s="69"/>
-      <c r="G31" s="100"/>
+      <c r="F31" s="100">
+        <v>1</v>
+      </c>
+      <c r="G31" s="100" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="40"/>
@@ -14798,7 +14800,9 @@
       <c r="K33" s="98"/>
     </row>
     <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="65"/>
+      <c r="B34" s="65" t="s">
+        <v>222</v>
+      </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1669" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556B5891-80F8-40FE-A717-74A93E6B028E}"/>
+  <xr:revisionPtr revIDLastSave="1857" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F244AF0-57D2-4F61-A39F-F4C178A5A21E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="550">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -3759,15 +3759,15 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="S5" s="102"/>
       <c r="T5" s="101"/>
@@ -3786,15 +3786,13 @@
         <v>284</v>
       </c>
       <c r="F6" s="21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" s="86">
         <v>46093</v>
       </c>
       <c r="H6" s="84"/>
-      <c r="I6" s="81">
-        <v>1</v>
-      </c>
+      <c r="I6" s="81"/>
       <c r="J6" s="79"/>
       <c r="K6" s="23" t="str">
         <f>D29</f>
@@ -3806,15 +3804,15 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S6" s="102"/>
       <c r="T6" s="101"/>
@@ -3841,15 +3839,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3885,15 +3883,15 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3911,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="83"/>
       <c r="H9" s="75"/>
@@ -3927,15 +3925,15 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3973,15 +3971,15 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="R10" s="119"/>
       <c r="S10" s="119"/>
@@ -4022,15 +4020,15 @@
       </c>
       <c r="M11" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N11" s="26">
         <f>SUM(F170:F187)</f>
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="O11" s="27">
         <f>SUM(F167:F169)</f>
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="S11" s="102"/>
       <c r="T11" s="101"/>
@@ -4071,15 +4069,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4103,9 +4101,7 @@
         <v>45932</v>
       </c>
       <c r="H13" s="84"/>
-      <c r="I13" s="99">
-        <v>1</v>
-      </c>
+      <c r="I13" s="99"/>
       <c r="J13" s="82"/>
       <c r="K13" s="71" t="str">
         <f>D218</f>
@@ -4117,15 +4113,15 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4148,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" s="87"/>
       <c r="H14" s="84"/>
@@ -4164,15 +4160,15 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="S14" s="102"/>
       <c r="T14" s="101"/>
@@ -4213,15 +4209,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4239,7 +4235,7 @@
         <v>284</v>
       </c>
       <c r="F16" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="84">
         <v>45897</v>
@@ -4257,15 +4253,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4283,7 +4279,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="84"/>
       <c r="H17" s="84"/>
@@ -4299,15 +4295,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="R17" s="119"/>
       <c r="S17" s="119"/>
@@ -4350,15 +4346,15 @@
       </c>
       <c r="M18" s="25">
         <f>N18-O18</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N18" s="26">
         <f>SUM(F359:F376)</f>
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="O18" s="27">
         <f>SUM(F356:F358)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S18" s="102"/>
       <c r="T18" s="101"/>
@@ -4410,15 +4406,13 @@
         <v>284</v>
       </c>
       <c r="F20" s="30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="87">
         <v>45932</v>
       </c>
       <c r="H20" s="84"/>
-      <c r="I20" s="99">
-        <v>1</v>
-      </c>
+      <c r="I20" s="99"/>
       <c r="J20" s="76"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -4480,7 +4474,7 @@
         <v>284</v>
       </c>
       <c r="F22" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="87">
         <v>46002</v>
@@ -4576,7 +4570,7 @@
         <v>284</v>
       </c>
       <c r="F25" s="30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="87">
         <v>46023</v>
@@ -4604,7 +4598,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4733,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="113">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G32" s="80" t="s">
         <v>285</v>
@@ -4762,7 +4756,7 @@
         <v>284</v>
       </c>
       <c r="F33" s="115">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33" s="86">
         <v>46072</v>
@@ -4791,7 +4785,7 @@
         <v>284</v>
       </c>
       <c r="F34" s="21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G34" s="86">
         <v>46107</v>
@@ -4820,7 +4814,7 @@
         <v>4</v>
       </c>
       <c r="F35" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G35" s="83"/>
       <c r="H35" s="91"/>
@@ -4847,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="91"/>
       <c r="H36" s="91"/>
@@ -4933,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="30">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -5053,7 +5047,7 @@
         <v>284</v>
       </c>
       <c r="F43" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="87">
         <v>46107</v>
@@ -5082,7 +5076,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -5322,7 +5316,7 @@
         <v>24</v>
       </c>
       <c r="F52" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G52" s="87"/>
       <c r="H52" s="91"/>
@@ -5345,7 +5339,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5469,7 +5463,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -5746,7 +5740,7 @@
         <v>284</v>
       </c>
       <c r="F70" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="87">
         <v>46058</v>
@@ -5924,7 +5918,7 @@
         <v>284</v>
       </c>
       <c r="F76" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G76" s="87">
         <v>46044</v>
@@ -6040,7 +6034,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6164,7 +6158,7 @@
         <v>8</v>
       </c>
       <c r="F86" s="15">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -6397,7 +6391,7 @@
         <v>19</v>
       </c>
       <c r="F95" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G95" s="91"/>
       <c r="H95" s="91"/>
@@ -6573,7 +6567,7 @@
         <v>284</v>
       </c>
       <c r="F101" s="30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G101" s="87">
         <v>45918</v>
@@ -6633,7 +6627,7 @@
         <v>284</v>
       </c>
       <c r="F103" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G103" s="87">
         <v>46079</v>
@@ -6749,7 +6743,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -6873,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="15">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G113" s="80"/>
       <c r="H113" s="94"/>
@@ -7048,7 +7042,7 @@
         <v>20</v>
       </c>
       <c r="F120" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G120" s="87"/>
       <c r="H120" s="91"/>
@@ -7106,7 +7100,7 @@
         <v>284</v>
       </c>
       <c r="F122" s="30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G122" s="87">
         <v>45974</v>
@@ -7255,7 +7249,7 @@
         <v>284</v>
       </c>
       <c r="F127" s="30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G127" s="87">
         <v>46023</v>
@@ -7375,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G131" s="87"/>
       <c r="H131" s="91"/>
@@ -7433,7 +7427,7 @@
         <v>284</v>
       </c>
       <c r="F133" s="30">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G133" s="87">
         <v>45932</v>
@@ -7458,7 +7452,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7640,7 +7634,7 @@
         <v>284</v>
       </c>
       <c r="F142" s="21">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G142" s="86">
         <v>45974</v>
@@ -7696,7 +7690,7 @@
         <v>1</v>
       </c>
       <c r="F144" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G144" s="83"/>
       <c r="H144" s="91"/>
@@ -7723,7 +7717,7 @@
         <v>42</v>
       </c>
       <c r="F145" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G145" s="87"/>
       <c r="H145" s="91"/>
@@ -7808,7 +7802,7 @@
         <v>284</v>
       </c>
       <c r="F148" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G148" s="87">
         <v>45974</v>
@@ -7868,7 +7862,7 @@
         <v>284</v>
       </c>
       <c r="F150" s="30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G150" s="87">
         <v>46030</v>
@@ -7928,7 +7922,7 @@
         <v>284</v>
       </c>
       <c r="F152" s="30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G152" s="87">
         <v>46072</v>
@@ -8050,7 +8044,7 @@
         <v>284</v>
       </c>
       <c r="F156" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" s="87">
         <v>46044</v>
@@ -8079,7 +8073,7 @@
         <v>25</v>
       </c>
       <c r="F157" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G157" s="87"/>
       <c r="H157" s="91"/>
@@ -8193,7 +8187,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -8346,7 +8340,7 @@
         <v>284</v>
       </c>
       <c r="F168" s="21">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G168" s="86">
         <v>46318</v>
@@ -8419,7 +8413,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G171" s="87"/>
       <c r="H171" s="91"/>
@@ -8552,7 +8546,7 @@
         <v>284</v>
       </c>
       <c r="F176" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G176" s="91">
         <v>45953</v>
@@ -8581,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G177" s="91"/>
       <c r="H177" s="91"/>
@@ -8728,7 +8722,7 @@
         <v>7</v>
       </c>
       <c r="F182" s="30">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G182" s="87"/>
       <c r="H182" s="91"/>
@@ -8786,7 +8780,7 @@
         <v>284</v>
       </c>
       <c r="F184" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G184" s="87">
         <v>45953</v>
@@ -8902,7 +8896,7 @@
       </c>
       <c r="F188" s="36">
         <f>SUM(F170:F187)-SUM(F167:F169)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G188" s="87"/>
       <c r="H188" s="91"/>
@@ -9026,7 +9020,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -9158,7 +9152,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9317,7 +9311,7 @@
         <v>1</v>
       </c>
       <c r="F207" s="30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G207" s="83"/>
       <c r="H207" s="90"/>
@@ -9344,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G208" s="83"/>
       <c r="H208" s="91"/>
@@ -9489,7 +9483,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9671,7 +9665,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9802,7 +9796,7 @@
         <v>284</v>
       </c>
       <c r="F228" s="30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G228" s="87">
         <v>45918</v>
@@ -9980,7 +9974,7 @@
         <v>36</v>
       </c>
       <c r="F234" s="30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G234" s="87"/>
       <c r="H234" s="91"/>
@@ -10034,7 +10028,7 @@
         <v>8</v>
       </c>
       <c r="F236" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G236" s="83"/>
       <c r="H236" s="91"/>
@@ -10194,7 +10188,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10368,7 +10362,7 @@
         <v>284</v>
       </c>
       <c r="F250" s="21">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G250" s="86">
         <v>46037</v>
@@ -10451,7 +10445,7 @@
         <v>1</v>
       </c>
       <c r="F253" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G253" s="83"/>
       <c r="H253" s="91"/>
@@ -10540,7 +10534,7 @@
         <v>284</v>
       </c>
       <c r="F256" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G256" s="87">
         <v>46030</v>
@@ -10569,7 +10563,7 @@
         <v>3</v>
       </c>
       <c r="F257" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G257" s="87"/>
       <c r="H257" s="91"/>
@@ -10627,7 +10621,7 @@
         <v>284</v>
       </c>
       <c r="F259" s="30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G259" s="87">
         <v>46107</v>
@@ -10656,7 +10650,7 @@
         <v>18</v>
       </c>
       <c r="F260" s="30">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -10714,7 +10708,7 @@
         <v>284</v>
       </c>
       <c r="F262" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G262" s="87">
         <v>45946</v>
@@ -10776,7 +10770,7 @@
         <v>284</v>
       </c>
       <c r="F264" s="30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G264" s="87">
         <v>45953</v>
@@ -10925,7 +10919,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11078,7 +11072,7 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
@@ -11222,7 +11216,7 @@
         <v>40</v>
       </c>
       <c r="F282" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G282" s="91"/>
       <c r="H282" s="91"/>
@@ -11280,7 +11274,7 @@
         <v>284</v>
       </c>
       <c r="F284" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G284" s="87">
         <v>45876</v>
@@ -11343,7 +11337,7 @@
         <v>12</v>
       </c>
       <c r="F287" s="30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G287" s="87"/>
       <c r="H287" s="91"/>
@@ -11428,7 +11422,7 @@
         <v>284</v>
       </c>
       <c r="F290" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G290" s="87">
         <v>45946</v>
@@ -11484,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="F292" s="30">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G292" s="87"/>
       <c r="H292" s="91"/>
@@ -11558,7 +11552,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11740,7 +11734,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -11854,7 +11848,7 @@
         <v>284</v>
       </c>
       <c r="F308" s="30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G308" s="87">
         <v>46002</v>
@@ -11914,7 +11908,7 @@
         <v>284</v>
       </c>
       <c r="F310" s="30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G310" s="87">
         <v>45911</v>
@@ -11974,7 +11968,7 @@
         <v>284</v>
       </c>
       <c r="F312" s="30">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G312" s="87">
         <v>45961</v>
@@ -12003,7 +11997,7 @@
         <v>54</v>
       </c>
       <c r="F313" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -12061,7 +12055,7 @@
         <v>284</v>
       </c>
       <c r="F315" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G315" s="87">
         <v>45939</v>
@@ -12121,7 +12115,7 @@
         <v>284</v>
       </c>
       <c r="F317" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G317" s="87">
         <v>46093</v>
@@ -12212,7 +12206,7 @@
         <v>284</v>
       </c>
       <c r="F320" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G320" s="87">
         <v>46051</v>
@@ -12272,7 +12266,7 @@
         <v>284</v>
       </c>
       <c r="F322" s="30">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G322" s="87">
         <v>45890</v>
@@ -12297,7 +12291,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12421,7 +12415,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -12482,7 +12476,7 @@
         <v>1</v>
       </c>
       <c r="F332" s="30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G332" s="83"/>
       <c r="H332" s="90"/>
@@ -12765,9 +12759,11 @@
         <v>1</v>
       </c>
       <c r="F343" s="30">
-        <v>13</v>
-      </c>
-      <c r="G343" s="87"/>
+        <v>16</v>
+      </c>
+      <c r="G343" s="87">
+        <v>46072</v>
+      </c>
       <c r="H343" s="91"/>
       <c r="I343" s="90"/>
       <c r="J343" s="1"/>
@@ -12843,7 +12839,7 @@
         <v>1</v>
       </c>
       <c r="F346" s="30">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G346" s="83"/>
       <c r="H346" s="91"/>
@@ -12931,7 +12927,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -13013,7 +13009,7 @@
         <v>5</v>
       </c>
       <c r="F356" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G356" s="1"/>
       <c r="H356" s="103"/>
@@ -13056,7 +13052,7 @@
         <v>4</v>
       </c>
       <c r="F359" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G359" s="1"/>
       <c r="H359" s="1"/>
@@ -13098,7 +13094,7 @@
         <v>32</v>
       </c>
       <c r="F361" s="30">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G361" s="1"/>
       <c r="H361" s="1"/>
@@ -13169,7 +13165,7 @@
         <v>284</v>
       </c>
       <c r="F364" s="30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G364" s="103">
         <v>46086</v>
@@ -13309,7 +13305,7 @@
         <v>5</v>
       </c>
       <c r="F370" s="30">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G370" s="103"/>
       <c r="H370" s="1"/>
@@ -13380,7 +13376,7 @@
         <v>284</v>
       </c>
       <c r="F373" s="30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G373" s="103">
         <v>46086</v>
@@ -13453,7 +13449,7 @@
         <v>284</v>
       </c>
       <c r="F376" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G376" s="103">
         <v>45939</v>
@@ -13472,7 +13468,7 @@
       </c>
       <c r="F377" s="36">
         <f>SUM(F359:F376)-SUM(F356:F358)</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G377" s="1"/>
       <c r="H377" s="1"/>
@@ -13841,19 +13837,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="55" t="s">
-        <v>15</v>
+        <v>98</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>233</v>
       </c>
       <c r="E7" s="25">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F7" s="26">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="G7" s="27">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13866,19 +13862,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>233</v>
+        <v>51</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>203</v>
       </c>
       <c r="E8" s="25">
-        <v>38</v>
-      </c>
-      <c r="F8" s="26">
-        <v>96</v>
-      </c>
-      <c r="G8" s="27">
-        <v>58</v>
+        <v>40</v>
+      </c>
+      <c r="F8" s="56">
+        <v>93</v>
+      </c>
+      <c r="G8" s="57">
+        <v>53</v>
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="41"/>
@@ -13891,19 +13887,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="25">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F9" s="26">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G9" s="27">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13916,19 +13912,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>198</v>
+        <v>31</v>
       </c>
       <c r="E10" s="25">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="26">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="G10" s="27">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H10" s="117"/>
       <c r="I10" s="41"/>
@@ -13941,19 +13937,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>203</v>
+        <v>1</v>
       </c>
       <c r="E11" s="25">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" s="26">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G11" s="27">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H11" s="117"/>
       <c r="I11" s="41"/>
@@ -13966,19 +13962,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>188</v>
       </c>
       <c r="E12" s="25">
-        <v>31</v>
-      </c>
-      <c r="F12" s="56">
-        <v>68</v>
-      </c>
-      <c r="G12" s="57">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="F12" s="26">
+        <v>97</v>
+      </c>
+      <c r="G12" s="27">
+        <v>63</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13991,19 +13987,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E13" s="25">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F13" s="26">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" s="27">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -14016,19 +14012,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>267</v>
+        <v>55</v>
+      </c>
+      <c r="D14" s="55" t="s">
+        <v>222</v>
       </c>
       <c r="E14" s="25">
-        <v>21</v>
-      </c>
-      <c r="F14" s="26">
-        <v>90</v>
-      </c>
-      <c r="G14" s="27">
-        <v>69</v>
+        <v>29</v>
+      </c>
+      <c r="F14" s="56">
+        <v>94</v>
+      </c>
+      <c r="G14" s="57">
+        <v>65</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -14041,19 +14037,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="E15" s="25">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F15" s="26">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G15" s="27">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
@@ -14066,19 +14062,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>244</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>140</v>
+        <v>245</v>
       </c>
       <c r="E16" s="25">
-        <v>16</v>
-      </c>
-      <c r="F16" s="56">
-        <v>70</v>
-      </c>
-      <c r="G16" s="57">
-        <v>54</v>
+        <v>22</v>
+      </c>
+      <c r="F16" s="26">
+        <v>73</v>
+      </c>
+      <c r="G16" s="27">
+        <v>51</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="41"/>
@@ -14091,19 +14087,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="E17" s="25">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="26">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G17" s="27">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="41"/>
@@ -14113,22 +14109,22 @@
     <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47"/>
       <c r="B18" s="54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="E18" s="25">
-        <v>11</v>
-      </c>
-      <c r="F18" s="56">
-        <v>60</v>
-      </c>
-      <c r="G18" s="57">
-        <v>49</v>
+        <v>13</v>
+      </c>
+      <c r="F18" s="26">
+        <v>75</v>
+      </c>
+      <c r="G18" s="27">
+        <v>62</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -14143,17 +14139,17 @@
       <c r="C19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="55" t="s">
         <v>243</v>
       </c>
       <c r="E19" s="25">
-        <v>11</v>
-      </c>
-      <c r="F19" s="26">
-        <v>57</v>
-      </c>
-      <c r="G19" s="27">
-        <v>46</v>
+        <v>13</v>
+      </c>
+      <c r="F19" s="56">
+        <v>64</v>
+      </c>
+      <c r="G19" s="57">
+        <v>51</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -14172,13 +14168,13 @@
         <v>53</v>
       </c>
       <c r="E20" s="25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" s="26">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G20" s="27">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>
@@ -14770,13 +14766,21 @@
       <c r="B31" s="65" t="s">
         <v>222</v>
       </c>
-      <c r="C31" s="68"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="65" t="s">
+      <c r="C31" s="64">
+        <v>3</v>
+      </c>
+      <c r="D31" s="64" t="s">
+        <v>524</v>
+      </c>
+      <c r="E31" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="F31" s="69"/>
-      <c r="G31" s="100"/>
+      <c r="F31" s="100">
+        <v>1</v>
+      </c>
+      <c r="G31" s="100" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="40"/>
@@ -14798,7 +14802,9 @@
       <c r="K33" s="98"/>
     </row>
     <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="65"/>
+      <c r="B34" s="65" t="s">
+        <v>222</v>
+      </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1857" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F244AF0-57D2-4F61-A39F-F4C178A5A21E}"/>
+  <xr:revisionPtr revIDLastSave="1910" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAF966E6-A44A-4451-95BC-120138AC407E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId1"/>
-    <sheet name="Stats" sheetId="2" r:id="rId2"/>
-    <sheet name="Table" sheetId="3" r:id="rId3"/>
-    <sheet name="Cup" sheetId="4" r:id="rId4"/>
-    <sheet name="BFL Challenge" sheetId="6" r:id="rId5"/>
-    <sheet name="Player Count" sheetId="7" r:id="rId6"/>
+    <sheet name="Stats" sheetId="2" r:id="rId1"/>
+    <sheet name="Table" sheetId="3" r:id="rId2"/>
+    <sheet name="Cup" sheetId="4" r:id="rId3"/>
+    <sheet name="BFL Challenge" sheetId="6" r:id="rId4"/>
+    <sheet name="Player Count" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Table!$C$6:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Table!$C$6:$G$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3589,19 +3588,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B0B01F-0D2B-4847-9C61-79B0D773C0FB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <customProperties>
-    <customPr name="_pios_id" r:id="rId1"/>
-    <customPr name="EpmWorksheetKeyString_GUID" r:id="rId2"/>
-  </customProperties>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:IX404"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.4" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3759,11 +3745,11 @@
       </c>
       <c r="M5" s="18">
         <f t="shared" ref="M5:M17" si="0">N5-O5</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N5" s="19">
         <f>SUM(F8:F25)</f>
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O5" s="20">
         <f>SUM(F5:F7)</f>
@@ -3804,11 +3790,11 @@
       </c>
       <c r="M6" s="25">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="N6" s="26">
         <f>SUM(F35:F52)</f>
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="O6" s="27">
         <f>SUM(F32:F34)</f>
@@ -3839,15 +3825,15 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
@@ -3883,7 +3869,7 @@
       </c>
       <c r="M8" s="25">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N8" s="26">
         <f>SUM(F89:F106)</f>
@@ -3891,7 +3877,7 @@
       </c>
       <c r="O8" s="27">
         <f>SUM(F86:F88)</f>
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3925,11 +3911,11 @@
       </c>
       <c r="M9" s="25">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N9" s="73">
         <f>SUM(F116:F133)</f>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O9" s="74">
         <f>SUM(F113:F115)</f>
@@ -3971,11 +3957,11 @@
       </c>
       <c r="M10" s="25">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N10" s="26">
         <f>SUM(F143:F160)</f>
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O10" s="27">
         <f>SUM(F140:F142)</f>
@@ -4069,15 +4055,15 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4113,11 +4099,11 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
@@ -4160,11 +4146,11 @@
       </c>
       <c r="M14" s="25">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N14" s="73">
         <f>SUM(F251:F268)</f>
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="O14" s="74">
         <f>SUM(F248:F250)</f>
@@ -4209,15 +4195,15 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4253,15 +4239,15 @@
       </c>
       <c r="M16" s="25">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N16" s="26">
         <f>SUM(F305:F322)</f>
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(F302:F304)</f>
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4295,15 +4281,15 @@
       </c>
       <c r="M17" s="25">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N17" s="26">
         <f>SUM(F332:F349)</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O17" s="27">
         <f>SUM(F329:F331)</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R17" s="119"/>
       <c r="S17" s="119"/>
@@ -4570,7 +4556,7 @@
         <v>284</v>
       </c>
       <c r="F25" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="87">
         <v>46023</v>
@@ -4598,7 +4584,7 @@
       </c>
       <c r="F26" s="36">
         <f>SUM(F8:F25)-SUM(F5:F7)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G26" s="80"/>
       <c r="H26" s="92"/>
@@ -4841,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G36" s="91"/>
       <c r="H36" s="91"/>
@@ -4868,7 +4854,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="83"/>
       <c r="H37" s="91"/>
@@ -4895,7 +4881,7 @@
         <v>12</v>
       </c>
       <c r="F38" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38" s="87"/>
       <c r="H38" s="91"/>
@@ -4927,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G39" s="87"/>
       <c r="H39" s="91"/>
@@ -5076,7 +5062,7 @@
         <v>12</v>
       </c>
       <c r="F44" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G44" s="87"/>
       <c r="H44" s="91"/>
@@ -5316,7 +5302,7 @@
         <v>24</v>
       </c>
       <c r="F52" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G52" s="87"/>
       <c r="H52" s="91"/>
@@ -5339,7 +5325,7 @@
       </c>
       <c r="F53" s="36">
         <f>SUM(F35:F52)-SUM(F32:F34)</f>
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G53" s="80"/>
       <c r="H53" s="92"/>
@@ -5463,7 +5449,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -5595,7 +5581,7 @@
         <v>30</v>
       </c>
       <c r="F65" s="30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G65" s="83"/>
       <c r="H65" s="90"/>
@@ -5622,7 +5608,7 @@
         <v>5</v>
       </c>
       <c r="F66" s="30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G66" s="83"/>
       <c r="H66" s="91"/>
@@ -5680,7 +5666,7 @@
         <v>284</v>
       </c>
       <c r="F68" s="30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G68" s="91">
         <v>45904</v>
@@ -5918,7 +5904,7 @@
         <v>284</v>
       </c>
       <c r="F76" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G76" s="87">
         <v>46044</v>
@@ -6034,7 +6020,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6158,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="F86" s="15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G86" s="80"/>
       <c r="H86" s="94"/>
@@ -6743,7 +6729,7 @@
       </c>
       <c r="F107" s="36">
         <f>SUM(F89:F106)-SUM(F86:F88)</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G107" s="80"/>
       <c r="H107" s="92"/>
@@ -7013,7 +6999,7 @@
         <v>284</v>
       </c>
       <c r="F119" s="30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G119" s="87">
         <v>46079</v>
@@ -7427,7 +7413,7 @@
         <v>284</v>
       </c>
       <c r="F133" s="30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G133" s="87">
         <v>45932</v>
@@ -7452,7 +7438,7 @@
       </c>
       <c r="F134" s="36">
         <f>SUM(F116:F133)-SUM(F113:F115)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G134" s="80"/>
       <c r="H134" s="92"/>
@@ -7802,7 +7788,7 @@
         <v>284</v>
       </c>
       <c r="F148" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G148" s="87">
         <v>45974</v>
@@ -8187,7 +8173,7 @@
       </c>
       <c r="F161" s="36">
         <f>SUM(F143:F160)-SUM(F140:F142)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G161" s="80"/>
       <c r="H161" s="92"/>
@@ -9020,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -9152,7 +9138,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="30">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G200" s="83"/>
       <c r="H200" s="90"/>
@@ -9483,7 +9469,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -10146,7 +10132,7 @@
         <v>284</v>
       </c>
       <c r="F240" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G240" s="87">
         <v>45911</v>
@@ -10188,7 +10174,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10650,7 +10636,7 @@
         <v>18</v>
       </c>
       <c r="F260" s="30">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G260" s="87"/>
       <c r="H260" s="91"/>
@@ -10714,9 +10700,7 @@
         <v>45946</v>
       </c>
       <c r="H262" s="91"/>
-      <c r="I262" s="90">
-        <v>1</v>
-      </c>
+      <c r="I262" s="90"/>
       <c r="J262" s="1"/>
       <c r="K262" s="1"/>
       <c r="L262" s="1"/>
@@ -10776,9 +10760,7 @@
         <v>45953</v>
       </c>
       <c r="H264" s="91"/>
-      <c r="I264" s="90">
-        <v>2</v>
-      </c>
+      <c r="I264" s="90"/>
       <c r="J264" s="1"/>
       <c r="K264" s="1"/>
       <c r="L264" s="1"/>
@@ -10919,7 +10901,7 @@
       </c>
       <c r="F269" s="36">
         <f>SUM(F251:F268)-SUM(F248:F250)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G269" s="80"/>
       <c r="H269" s="92"/>
@@ -11072,7 +11054,7 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
@@ -11189,7 +11171,7 @@
         <v>25</v>
       </c>
       <c r="F281" s="30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G281" s="83"/>
       <c r="H281" s="91"/>
@@ -11337,7 +11319,7 @@
         <v>12</v>
       </c>
       <c r="F287" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G287" s="87"/>
       <c r="H287" s="91"/>
@@ -11552,7 +11534,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11734,7 +11716,7 @@
         <v>284</v>
       </c>
       <c r="F304" s="21">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G304" s="87">
         <v>45953</v>
@@ -11763,7 +11745,7 @@
         <v>2</v>
       </c>
       <c r="F305" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G305" s="83"/>
       <c r="H305" s="91"/>
@@ -11908,7 +11890,7 @@
         <v>284</v>
       </c>
       <c r="F310" s="30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G310" s="87">
         <v>45911</v>
@@ -11997,7 +11979,7 @@
         <v>54</v>
       </c>
       <c r="F313" s="30">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G313" s="87"/>
       <c r="H313" s="91"/>
@@ -12115,7 +12097,7 @@
         <v>284</v>
       </c>
       <c r="F317" s="30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G317" s="87">
         <v>46093</v>
@@ -12266,7 +12248,7 @@
         <v>284</v>
       </c>
       <c r="F322" s="30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G322" s="87">
         <v>45890</v>
@@ -12291,7 +12273,7 @@
       </c>
       <c r="F323" s="36">
         <f>SUM(F305:F322)-SUM(F302:F304)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G323" s="80"/>
       <c r="H323" s="92"/>
@@ -12415,7 +12397,7 @@
         <v>1</v>
       </c>
       <c r="F329" s="15">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G329" s="83"/>
       <c r="H329" s="87"/>
@@ -12638,7 +12620,7 @@
         <v>284</v>
       </c>
       <c r="F338" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G338" s="87">
         <v>46072</v>
@@ -12927,7 +12909,7 @@
       </c>
       <c r="F350" s="36">
         <f>SUM(F332:F349)-SUM(F329:F331)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G350" s="83"/>
       <c r="H350" s="90"/>
@@ -13716,7 +13698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -13839,17 +13821,17 @@
       <c r="C7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="55" t="s">
         <v>233</v>
       </c>
       <c r="E7" s="25">
-        <v>54</v>
-      </c>
-      <c r="F7" s="26">
-        <v>117</v>
-      </c>
-      <c r="G7" s="27">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="F7" s="56">
+        <v>123</v>
+      </c>
+      <c r="G7" s="57">
+        <v>66</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="41"/>
@@ -13864,16 +13846,16 @@
       <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="24" t="s">
         <v>203</v>
       </c>
       <c r="E8" s="25">
-        <v>40</v>
-      </c>
-      <c r="F8" s="56">
-        <v>93</v>
-      </c>
-      <c r="G8" s="57">
+        <v>42</v>
+      </c>
+      <c r="F8" s="26">
+        <v>95</v>
+      </c>
+      <c r="G8" s="27">
         <v>53</v>
       </c>
       <c r="H8" s="52"/>
@@ -13887,19 +13869,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="E9" s="25">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F9" s="26">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="G9" s="27">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H9" s="52"/>
       <c r="I9" s="41"/>
@@ -13918,10 +13900,10 @@
         <v>31</v>
       </c>
       <c r="E10" s="25">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10" s="26">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G10" s="27">
         <v>68</v>
@@ -13939,14 +13921,14 @@
       <c r="C11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="55" t="s">
         <v>1</v>
       </c>
       <c r="E11" s="25">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" s="26">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="27">
         <v>42</v>
@@ -13962,19 +13944,19 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>188</v>
+        <v>15</v>
       </c>
       <c r="E12" s="25">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="26">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G12" s="27">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H12" s="52"/>
       <c r="I12" s="41"/>
@@ -13987,19 +13969,19 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="E13" s="25">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F13" s="26">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="G13" s="27">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H13" s="117"/>
       <c r="I13" s="41"/>
@@ -14012,19 +13994,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="E14" s="25">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F14" s="56">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G14" s="57">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
@@ -14043,10 +14025,10 @@
         <v>267</v>
       </c>
       <c r="E15" s="25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="26">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G15" s="27">
         <v>73</v>
@@ -14070,10 +14052,10 @@
       <c r="E16" s="25">
         <v>22</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="56">
         <v>73</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="57">
         <v>51</v>
       </c>
       <c r="H16" s="52"/>
@@ -14089,7 +14071,7 @@
       <c r="C17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="55" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="25">
@@ -14114,17 +14096,17 @@
       <c r="C18" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="24" t="s">
         <v>140</v>
       </c>
       <c r="E18" s="25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="26">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G18" s="27">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
@@ -14139,17 +14121,17 @@
       <c r="C19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="24" t="s">
         <v>243</v>
       </c>
       <c r="E19" s="25">
-        <v>13</v>
-      </c>
-      <c r="F19" s="56">
-        <v>64</v>
-      </c>
-      <c r="G19" s="57">
-        <v>51</v>
+        <v>11</v>
+      </c>
+      <c r="F19" s="26">
+        <v>65</v>
+      </c>
+      <c r="G19" s="27">
+        <v>54</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="41"/>
@@ -14168,13 +14150,13 @@
         <v>53</v>
       </c>
       <c r="E20" s="25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F20" s="26">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G20" s="27">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>
@@ -14225,7 +14207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IW34"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -14824,7 +14806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA85496-96FC-4E57-B88C-D037E5ADD8C6}">
   <dimension ref="A1:X71"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
@@ -16871,7 +16853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5616AB3-C7B1-4511-93B2-51A6298AD44C}">
   <dimension ref="A5:Q38"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\80010008\git\dreamleague\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1910" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAF966E6-A44A-4451-95BC-120138AC407E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF4598B-47B9-4EE7-8DD7-5378FEB61E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25017" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -3590,30 +3590,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:IX404"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.296875" style="77" customWidth="1"/>
+    <col min="1" max="1" width="1.28515625" style="77" customWidth="1"/>
     <col min="2" max="2" width="16" style="77" customWidth="1"/>
-    <col min="3" max="3" width="39.296875" style="77" customWidth="1"/>
-    <col min="4" max="4" width="32.796875" style="77" customWidth="1"/>
-    <col min="5" max="5" width="11.796875" style="77" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="77" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="77" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="77" customWidth="1"/>
     <col min="6" max="6" width="17" style="77" customWidth="1"/>
-    <col min="7" max="8" width="11.296875" style="77" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.69921875" style="77" customWidth="1"/>
-    <col min="10" max="10" width="7.09765625" style="77" customWidth="1"/>
-    <col min="11" max="11" width="25.69921875" style="77" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.296875" style="77" customWidth="1"/>
+    <col min="7" max="8" width="11.28515625" style="77" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" style="77" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" style="77" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" style="77" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.28515625" style="77" customWidth="1"/>
     <col min="13" max="14" width="12" style="77" customWidth="1"/>
-    <col min="15" max="15" width="10.296875" style="77" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" style="77" customWidth="1"/>
     <col min="16" max="17" width="9" style="77" customWidth="1"/>
-    <col min="18" max="18" width="32.296875" style="77" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.28515625" style="77" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="9" style="77" customWidth="1"/>
-    <col min="22" max="22" width="30.09765625" style="77" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.140625" style="77" bestFit="1" customWidth="1"/>
     <col min="23" max="258" width="9" style="77" customWidth="1"/>
     <col min="259" max="16384" width="9" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3632,7 +3632,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
@@ -3653,7 +3653,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3670,7 +3670,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="79"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
@@ -3712,7 +3712,7 @@
       <c r="U4" s="119"/>
       <c r="V4" s="119"/>
     </row>
-    <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>13</v>
@@ -3759,7 +3759,7 @@
       <c r="T5" s="101"/>
       <c r="U5" s="102"/>
     </row>
-    <row r="6" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="79"/>
       <c r="B6" s="21" t="s">
         <v>13</v>
@@ -3804,7 +3804,7 @@
       <c r="T6" s="101"/>
       <c r="U6" s="102"/>
     </row>
-    <row r="7" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="79"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -3839,7 +3839,7 @@
       <c r="T7" s="101"/>
       <c r="U7" s="102"/>
     </row>
-    <row r="8" spans="1:22" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="12.45" x14ac:dyDescent="0.2">
       <c r="A8" s="79"/>
       <c r="B8" s="28" t="s">
         <v>14</v>
@@ -3880,7 +3880,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="79"/>
       <c r="B9" s="28" t="s">
         <v>14</v>
@@ -3922,7 +3922,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="79"/>
       <c r="B10" s="106" t="s">
         <v>16</v>
@@ -3973,7 +3973,7 @@
       <c r="U10" s="119"/>
       <c r="V10" s="119"/>
     </row>
-    <row r="11" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="79"/>
       <c r="B11" s="28" t="s">
         <v>16</v>
@@ -4020,7 +4020,7 @@
       <c r="T11" s="101"/>
       <c r="U11" s="102"/>
     </row>
-    <row r="12" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="79"/>
       <c r="B12" s="106" t="s">
         <v>16</v>
@@ -4066,7 +4066,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="79"/>
       <c r="B13" s="28" t="s">
         <v>16</v>
@@ -4115,7 +4115,7 @@
       <c r="U13" s="119"/>
       <c r="V13" s="119"/>
     </row>
-    <row r="14" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="79"/>
       <c r="B14" s="28" t="s">
         <v>16</v>
@@ -4160,7 +4160,7 @@
       <c r="T14" s="101"/>
       <c r="U14" s="102"/>
     </row>
-    <row r="15" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="79"/>
       <c r="B15" s="106" t="s">
         <v>17</v>
@@ -4206,7 +4206,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="79"/>
       <c r="B16" s="28" t="s">
         <v>17</v>
@@ -4250,7 +4250,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="79"/>
       <c r="B17" s="28" t="s">
         <v>17</v>
@@ -4297,7 +4297,7 @@
       <c r="U17" s="119"/>
       <c r="V17" s="119"/>
     </row>
-    <row r="18" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="79"/>
       <c r="B18" s="106" t="s">
         <v>17</v>
@@ -4346,7 +4346,7 @@
       <c r="T18" s="101"/>
       <c r="U18" s="102"/>
     </row>
-    <row r="19" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="79"/>
       <c r="B19" s="106" t="s">
         <v>17</v>
@@ -4377,7 +4377,7 @@
       <c r="N19" s="88"/>
       <c r="O19" s="88"/>
     </row>
-    <row r="20" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="79"/>
       <c r="B20" s="28" t="s">
         <v>17</v>
@@ -4411,7 +4411,7 @@
       <c r="U20" s="119"/>
       <c r="V20" s="119"/>
     </row>
-    <row r="21" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="79"/>
       <c r="B21" s="106" t="s">
         <v>17</v>
@@ -4445,7 +4445,7 @@
       <c r="T21" s="101"/>
       <c r="U21" s="102"/>
     </row>
-    <row r="22" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="79"/>
       <c r="B22" s="28" t="s">
         <v>17</v>
@@ -4474,7 +4474,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="79"/>
       <c r="B23" s="106" t="s">
         <v>17</v>
@@ -4505,7 +4505,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="79"/>
       <c r="B24" s="106" t="s">
         <v>17</v>
@@ -4541,7 +4541,7 @@
       <c r="U24" s="119"/>
       <c r="V24" s="119"/>
     </row>
-    <row r="25" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="79"/>
       <c r="B25" s="28" t="s">
         <v>17</v>
@@ -4573,7 +4573,7 @@
       <c r="T25" s="101"/>
       <c r="U25" s="102"/>
     </row>
-    <row r="26" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
@@ -4596,7 +4596,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4613,7 +4613,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4635,7 +4635,7 @@
       <c r="U28" s="119"/>
       <c r="V28" s="119"/>
     </row>
-    <row r="29" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
@@ -4656,7 +4656,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -4673,7 +4673,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="79"/>
       <c r="B31" s="6" t="s">
         <v>3</v>
@@ -4700,7 +4700,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="79"/>
       <c r="B32" s="115" t="s">
         <v>13</v>
@@ -4729,7 +4729,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="79"/>
       <c r="B33" s="115" t="s">
         <v>13</v>
@@ -4758,7 +4758,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="79"/>
       <c r="B34" s="28" t="s">
         <v>13</v>
@@ -4785,7 +4785,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="79"/>
       <c r="B35" s="28" t="s">
         <v>14</v>
@@ -4812,7 +4812,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="79"/>
       <c r="B36" s="28" t="s">
         <v>14</v>
@@ -4839,7 +4839,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="79"/>
       <c r="B37" s="28" t="s">
         <v>16</v>
@@ -4866,7 +4866,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="79"/>
       <c r="B38" s="28" t="s">
         <v>16</v>
@@ -4898,7 +4898,7 @@
       <c r="U38" s="119"/>
       <c r="V38" s="119"/>
     </row>
-    <row r="39" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="79"/>
       <c r="B39" s="28" t="s">
         <v>16</v>
@@ -4925,7 +4925,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="79"/>
       <c r="B40" s="106" t="s">
         <v>17</v>
@@ -4956,7 +4956,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="79"/>
       <c r="B41" s="106" t="s">
         <v>17</v>
@@ -4987,7 +4987,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="79"/>
       <c r="B42" s="106" t="s">
         <v>17</v>
@@ -5018,7 +5018,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="79"/>
       <c r="B43" s="28" t="s">
         <v>17</v>
@@ -5047,7 +5047,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="79"/>
       <c r="B44" s="28" t="s">
         <v>17</v>
@@ -5074,7 +5074,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="79"/>
       <c r="B45" s="106" t="s">
         <v>17</v>
@@ -5105,7 +5105,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="79"/>
       <c r="B46" s="106" t="s">
         <v>17</v>
@@ -5136,7 +5136,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="79"/>
       <c r="B47" s="106" t="s">
         <v>17</v>
@@ -5167,7 +5167,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="79"/>
       <c r="B48" s="28" t="s">
         <v>17</v>
@@ -5196,7 +5196,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="79"/>
       <c r="B49" s="106" t="s">
         <v>17</v>
@@ -5227,7 +5227,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="79"/>
       <c r="B50" s="106" t="s">
         <v>17</v>
@@ -5258,7 +5258,7 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="79"/>
       <c r="B51" s="28" t="s">
         <v>17</v>
@@ -5287,7 +5287,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="79"/>
       <c r="B52" s="28" t="s">
         <v>17</v>
@@ -5314,7 +5314,7 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="33"/>
       <c r="C53" s="33"/>
@@ -5337,7 +5337,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -5354,7 +5354,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5371,7 +5371,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
@@ -5392,7 +5392,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5409,7 +5409,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="79"/>
       <c r="B58" s="6" t="s">
         <v>3</v>
@@ -5436,7 +5436,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="79"/>
       <c r="B59" s="12" t="s">
         <v>13</v>
@@ -5461,7 +5461,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="79"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -5478,7 +5478,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="79"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -5495,7 +5495,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="79"/>
       <c r="B62" s="28" t="s">
         <v>14</v>
@@ -5522,7 +5522,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="79"/>
       <c r="B63" s="28" t="s">
         <v>14</v>
@@ -5549,7 +5549,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="79"/>
       <c r="B64" s="28"/>
       <c r="C64" s="28"/>
@@ -5566,7 +5566,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="79"/>
       <c r="B65" s="28" t="s">
         <v>16</v>
@@ -5593,7 +5593,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="79"/>
       <c r="B66" s="28" t="s">
         <v>16</v>
@@ -5620,7 +5620,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="79"/>
       <c r="B67" s="106" t="s">
         <v>16</v>
@@ -5651,7 +5651,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="79"/>
       <c r="B68" s="28" t="s">
         <v>16</v>
@@ -5680,7 +5680,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="79"/>
       <c r="B69" s="106" t="s">
         <v>17</v>
@@ -5711,7 +5711,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="79"/>
       <c r="B70" s="28" t="s">
         <v>17</v>
@@ -5740,7 +5740,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="79"/>
       <c r="B71" s="106" t="s">
         <v>17</v>
@@ -5771,7 +5771,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="79"/>
       <c r="B72" s="28" t="s">
         <v>17</v>
@@ -5800,7 +5800,7 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="79"/>
       <c r="B73" s="28" t="s">
         <v>17</v>
@@ -5827,7 +5827,7 @@
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
-    <row r="74" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="79"/>
       <c r="B74" s="106" t="s">
         <v>17</v>
@@ -5858,7 +5858,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="79"/>
       <c r="B75" s="106" t="s">
         <v>17</v>
@@ -5889,7 +5889,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="79"/>
       <c r="B76" s="28" t="s">
         <v>17</v>
@@ -5918,7 +5918,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
     </row>
-    <row r="77" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="79"/>
       <c r="B77" s="106" t="s">
         <v>17</v>
@@ -5949,7 +5949,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
     </row>
-    <row r="78" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="79"/>
       <c r="B78" s="106" t="s">
         <v>17</v>
@@ -5980,7 +5980,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="79"/>
       <c r="B79" s="28" t="s">
         <v>17</v>
@@ -6009,7 +6009,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="33"/>
       <c r="C80" s="33"/>
@@ -6032,7 +6032,7 @@
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6049,7 +6049,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="82" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6066,7 +6066,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="3" t="s">
@@ -6087,7 +6087,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
     </row>
-    <row r="84" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -6104,7 +6104,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="79"/>
       <c r="B85" s="6" t="s">
         <v>3</v>
@@ -6131,7 +6131,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="79"/>
       <c r="B86" s="12" t="s">
         <v>13</v>
@@ -6156,7 +6156,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
     </row>
-    <row r="87" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="79"/>
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
@@ -6173,7 +6173,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="79"/>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
@@ -6190,7 +6190,7 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="79"/>
       <c r="B89" s="28" t="s">
         <v>14</v>
@@ -6217,7 +6217,7 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="79"/>
       <c r="B90" s="28" t="s">
         <v>14</v>
@@ -6244,7 +6244,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="79"/>
       <c r="B91" s="28" t="s">
         <v>16</v>
@@ -6271,7 +6271,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="79"/>
       <c r="B92" s="106" t="s">
         <v>16</v>
@@ -6302,7 +6302,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
     </row>
-    <row r="93" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="79"/>
       <c r="B93" s="106" t="s">
         <v>16</v>
@@ -6333,7 +6333,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="79"/>
       <c r="B94" s="28" t="s">
         <v>16</v>
@@ -6362,7 +6362,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="79"/>
       <c r="B95" s="28" t="s">
         <v>16</v>
@@ -6389,7 +6389,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="79"/>
       <c r="B96" s="28" t="s">
         <v>17</v>
@@ -6416,7 +6416,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="79"/>
       <c r="B97" s="106" t="s">
         <v>17</v>
@@ -6447,7 +6447,7 @@
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="79"/>
       <c r="B98" s="106" t="s">
         <v>17</v>
@@ -6478,7 +6478,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="79"/>
       <c r="B99" s="28" t="s">
         <v>17</v>
@@ -6507,7 +6507,7 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="79"/>
       <c r="B100" s="106" t="s">
         <v>17</v>
@@ -6538,7 +6538,7 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
-    <row r="101" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="79"/>
       <c r="B101" s="28" t="s">
         <v>17</v>
@@ -6567,7 +6567,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="79"/>
       <c r="B102" s="106" t="s">
         <v>17</v>
@@ -6598,7 +6598,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="79"/>
       <c r="B103" s="28" t="s">
         <v>17</v>
@@ -6627,7 +6627,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
-    <row r="104" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="79"/>
       <c r="B104" s="106" t="s">
         <v>17</v>
@@ -6658,7 +6658,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="79"/>
       <c r="B105" s="106" t="s">
         <v>17</v>
@@ -6689,7 +6689,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="79"/>
       <c r="B106" s="28" t="s">
         <v>17</v>
@@ -6718,7 +6718,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="33"/>
       <c r="C107" s="33"/>
@@ -6741,7 +6741,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
-    <row r="108" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -6758,7 +6758,7 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
-    <row r="109" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -6775,7 +6775,7 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
@@ -6796,7 +6796,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
-    <row r="111" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -6813,7 +6813,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
-    <row r="112" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="79"/>
       <c r="B112" s="6" t="s">
         <v>3</v>
@@ -6840,7 +6840,7 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
-    <row r="113" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="79"/>
       <c r="B113" s="12" t="s">
         <v>13</v>
@@ -6865,7 +6865,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="79"/>
       <c r="B114" s="21"/>
       <c r="C114" s="21"/>
@@ -6882,7 +6882,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="79"/>
       <c r="B115" s="21"/>
       <c r="C115" s="21"/>
@@ -6899,7 +6899,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="79"/>
       <c r="B116" s="28" t="s">
         <v>14</v>
@@ -6926,7 +6926,7 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
-    <row r="117" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="79"/>
       <c r="B117" s="28" t="s">
         <v>14</v>
@@ -6953,7 +6953,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
-    <row r="118" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="79"/>
       <c r="B118" s="106" t="s">
         <v>16</v>
@@ -6984,7 +6984,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
-    <row r="119" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="79"/>
       <c r="B119" s="28" t="s">
         <v>16</v>
@@ -7013,7 +7013,7 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
-    <row r="120" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="79"/>
       <c r="B120" s="28" t="s">
         <v>16</v>
@@ -7040,7 +7040,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
     </row>
-    <row r="121" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="79"/>
       <c r="B121" s="106" t="s">
         <v>16</v>
@@ -7071,7 +7071,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
-    <row r="122" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="79"/>
       <c r="B122" s="28" t="s">
         <v>16</v>
@@ -7100,7 +7100,7 @@
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
-    <row r="123" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="79"/>
       <c r="B123" s="28" t="s">
         <v>17</v>
@@ -7127,7 +7127,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
-    <row r="124" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="79"/>
       <c r="B124" s="106" t="s">
         <v>17</v>
@@ -7158,7 +7158,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
-    <row r="125" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="79"/>
       <c r="B125" s="106" t="s">
         <v>17</v>
@@ -7189,7 +7189,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
-    <row r="126" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="79"/>
       <c r="B126" s="106" t="s">
         <v>17</v>
@@ -7220,7 +7220,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="79"/>
       <c r="B127" s="28" t="s">
         <v>17</v>
@@ -7249,7 +7249,7 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
-    <row r="128" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="79"/>
       <c r="B128" s="106" t="s">
         <v>17</v>
@@ -7280,7 +7280,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
-    <row r="129" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="79"/>
       <c r="B129" s="106" t="s">
         <v>17</v>
@@ -7311,7 +7311,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
-    <row r="130" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="79"/>
       <c r="B130" s="28" t="s">
         <v>17</v>
@@ -7340,7 +7340,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
-    <row r="131" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="79"/>
       <c r="B131" s="28" t="s">
         <v>17</v>
@@ -7367,7 +7367,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
-    <row r="132" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="79"/>
       <c r="B132" s="106" t="s">
         <v>17</v>
@@ -7398,7 +7398,7 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
     </row>
-    <row r="133" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="79"/>
       <c r="B133" s="28" t="s">
         <v>17</v>
@@ -7427,7 +7427,7 @@
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
     </row>
-    <row r="134" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="33"/>
       <c r="C134" s="33"/>
@@ -7450,7 +7450,7 @@
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
     </row>
-    <row r="135" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -7467,7 +7467,7 @@
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
     </row>
-    <row r="136" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -7484,7 +7484,7 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
     </row>
-    <row r="137" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="3" t="s">
@@ -7505,7 +7505,7 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
     </row>
-    <row r="138" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -7522,7 +7522,7 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
     </row>
-    <row r="139" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="79"/>
       <c r="B139" s="6" t="s">
         <v>3</v>
@@ -7549,7 +7549,7 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="79"/>
       <c r="B140" s="110" t="s">
         <v>13</v>
@@ -7578,7 +7578,7 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
     </row>
-    <row r="141" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="79"/>
       <c r="B141" s="115" t="s">
         <v>13</v>
@@ -7607,7 +7607,7 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
     </row>
-    <row r="142" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="79"/>
       <c r="B142" s="21" t="s">
         <v>13</v>
@@ -7634,7 +7634,7 @@
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
     </row>
-    <row r="143" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="79"/>
       <c r="B143" s="28" t="s">
         <v>14</v>
@@ -7661,7 +7661,7 @@
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
     </row>
-    <row r="144" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="79"/>
       <c r="B144" s="28" t="s">
         <v>14</v>
@@ -7688,7 +7688,7 @@
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
     </row>
-    <row r="145" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="79"/>
       <c r="B145" s="28" t="s">
         <v>16</v>
@@ -7715,7 +7715,7 @@
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
     </row>
-    <row r="146" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="79"/>
       <c r="B146" s="28" t="s">
         <v>16</v>
@@ -7742,7 +7742,7 @@
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
     </row>
-    <row r="147" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="79"/>
       <c r="B147" s="106" t="s">
         <v>16</v>
@@ -7773,7 +7773,7 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
     </row>
-    <row r="148" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="79"/>
       <c r="B148" s="28" t="s">
         <v>16</v>
@@ -7802,7 +7802,7 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
     </row>
-    <row r="149" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="79"/>
       <c r="B149" s="106" t="s">
         <v>17</v>
@@ -7833,7 +7833,7 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
     </row>
-    <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="79"/>
       <c r="B150" s="28" t="s">
         <v>17</v>
@@ -7862,7 +7862,7 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
     </row>
-    <row r="151" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="79"/>
       <c r="B151" s="106" t="s">
         <v>17</v>
@@ -7893,7 +7893,7 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
     </row>
-    <row r="152" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="79"/>
       <c r="B152" s="28" t="s">
         <v>17</v>
@@ -7922,7 +7922,7 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
     </row>
-    <row r="153" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="79"/>
       <c r="B153" s="106" t="s">
         <v>17</v>
@@ -7953,7 +7953,7 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
     </row>
-    <row r="154" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="79"/>
       <c r="B154" s="106" t="s">
         <v>17</v>
@@ -7984,7 +7984,7 @@
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
     </row>
-    <row r="155" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="79"/>
       <c r="B155" s="106" t="s">
         <v>17</v>
@@ -8015,7 +8015,7 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
     </row>
-    <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="79"/>
       <c r="B156" s="28" t="s">
         <v>17</v>
@@ -8044,7 +8044,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
     </row>
-    <row r="157" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="79"/>
       <c r="B157" s="28" t="s">
         <v>17</v>
@@ -8071,7 +8071,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
     </row>
-    <row r="158" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="79"/>
       <c r="B158" s="106" t="s">
         <v>17</v>
@@ -8102,7 +8102,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
     </row>
-    <row r="159" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="79"/>
       <c r="B159" s="106" t="s">
         <v>17</v>
@@ -8133,7 +8133,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
     </row>
-    <row r="160" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="79"/>
       <c r="B160" s="28" t="s">
         <v>17</v>
@@ -8162,7 +8162,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
     </row>
-    <row r="161" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="33"/>
       <c r="C161" s="33"/>
@@ -8185,7 +8185,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
     </row>
-    <row r="162" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -8202,7 +8202,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
     </row>
-    <row r="163" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -8219,7 +8219,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
     </row>
-    <row r="164" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="3" t="s">
@@ -8240,7 +8240,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
     </row>
-    <row r="165" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -8257,7 +8257,7 @@
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
     </row>
-    <row r="166" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A166" s="79"/>
       <c r="B166" s="6" t="s">
         <v>3</v>
@@ -8284,7 +8284,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
     </row>
-    <row r="167" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A167" s="79"/>
       <c r="B167" s="110" t="s">
         <v>13</v>
@@ -8313,7 +8313,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
     </row>
-    <row r="168" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="79"/>
       <c r="B168" s="12" t="s">
         <v>13</v>
@@ -8340,7 +8340,7 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
     </row>
-    <row r="169" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="79"/>
       <c r="B169" s="21"/>
       <c r="C169" s="21"/>
@@ -8357,7 +8357,7 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
     </row>
-    <row r="170" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="79"/>
       <c r="B170" s="28" t="s">
         <v>14</v>
@@ -8384,7 +8384,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
     </row>
-    <row r="171" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="79"/>
       <c r="B171" s="28" t="s">
         <v>14</v>
@@ -8411,7 +8411,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
     </row>
-    <row r="172" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="79"/>
       <c r="B172" s="28"/>
       <c r="C172" s="28"/>
@@ -8428,7 +8428,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
     </row>
-    <row r="173" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="79"/>
       <c r="B173" s="28" t="s">
         <v>16</v>
@@ -8455,7 +8455,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
     </row>
-    <row r="174" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="79"/>
       <c r="B174" s="106" t="s">
         <v>16</v>
@@ -8486,7 +8486,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
     </row>
-    <row r="175" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="79"/>
       <c r="B175" s="106" t="s">
         <v>16</v>
@@ -8517,7 +8517,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
     </row>
-    <row r="176" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="79"/>
       <c r="B176" s="28" t="s">
         <v>16</v>
@@ -8546,7 +8546,7 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
     </row>
-    <row r="177" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="79"/>
       <c r="B177" s="28" t="s">
         <v>16</v>
@@ -8573,7 +8573,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
     </row>
-    <row r="178" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="79"/>
       <c r="B178" s="106" t="s">
         <v>17</v>
@@ -8604,7 +8604,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
     </row>
-    <row r="179" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="79"/>
       <c r="B179" s="106" t="s">
         <v>17</v>
@@ -8635,7 +8635,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
     </row>
-    <row r="180" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="79"/>
       <c r="B180" s="28" t="s">
         <v>17</v>
@@ -8664,7 +8664,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
     </row>
-    <row r="181" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="79"/>
       <c r="B181" s="28" t="s">
         <v>17</v>
@@ -8693,7 +8693,7 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
     </row>
-    <row r="182" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="79"/>
       <c r="B182" s="28" t="s">
         <v>17</v>
@@ -8720,7 +8720,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
     </row>
-    <row r="183" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="79"/>
       <c r="B183" s="106" t="s">
         <v>17</v>
@@ -8751,7 +8751,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
     </row>
-    <row r="184" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="79"/>
       <c r="B184" s="28" t="s">
         <v>17</v>
@@ -8780,7 +8780,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="79"/>
       <c r="B185" s="106" t="s">
         <v>17</v>
@@ -8811,7 +8811,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
     </row>
-    <row r="186" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="79"/>
       <c r="B186" s="106" t="s">
         <v>17</v>
@@ -8842,7 +8842,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
     </row>
-    <row r="187" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A187" s="79"/>
       <c r="B187" s="28" t="s">
         <v>17</v>
@@ -8871,7 +8871,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="33"/>
       <c r="C188" s="33"/>
@@ -8894,7 +8894,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
     </row>
-    <row r="189" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8911,7 +8911,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
     </row>
-    <row r="190" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8928,7 +8928,7 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
@@ -8949,7 +8949,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -8966,7 +8966,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A193" s="79"/>
       <c r="B193" s="6" t="s">
         <v>3</v>
@@ -8993,7 +8993,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="79"/>
       <c r="B194" s="12" t="s">
         <v>13</v>
@@ -9018,7 +9018,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="79"/>
       <c r="B195" s="21"/>
       <c r="C195" s="21"/>
@@ -9035,7 +9035,7 @@
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
     </row>
-    <row r="196" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="79"/>
       <c r="B196" s="21"/>
       <c r="C196" s="21"/>
@@ -9052,7 +9052,7 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
     </row>
-    <row r="197" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="79"/>
       <c r="B197" s="28" t="s">
         <v>14</v>
@@ -9079,7 +9079,7 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
     </row>
-    <row r="198" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="79"/>
       <c r="B198" s="28" t="s">
         <v>14</v>
@@ -9106,7 +9106,7 @@
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
     </row>
-    <row r="199" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="79"/>
       <c r="B199" s="28"/>
       <c r="C199" s="28"/>
@@ -9123,7 +9123,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="79"/>
       <c r="B200" s="28" t="s">
         <v>16</v>
@@ -9150,7 +9150,7 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="79"/>
       <c r="B201" s="28" t="s">
         <v>16</v>
@@ -9177,7 +9177,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
     </row>
-    <row r="202" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="79"/>
       <c r="B202" s="28" t="s">
         <v>16</v>
@@ -9204,7 +9204,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
     </row>
-    <row r="203" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="79"/>
       <c r="B203" s="28"/>
       <c r="C203" s="28"/>
@@ -9221,7 +9221,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="79"/>
       <c r="B204" s="28"/>
       <c r="C204" s="28"/>
@@ -9238,7 +9238,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
     </row>
-    <row r="205" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="79"/>
       <c r="B205" s="28"/>
       <c r="C205" s="28"/>
@@ -9255,7 +9255,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
     </row>
-    <row r="206" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="79"/>
       <c r="B206" s="28" t="s">
         <v>17</v>
@@ -9282,7 +9282,7 @@
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
     </row>
-    <row r="207" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="79"/>
       <c r="B207" s="28" t="s">
         <v>17</v>
@@ -9309,7 +9309,7 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
     </row>
-    <row r="208" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="79"/>
       <c r="B208" s="28" t="s">
         <v>17</v>
@@ -9336,7 +9336,7 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
     </row>
-    <row r="209" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="79"/>
       <c r="B209" s="28" t="s">
         <v>17</v>
@@ -9363,7 +9363,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="79"/>
       <c r="B210" s="28" t="s">
         <v>17</v>
@@ -9390,7 +9390,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
     </row>
-    <row r="211" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="79"/>
       <c r="B211" s="28"/>
       <c r="C211" s="28"/>
@@ -9407,7 +9407,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
     </row>
-    <row r="212" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="79"/>
       <c r="B212" s="28"/>
       <c r="C212" s="28"/>
@@ -9424,7 +9424,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
     </row>
-    <row r="213" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="79"/>
       <c r="B213" s="28"/>
       <c r="C213" s="28"/>
@@ -9441,7 +9441,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A214" s="79"/>
       <c r="B214" s="28"/>
       <c r="C214" s="28"/>
@@ -9458,7 +9458,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="33"/>
       <c r="C215" s="33"/>
@@ -9481,7 +9481,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9498,7 +9498,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9515,7 +9515,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="3" t="s">
@@ -9536,7 +9536,7 @@
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -9553,7 +9553,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A220" s="79"/>
       <c r="B220" s="6" t="s">
         <v>3</v>
@@ -9580,7 +9580,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="58"/>
       <c r="B221" s="110" t="s">
         <v>13</v>
@@ -9609,7 +9609,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="79"/>
       <c r="B222" s="115" t="s">
         <v>13</v>
@@ -9638,7 +9638,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
-    <row r="223" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="79"/>
       <c r="B223" s="21" t="s">
         <v>13</v>
@@ -9665,7 +9665,7 @@
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
     </row>
-    <row r="224" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="79"/>
       <c r="B224" s="28" t="s">
         <v>14</v>
@@ -9692,7 +9692,7 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
     </row>
-    <row r="225" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="79"/>
       <c r="B225" s="28" t="s">
         <v>14</v>
@@ -9719,7 +9719,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
     </row>
-    <row r="226" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="79"/>
       <c r="B226" s="28"/>
       <c r="C226" s="28"/>
@@ -9736,7 +9736,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
     </row>
-    <row r="227" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="79"/>
       <c r="B227" s="106" t="s">
         <v>16</v>
@@ -9767,7 +9767,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="79"/>
       <c r="B228" s="28" t="s">
         <v>16</v>
@@ -9796,7 +9796,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
     </row>
-    <row r="229" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="79"/>
       <c r="B229" s="28" t="s">
         <v>16</v>
@@ -9823,7 +9823,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
     </row>
-    <row r="230" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="79"/>
       <c r="B230" s="106" t="s">
         <v>16</v>
@@ -9854,7 +9854,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
-    <row r="231" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="79"/>
       <c r="B231" s="106" t="s">
         <v>16</v>
@@ -9885,7 +9885,7 @@
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
-    <row r="232" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="79"/>
       <c r="B232" s="106" t="s">
         <v>16</v>
@@ -9916,7 +9916,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
-    <row r="233" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="79"/>
       <c r="B233" s="28" t="s">
         <v>16</v>
@@ -9945,7 +9945,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
-    <row r="234" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="79"/>
       <c r="B234" s="28" t="s">
         <v>17</v>
@@ -9972,7 +9972,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
-    <row r="235" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="79"/>
       <c r="B235" s="28" t="s">
         <v>17</v>
@@ -9999,7 +9999,7 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
-    <row r="236" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="79"/>
       <c r="B236" s="28" t="s">
         <v>17</v>
@@ -10026,7 +10026,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
-    <row r="237" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="79"/>
       <c r="B237" s="106" t="s">
         <v>17</v>
@@ -10057,7 +10057,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
-    <row r="238" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="79"/>
       <c r="B238" s="28" t="s">
         <v>17</v>
@@ -10086,7 +10086,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
-    <row r="239" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="79"/>
       <c r="B239" s="106" t="s">
         <v>17</v>
@@ -10117,7 +10117,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
-    <row r="240" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="79"/>
       <c r="B240" s="28" t="s">
         <v>17</v>
@@ -10146,7 +10146,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
-    <row r="241" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A241" s="79"/>
       <c r="B241" s="28"/>
       <c r="C241" s="28"/>
@@ -10163,7 +10163,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
-    <row r="242" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="33"/>
       <c r="C242" s="33"/>
@@ -10186,7 +10186,7 @@
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
-    <row r="243" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -10203,7 +10203,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
-    <row r="244" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" ht="13.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -10220,7 +10220,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
-    <row r="245" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="3" t="s">
@@ -10241,7 +10241,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
-    <row r="246" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -10258,7 +10258,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
-    <row r="247" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A247" s="79"/>
       <c r="B247" s="6" t="s">
         <v>3</v>
@@ -10277,7 +10277,7 @@
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
-    <row r="248" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="79"/>
       <c r="B248" s="110" t="s">
         <v>13</v>
@@ -10306,7 +10306,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
-    <row r="249" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="79"/>
       <c r="B249" s="115" t="s">
         <v>13</v>
@@ -10335,7 +10335,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
-    <row r="250" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="79"/>
       <c r="B250" s="21" t="s">
         <v>13</v>
@@ -10362,7 +10362,7 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
-    <row r="251" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="79"/>
       <c r="B251" s="28" t="s">
         <v>14</v>
@@ -10389,7 +10389,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
-    <row r="252" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="79"/>
       <c r="B252" s="28" t="s">
         <v>14</v>
@@ -10416,7 +10416,7 @@
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
-    <row r="253" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="79"/>
       <c r="B253" s="28" t="s">
         <v>16</v>
@@ -10443,7 +10443,7 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
-    <row r="254" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="79"/>
       <c r="B254" s="106" t="s">
         <v>16</v>
@@ -10474,7 +10474,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
-    <row r="255" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="79"/>
       <c r="B255" s="106" t="s">
         <v>16</v>
@@ -10505,7 +10505,7 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
     </row>
-    <row r="256" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="79"/>
       <c r="B256" s="28" t="s">
         <v>16</v>
@@ -10534,7 +10534,7 @@
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
     </row>
-    <row r="257" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="79"/>
       <c r="B257" s="28" t="s">
         <v>16</v>
@@ -10561,7 +10561,7 @@
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
     </row>
-    <row r="258" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="79"/>
       <c r="B258" s="106" t="s">
         <v>17</v>
@@ -10592,7 +10592,7 @@
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
     </row>
-    <row r="259" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="79"/>
       <c r="B259" s="28" t="s">
         <v>17</v>
@@ -10621,7 +10621,7 @@
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
     </row>
-    <row r="260" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="79"/>
       <c r="B260" s="28" t="s">
         <v>17</v>
@@ -10648,7 +10648,7 @@
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
     </row>
-    <row r="261" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="79"/>
       <c r="B261" s="106" t="s">
         <v>17</v>
@@ -10679,7 +10679,7 @@
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
     </row>
-    <row r="262" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="79"/>
       <c r="B262" s="28" t="s">
         <v>17</v>
@@ -10708,7 +10708,7 @@
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
     </row>
-    <row r="263" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="79"/>
       <c r="B263" s="106" t="s">
         <v>17</v>
@@ -10739,7 +10739,7 @@
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
     </row>
-    <row r="264" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="79"/>
       <c r="B264" s="28" t="s">
         <v>17</v>
@@ -10768,7 +10768,7 @@
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
     </row>
-    <row r="265" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="79"/>
       <c r="B265" s="106" t="s">
         <v>17</v>
@@ -10799,7 +10799,7 @@
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
     </row>
-    <row r="266" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="79"/>
       <c r="B266" s="106" t="s">
         <v>17</v>
@@ -10830,7 +10830,7 @@
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
     </row>
-    <row r="267" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="79"/>
       <c r="B267" s="106" t="s">
         <v>17</v>
@@ -10861,7 +10861,7 @@
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
     </row>
-    <row r="268" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A268" s="79"/>
       <c r="B268" s="28" t="s">
         <v>17</v>
@@ -10890,7 +10890,7 @@
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
     </row>
-    <row r="269" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="33"/>
       <c r="C269" s="33"/>
@@ -10913,7 +10913,7 @@
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
     </row>
-    <row r="270" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -10930,7 +10930,7 @@
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
     </row>
-    <row r="271" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -10947,7 +10947,7 @@
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
     </row>
-    <row r="272" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1" t="s">
@@ -10968,7 +10968,7 @@
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
     </row>
-    <row r="273" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -10985,7 +10985,7 @@
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
     </row>
-    <row r="274" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A274" s="79"/>
       <c r="B274" s="6" t="s">
         <v>3</v>
@@ -11012,7 +11012,7 @@
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
     </row>
-    <row r="275" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A275" s="79"/>
       <c r="B275" s="110" t="s">
         <v>13</v>
@@ -11041,7 +11041,7 @@
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
     </row>
-    <row r="276" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="79"/>
       <c r="B276" s="12" t="s">
         <v>13</v>
@@ -11068,7 +11068,7 @@
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
     </row>
-    <row r="277" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="79"/>
       <c r="B277" s="21"/>
       <c r="C277" s="21"/>
@@ -11085,7 +11085,7 @@
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
     </row>
-    <row r="278" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="79"/>
       <c r="B278" s="28" t="s">
         <v>14</v>
@@ -11112,7 +11112,7 @@
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
     </row>
-    <row r="279" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="79"/>
       <c r="B279" s="28" t="s">
         <v>14</v>
@@ -11139,7 +11139,7 @@
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
     </row>
-    <row r="280" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="79"/>
       <c r="B280" s="28"/>
       <c r="C280" s="28"/>
@@ -11156,7 +11156,7 @@
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
     </row>
-    <row r="281" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="79"/>
       <c r="B281" s="28" t="s">
         <v>16</v>
@@ -11183,7 +11183,7 @@
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
     </row>
-    <row r="282" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="79"/>
       <c r="B282" s="28" t="s">
         <v>16</v>
@@ -11210,7 +11210,7 @@
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
     </row>
-    <row r="283" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="79"/>
       <c r="B283" s="106" t="s">
         <v>16</v>
@@ -11241,7 +11241,7 @@
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
     </row>
-    <row r="284" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="79"/>
       <c r="B284" s="28" t="s">
         <v>16</v>
@@ -11270,7 +11270,7 @@
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
     </row>
-    <row r="285" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="79"/>
       <c r="B285" s="28"/>
       <c r="C285" s="28"/>
@@ -11287,7 +11287,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
-    <row r="286" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="79"/>
       <c r="B286" s="28"/>
       <c r="C286" s="28"/>
@@ -11304,7 +11304,7 @@
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
-    <row r="287" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="79"/>
       <c r="B287" s="28" t="s">
         <v>17</v>
@@ -11331,7 +11331,7 @@
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
-    <row r="288" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="79"/>
       <c r="B288" s="28" t="s">
         <v>17</v>
@@ -11358,7 +11358,7 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
-    <row r="289" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="79"/>
       <c r="B289" s="106" t="s">
         <v>17</v>
@@ -11389,7 +11389,7 @@
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
-    <row r="290" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="79"/>
       <c r="B290" s="28" t="s">
         <v>17</v>
@@ -11418,7 +11418,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
-    <row r="291" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="79"/>
       <c r="B291" s="28" t="s">
         <v>17</v>
@@ -11445,7 +11445,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
-    <row r="292" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="79"/>
       <c r="B292" s="28" t="s">
         <v>17</v>
@@ -11472,7 +11472,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
-    <row r="293" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="79"/>
       <c r="B293" s="28"/>
       <c r="C293" s="28"/>
@@ -11489,7 +11489,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
-    <row r="294" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="79"/>
       <c r="B294" s="28"/>
       <c r="C294" s="28"/>
@@ -11506,7 +11506,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
-    <row r="295" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A295" s="79"/>
       <c r="B295" s="28"/>
       <c r="C295" s="28"/>
@@ -11523,7 +11523,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
-    <row r="296" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="33"/>
       <c r="C296" s="33"/>
@@ -11546,7 +11546,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
-    <row r="297" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -11563,7 +11563,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
-    <row r="298" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -11580,7 +11580,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
-    <row r="299" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="s">
@@ -11601,7 +11601,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
-    <row r="300" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -11618,7 +11618,7 @@
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
-    <row r="301" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A301" s="79"/>
       <c r="B301" s="6" t="s">
         <v>3</v>
@@ -11645,7 +11645,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="79"/>
       <c r="B302" s="110" t="s">
         <v>13</v>
@@ -11674,7 +11674,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
-    <row r="303" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="79"/>
       <c r="B303" s="115" t="s">
         <v>13</v>
@@ -11703,7 +11703,7 @@
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
-    <row r="304" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="79"/>
       <c r="B304" s="21" t="s">
         <v>13</v>
@@ -11730,7 +11730,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
-    <row r="305" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="79"/>
       <c r="B305" s="28" t="s">
         <v>14</v>
@@ -11757,7 +11757,7 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
-    <row r="306" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="79"/>
       <c r="B306" s="28" t="s">
         <v>14</v>
@@ -11784,7 +11784,7 @@
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
-    <row r="307" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="79"/>
       <c r="B307" s="106" t="s">
         <v>16</v>
@@ -11815,7 +11815,7 @@
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
-    <row r="308" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="79"/>
       <c r="B308" s="28" t="s">
         <v>16</v>
@@ -11844,7 +11844,7 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
-    <row r="309" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="79"/>
       <c r="B309" s="106" t="s">
         <v>16</v>
@@ -11875,7 +11875,7 @@
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
-    <row r="310" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="79"/>
       <c r="B310" s="28" t="s">
         <v>16</v>
@@ -11904,7 +11904,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
-    <row r="311" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="79"/>
       <c r="B311" s="106" t="s">
         <v>16</v>
@@ -11935,7 +11935,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
-    <row r="312" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="79"/>
       <c r="B312" s="28" t="s">
         <v>16</v>
@@ -11964,7 +11964,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
-    <row r="313" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="79"/>
       <c r="B313" s="28" t="s">
         <v>17</v>
@@ -11991,7 +11991,7 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
-    <row r="314" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="79"/>
       <c r="B314" s="106" t="s">
         <v>17</v>
@@ -12022,7 +12022,7 @@
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
-    <row r="315" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="79"/>
       <c r="B315" s="28" t="s">
         <v>17</v>
@@ -12051,7 +12051,7 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
-    <row r="316" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="79"/>
       <c r="B316" s="106" t="s">
         <v>17</v>
@@ -12082,7 +12082,7 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
-    <row r="317" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="79"/>
       <c r="B317" s="28" t="s">
         <v>17</v>
@@ -12111,7 +12111,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
-    <row r="318" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="79"/>
       <c r="B318" s="106" t="s">
         <v>17</v>
@@ -12142,7 +12142,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
-    <row r="319" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="79"/>
       <c r="B319" s="106" t="s">
         <v>17</v>
@@ -12173,7 +12173,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
-    <row r="320" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="79"/>
       <c r="B320" s="28" t="s">
         <v>17</v>
@@ -12202,7 +12202,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
-    <row r="321" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="79"/>
       <c r="B321" s="106" t="s">
         <v>17</v>
@@ -12233,7 +12233,7 @@
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
-    <row r="322" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A322" s="79"/>
       <c r="B322" s="28" t="s">
         <v>17</v>
@@ -12262,7 +12262,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
-    <row r="323" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="33"/>
       <c r="C323" s="33"/>
@@ -12285,7 +12285,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
-    <row r="324" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -12302,7 +12302,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
-    <row r="325" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -12319,7 +12319,7 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
-    <row r="326" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="s">
@@ -12340,7 +12340,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
-    <row r="327" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -12357,7 +12357,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
-    <row r="328" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A328" s="79"/>
       <c r="B328" s="6" t="s">
         <v>3</v>
@@ -12384,7 +12384,7 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
-    <row r="329" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="79"/>
       <c r="B329" s="12" t="s">
         <v>13</v>
@@ -12409,7 +12409,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
-    <row r="330" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="79"/>
       <c r="B330" s="21"/>
       <c r="C330" s="21"/>
@@ -12426,7 +12426,7 @@
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
-    <row r="331" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="79"/>
       <c r="B331" s="21"/>
       <c r="C331" s="21"/>
@@ -12443,7 +12443,7 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
-    <row r="332" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="79"/>
       <c r="B332" s="28" t="s">
         <v>14</v>
@@ -12470,7 +12470,7 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
-    <row r="333" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="79"/>
       <c r="B333" s="28" t="s">
         <v>14</v>
@@ -12497,7 +12497,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
-    <row r="334" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="79"/>
       <c r="B334" s="28"/>
       <c r="C334" s="28"/>
@@ -12514,7 +12514,7 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
-    <row r="335" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="79"/>
       <c r="B335" s="106" t="s">
         <v>16</v>
@@ -12545,7 +12545,7 @@
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
-    <row r="336" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="79"/>
       <c r="B336" s="28" t="s">
         <v>16</v>
@@ -12574,7 +12574,7 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
     </row>
-    <row r="337" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="79"/>
       <c r="B337" s="106" t="s">
         <v>16</v>
@@ -12605,7 +12605,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
     </row>
-    <row r="338" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="79"/>
       <c r="B338" s="28" t="s">
         <v>16</v>
@@ -12634,7 +12634,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
     </row>
-    <row r="339" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="79"/>
       <c r="B339" s="28" t="s">
         <v>16</v>
@@ -12658,7 +12658,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
     </row>
-    <row r="340" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="79"/>
       <c r="B340" s="28"/>
       <c r="C340" s="28"/>
@@ -12672,7 +12672,7 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
     </row>
-    <row r="341" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="79"/>
       <c r="B341" s="106" t="s">
         <v>17</v>
@@ -12700,7 +12700,7 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
     </row>
-    <row r="342" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="79"/>
       <c r="B342" s="28" t="s">
         <v>17</v>
@@ -12726,7 +12726,7 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
     </row>
-    <row r="343" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="79"/>
       <c r="B343" s="28" t="s">
         <v>17</v>
@@ -12743,16 +12743,14 @@
       <c r="F343" s="30">
         <v>16</v>
       </c>
-      <c r="G343" s="87">
-        <v>46072</v>
-      </c>
+      <c r="G343" s="87"/>
       <c r="H343" s="91"/>
       <c r="I343" s="90"/>
       <c r="J343" s="1"/>
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
-    <row r="344" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="79"/>
       <c r="B344" s="106" t="s">
         <v>17</v>
@@ -12780,7 +12778,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
     </row>
-    <row r="345" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="79"/>
       <c r="B345" s="28" t="s">
         <v>17</v>
@@ -12806,7 +12804,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
     </row>
-    <row r="346" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="79"/>
       <c r="B346" s="28" t="s">
         <v>17</v>
@@ -12830,7 +12828,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
     </row>
-    <row r="347" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="79"/>
       <c r="B347" s="106" t="s">
         <v>17</v>
@@ -12858,7 +12856,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
     </row>
-    <row r="348" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="79"/>
       <c r="B348" s="28" t="s">
         <v>17</v>
@@ -12884,7 +12882,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
     </row>
-    <row r="349" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A349" s="79"/>
       <c r="B349" s="28"/>
       <c r="C349" s="28"/>
@@ -12898,7 +12896,7 @@
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
     </row>
-    <row r="350" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="33"/>
       <c r="C350" s="33"/>
@@ -12918,7 +12916,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
     </row>
-    <row r="351" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12932,7 +12930,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
     </row>
-    <row r="353" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="s">
         <v>245</v>
@@ -12947,7 +12945,7 @@
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
     </row>
-    <row r="354" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
@@ -12958,7 +12956,7 @@
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
     </row>
-    <row r="355" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B355" s="6" t="s">
         <v>3</v>
       </c>
@@ -12979,7 +12977,7 @@
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
     </row>
-    <row r="356" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B356" s="12" t="s">
         <v>13</v>
       </c>
@@ -12998,7 +12996,7 @@
       <c r="I356" s="1"/>
       <c r="J356" s="1"/>
     </row>
-    <row r="357" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B357" s="21"/>
       <c r="C357" s="21"/>
       <c r="D357" s="21"/>
@@ -13009,7 +13007,7 @@
       <c r="I357" s="1"/>
       <c r="J357" s="1"/>
     </row>
-    <row r="358" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B358" s="21"/>
       <c r="C358" s="21"/>
       <c r="D358" s="21"/>
@@ -13020,7 +13018,7 @@
       <c r="I358" s="1"/>
       <c r="J358" s="1"/>
     </row>
-    <row r="359" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B359" s="28" t="s">
         <v>14</v>
       </c>
@@ -13041,7 +13039,7 @@
       <c r="I359" s="1"/>
       <c r="J359" s="1"/>
     </row>
-    <row r="360" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B360" s="28" t="s">
         <v>14</v>
       </c>
@@ -13062,7 +13060,7 @@
       <c r="I360" s="1"/>
       <c r="J360" s="1"/>
     </row>
-    <row r="361" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B361" s="28" t="s">
         <v>16</v>
       </c>
@@ -13083,7 +13081,7 @@
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
     </row>
-    <row r="362" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B362" s="106" t="s">
         <v>16</v>
       </c>
@@ -13108,7 +13106,7 @@
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
     </row>
-    <row r="363" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B363" s="106" t="s">
         <v>16</v>
       </c>
@@ -13133,7 +13131,7 @@
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
     </row>
-    <row r="364" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B364" s="28" t="s">
         <v>16</v>
       </c>
@@ -13156,7 +13154,7 @@
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
     </row>
-    <row r="365" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B365" s="106" t="s">
         <v>16</v>
       </c>
@@ -13181,7 +13179,7 @@
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
     </row>
-    <row r="366" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B366" s="28" t="s">
         <v>16</v>
       </c>
@@ -13204,7 +13202,7 @@
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
     </row>
-    <row r="367" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B367" s="106" t="s">
         <v>17</v>
       </c>
@@ -13229,7 +13227,7 @@
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
     </row>
-    <row r="368" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B368" s="28" t="s">
         <v>17</v>
       </c>
@@ -13252,7 +13250,7 @@
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
     </row>
-    <row r="369" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B369" s="28" t="s">
         <v>17</v>
       </c>
@@ -13273,7 +13271,7 @@
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
     </row>
-    <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B370" s="28" t="s">
         <v>17</v>
       </c>
@@ -13294,7 +13292,7 @@
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
-    <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B371" s="106" t="s">
         <v>17</v>
       </c>
@@ -13319,7 +13317,7 @@
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
-    <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B372" s="106" t="s">
         <v>17</v>
       </c>
@@ -13344,7 +13342,7 @@
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
-    <row r="373" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B373" s="28" t="s">
         <v>17</v>
       </c>
@@ -13367,7 +13365,7 @@
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
-    <row r="374" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B374" s="106" t="s">
         <v>17</v>
       </c>
@@ -13392,7 +13390,7 @@
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
     </row>
-    <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B375" s="106" t="s">
         <v>17</v>
       </c>
@@ -13417,7 +13415,7 @@
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
     </row>
-    <row r="376" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B376" s="28" t="s">
         <v>17</v>
       </c>
@@ -13440,7 +13438,7 @@
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
     </row>
-    <row r="377" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B377" s="33"/>
       <c r="C377" s="33"/>
       <c r="D377" s="34"/>
@@ -13457,7 +13455,7 @@
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
     </row>
-    <row r="380" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B380" s="1"/>
       <c r="C380" s="3" t="s">
         <v>111</v>
@@ -13468,14 +13466,14 @@
       <c r="E380" s="2"/>
       <c r="F380" s="1"/>
     </row>
-    <row r="381" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
       <c r="E381" s="5"/>
       <c r="F381" s="4"/>
     </row>
-    <row r="382" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B382" s="6" t="s">
         <v>3</v>
       </c>
@@ -13492,7 +13490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B383" s="12" t="s">
         <v>13</v>
       </c>
@@ -13501,21 +13499,21 @@
       <c r="E383" s="14"/>
       <c r="F383" s="15"/>
     </row>
-    <row r="384" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B384" s="21"/>
       <c r="C384" s="21"/>
       <c r="D384" s="21"/>
       <c r="E384" s="22"/>
       <c r="F384" s="21"/>
     </row>
-    <row r="385" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B385" s="21"/>
       <c r="C385" s="21"/>
       <c r="D385" s="21"/>
       <c r="E385" s="22"/>
       <c r="F385" s="21"/>
     </row>
-    <row r="386" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B386" s="28" t="s">
         <v>14</v>
       </c>
@@ -13524,7 +13522,7 @@
       <c r="E386" s="29"/>
       <c r="F386" s="30"/>
     </row>
-    <row r="387" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B387" s="28" t="s">
         <v>14</v>
       </c>
@@ -13533,14 +13531,14 @@
       <c r="E387" s="29"/>
       <c r="F387" s="30"/>
     </row>
-    <row r="388" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B388" s="28"/>
       <c r="C388" s="28"/>
       <c r="D388" s="28"/>
       <c r="E388" s="29"/>
       <c r="F388" s="30"/>
     </row>
-    <row r="389" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B389" s="28" t="s">
         <v>16</v>
       </c>
@@ -13549,7 +13547,7 @@
       <c r="E389" s="29"/>
       <c r="F389" s="30"/>
     </row>
-    <row r="390" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B390" s="28" t="s">
         <v>16</v>
       </c>
@@ -13558,7 +13556,7 @@
       <c r="E390" s="29"/>
       <c r="F390" s="30"/>
     </row>
-    <row r="391" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B391" s="28" t="s">
         <v>16</v>
       </c>
@@ -13567,28 +13565,28 @@
       <c r="E391" s="29"/>
       <c r="F391" s="30"/>
     </row>
-    <row r="392" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B392" s="28"/>
       <c r="C392" s="28"/>
       <c r="D392" s="28"/>
       <c r="E392" s="29"/>
       <c r="F392" s="30"/>
     </row>
-    <row r="393" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B393" s="28"/>
       <c r="C393" s="28"/>
       <c r="D393" s="28"/>
       <c r="E393" s="29"/>
       <c r="F393" s="30"/>
     </row>
-    <row r="394" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B394" s="28"/>
       <c r="C394" s="28"/>
       <c r="D394" s="28"/>
       <c r="E394" s="29"/>
       <c r="F394" s="30"/>
     </row>
-    <row r="395" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B395" s="28" t="s">
         <v>17</v>
       </c>
@@ -13597,7 +13595,7 @@
       <c r="E395" s="29"/>
       <c r="F395" s="30"/>
     </row>
-    <row r="396" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B396" s="28" t="s">
         <v>17</v>
       </c>
@@ -13606,7 +13604,7 @@
       <c r="E396" s="29"/>
       <c r="F396" s="30"/>
     </row>
-    <row r="397" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B397" s="28" t="s">
         <v>17</v>
       </c>
@@ -13615,7 +13613,7 @@
       <c r="E397" s="29"/>
       <c r="F397" s="30"/>
     </row>
-    <row r="398" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B398" s="28" t="s">
         <v>17</v>
       </c>
@@ -13624,7 +13622,7 @@
       <c r="E398" s="29"/>
       <c r="F398" s="30"/>
     </row>
-    <row r="399" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B399" s="28" t="s">
         <v>17</v>
       </c>
@@ -13633,35 +13631,35 @@
       <c r="E399" s="29"/>
       <c r="F399" s="30"/>
     </row>
-    <row r="400" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B400" s="28"/>
       <c r="C400" s="28"/>
       <c r="D400" s="28"/>
       <c r="E400" s="29"/>
       <c r="F400" s="30"/>
     </row>
-    <row r="401" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B401" s="28"/>
       <c r="C401" s="28"/>
       <c r="D401" s="28"/>
       <c r="E401" s="29"/>
       <c r="F401" s="30"/>
     </row>
-    <row r="402" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B402" s="28"/>
       <c r="C402" s="28"/>
       <c r="D402" s="28"/>
       <c r="E402" s="29"/>
       <c r="F402" s="30"/>
     </row>
-    <row r="403" spans="2:6" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:6" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B403" s="28"/>
       <c r="C403" s="28"/>
       <c r="D403" s="28"/>
       <c r="E403" s="29"/>
       <c r="F403" s="30"/>
     </row>
-    <row r="404" spans="2:6" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:6" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B404" s="33"/>
       <c r="C404" s="33"/>
       <c r="D404" s="34"/>
@@ -13704,18 +13702,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IV22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.8" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.296875" style="38" customWidth="1"/>
-    <col min="2" max="2" width="11.796875" style="38" customWidth="1"/>
+    <col min="1" max="1" width="1.28515625" style="38" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="38" customWidth="1"/>
     <col min="3" max="3" width="31" style="38" customWidth="1"/>
-    <col min="4" max="4" width="35.296875" style="38" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" style="38" customWidth="1"/>
     <col min="5" max="6" width="9" style="38" customWidth="1"/>
     <col min="7" max="7" width="11" style="38" customWidth="1"/>
     <col min="8" max="256" width="9" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -13732,7 +13730,7 @@
       </c>
       <c r="K1" s="41"/>
     </row>
-    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -13747,7 +13745,7 @@
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -13760,7 +13758,7 @@
       <c r="J3" s="41"/>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40"/>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -13775,7 +13773,7 @@
       <c r="J4" s="41"/>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="40"/>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -13788,7 +13786,7 @@
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" ht="14.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="14.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="47"/>
       <c r="B6" s="48" t="s">
         <v>3</v>
@@ -13813,7 +13811,7 @@
       <c r="J6" s="41"/>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47"/>
       <c r="B7" s="54">
         <v>1</v>
@@ -13838,7 +13836,7 @@
       <c r="J7" s="41"/>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47"/>
       <c r="B8" s="54">
         <v>2</v>
@@ -13863,7 +13861,7 @@
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="47"/>
       <c r="B9" s="54">
         <v>3</v>
@@ -13888,7 +13886,7 @@
       <c r="J9" s="41"/>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="47"/>
       <c r="B10" s="54">
         <v>4</v>
@@ -13913,7 +13911,7 @@
       <c r="J10" s="41"/>
       <c r="K10" s="53"/>
     </row>
-    <row r="11" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="47"/>
       <c r="B11" s="54">
         <v>5</v>
@@ -13938,7 +13936,7 @@
       <c r="J11" s="41"/>
       <c r="K11" s="41"/>
     </row>
-    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="47"/>
       <c r="B12" s="54">
         <v>6</v>
@@ -13963,7 +13961,7 @@
       <c r="J12" s="41"/>
       <c r="K12" s="41"/>
     </row>
-    <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="47"/>
       <c r="B13" s="54">
         <v>7</v>
@@ -13988,7 +13986,7 @@
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
     </row>
-    <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="47"/>
       <c r="B14" s="54">
         <v>8</v>
@@ -14013,7 +14011,7 @@
       <c r="J14" s="41"/>
       <c r="K14" s="41"/>
     </row>
-    <row r="15" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="47"/>
       <c r="B15" s="54">
         <v>9</v>
@@ -14038,7 +14036,7 @@
       <c r="J15" s="41"/>
       <c r="K15" s="41"/>
     </row>
-    <row r="16" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="47"/>
       <c r="B16" s="54">
         <v>10</v>
@@ -14063,7 +14061,7 @@
       <c r="J16" s="41"/>
       <c r="K16" s="41"/>
     </row>
-    <row r="17" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="47"/>
       <c r="B17" s="54">
         <v>11</v>
@@ -14088,7 +14086,7 @@
       <c r="J17" s="41"/>
       <c r="K17" s="41"/>
     </row>
-    <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="47"/>
       <c r="B18" s="54">
         <v>11</v>
@@ -14113,7 +14111,7 @@
       <c r="J18" s="41"/>
       <c r="K18" s="41"/>
     </row>
-    <row r="19" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="47"/>
       <c r="B19" s="54">
         <v>13</v>
@@ -14138,7 +14136,7 @@
       <c r="J19" s="41"/>
       <c r="K19" s="41"/>
     </row>
-    <row r="20" spans="1:11" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="47"/>
       <c r="B20" s="54">
         <v>14</v>
@@ -14163,7 +14161,7 @@
       <c r="J20" s="41"/>
       <c r="K20" s="41"/>
     </row>
-    <row r="21" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40"/>
       <c r="B21" s="59"/>
       <c r="C21" s="59"/>
@@ -14176,7 +14174,7 @@
       <c r="J21" s="41"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
@@ -14210,17 +14208,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IW34"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.8" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.296875" style="38" customWidth="1"/>
-    <col min="3" max="3" width="10.09765625" style="38" customWidth="1"/>
-    <col min="4" max="4" width="9.296875" style="38" customWidth="1"/>
-    <col min="5" max="5" width="31.296875" style="38" customWidth="1"/>
-    <col min="6" max="7" width="9.296875" style="38" customWidth="1"/>
-    <col min="8" max="257" width="8.796875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" style="38" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="38" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" style="38" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" style="38" customWidth="1"/>
+    <col min="8" max="257" width="8.85546875" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
         <v>253</v>
       </c>
@@ -14230,7 +14228,7 @@
       <c r="F1" s="40"/>
       <c r="G1" s="40"/>
     </row>
-    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -14238,7 +14236,7 @@
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
     </row>
-    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>38</v>
       </c>
@@ -14248,7 +14246,7 @@
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
     </row>
-    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>42</v>
       </c>
@@ -14277,7 +14275,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="67" t="s">
         <v>43</v>
       </c>
@@ -14306,7 +14304,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="67" t="s">
         <v>44</v>
       </c>
@@ -14335,7 +14333,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
         <v>45</v>
       </c>
@@ -14364,7 +14362,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="67" t="s">
         <v>46</v>
       </c>
@@ -14387,7 +14385,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
         <v>47</v>
       </c>
@@ -14413,7 +14411,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67"/>
       <c r="B10" s="65"/>
       <c r="C10" s="65"/>
@@ -14425,7 +14423,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
         <v>525</v>
@@ -14439,7 +14437,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67" t="s">
         <v>48</v>
       </c>
@@ -14462,7 +14460,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67"/>
       <c r="B13" s="65"/>
       <c r="C13" s="68"/>
@@ -14471,7 +14469,7 @@
       <c r="F13" s="68"/>
       <c r="G13" s="64"/>
     </row>
-    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67"/>
       <c r="B14" s="63" t="s">
         <v>62</v>
@@ -14482,7 +14480,7 @@
       <c r="F14" s="69"/>
       <c r="G14" s="100"/>
     </row>
-    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67" t="s">
         <v>49</v>
       </c>
@@ -14505,7 +14503,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67" t="s">
         <v>50</v>
       </c>
@@ -14528,7 +14526,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67" t="s">
         <v>63</v>
       </c>
@@ -14551,7 +14549,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67" t="s">
         <v>76</v>
       </c>
@@ -14574,7 +14572,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="63"/>
       <c r="C19" s="64"/>
       <c r="D19" s="64"/>
@@ -14582,7 +14580,7 @@
       <c r="F19" s="66"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
         <v>535</v>
@@ -14593,7 +14591,7 @@
       <c r="F20" s="68"/>
       <c r="G20" s="64"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
         <v>77</v>
       </c>
@@ -14616,7 +14614,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="65"/>
       <c r="C22" s="64"/>
       <c r="D22" s="61"/>
@@ -14624,7 +14622,7 @@
       <c r="F22" s="66"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="63" t="s">
         <v>39</v>
       </c>
@@ -14634,7 +14632,7 @@
       <c r="F23" s="66"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67" t="s">
         <v>78</v>
       </c>
@@ -14657,7 +14655,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67" t="s">
         <v>110</v>
       </c>
@@ -14680,7 +14678,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67"/>
       <c r="B26" s="65"/>
       <c r="C26" s="68"/>
@@ -14689,7 +14687,7 @@
       <c r="F26" s="69"/>
       <c r="G26" s="100"/>
     </row>
-    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
         <v>543</v>
@@ -14700,7 +14698,7 @@
       <c r="F27" s="68"/>
       <c r="G27" s="64"/>
     </row>
-    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67" t="s">
         <v>255</v>
       </c>
@@ -14723,7 +14721,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
       <c r="D29" s="64"/>
@@ -14731,7 +14729,7 @@
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="63" t="s">
         <v>40</v>
       </c>
@@ -14741,7 +14739,7 @@
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67" t="s">
         <v>256</v>
       </c>
@@ -14764,7 +14762,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="40"/>
       <c r="C32" s="40"/>
       <c r="D32" s="64"/>
@@ -14772,7 +14770,7 @@
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="63" t="s">
         <v>41</v>
       </c>
@@ -14783,7 +14781,7 @@
       <c r="G33" s="40"/>
       <c r="K33" s="98"/>
     </row>
-    <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="65" t="s">
         <v>222</v>
       </c>
@@ -14809,13 +14807,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA85496-96FC-4E57-B88C-D037E5ADD8C6}">
   <dimension ref="A1:X71"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.69921875" customWidth="1"/>
-    <col min="5" max="5" width="35.296875" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B1" s="62" t="s">
         <v>282</v>
       </c>
@@ -14842,7 +14840,7 @@
       <c r="W1" s="38"/>
       <c r="X1" s="38"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -14867,7 +14865,7 @@
       <c r="W2" s="38"/>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B3" s="63" t="s">
         <v>38</v>
       </c>
@@ -14894,7 +14892,7 @@
       <c r="W3" s="38"/>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>42</v>
       </c>
@@ -14936,7 +14934,7 @@
       <c r="W4" s="38"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="67" t="s">
         <v>43</v>
       </c>
@@ -14978,7 +14976,7 @@
       <c r="W5" s="38"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="67" t="s">
         <v>44</v>
       </c>
@@ -15020,7 +15018,7 @@
       <c r="W6" s="38"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
         <v>45</v>
       </c>
@@ -15062,7 +15060,7 @@
       <c r="W7" s="38"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="67" t="s">
         <v>46</v>
       </c>
@@ -15104,7 +15102,7 @@
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
         <v>47</v>
       </c>
@@ -15146,7 +15144,7 @@
       <c r="W9" s="38"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
         <v>48</v>
       </c>
@@ -15188,7 +15186,7 @@
       <c r="W10" s="38"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
         <v>49</v>
       </c>
@@ -15228,7 +15226,7 @@
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="67" t="s">
         <v>50</v>
       </c>
@@ -15268,7 +15266,7 @@
       <c r="W12" s="38"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="67" t="s">
         <v>63</v>
       </c>
@@ -15308,7 +15306,7 @@
       <c r="W13" s="38"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="67"/>
       <c r="B14" s="68"/>
       <c r="C14" s="64"/>
@@ -15334,7 +15332,7 @@
       <c r="W14" s="38"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="67"/>
       <c r="B15" s="63" t="s">
         <v>441</v>
@@ -15362,7 +15360,7 @@
       <c r="W15" s="38"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="67" t="s">
         <v>76</v>
       </c>
@@ -15402,7 +15400,7 @@
       <c r="W16" s="38"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="67"/>
       <c r="B17" s="65"/>
       <c r="C17" s="65"/>
@@ -15428,7 +15426,7 @@
       <c r="W17" s="38"/>
       <c r="X17" s="38"/>
     </row>
-    <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="67"/>
       <c r="B18" s="63" t="s">
         <v>254</v>
@@ -15456,7 +15454,7 @@
       <c r="W18" s="38"/>
       <c r="X18" s="38"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="67" t="s">
         <v>77</v>
       </c>
@@ -15496,7 +15494,7 @@
       <c r="W19" s="38"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="67" t="s">
         <v>78</v>
       </c>
@@ -15536,7 +15534,7 @@
       <c r="W20" s="38"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="67" t="s">
         <v>110</v>
       </c>
@@ -15576,7 +15574,7 @@
       <c r="W21" s="38"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="67" t="s">
         <v>255</v>
       </c>
@@ -15616,7 +15614,7 @@
       <c r="W22" s="38"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="67" t="s">
         <v>256</v>
       </c>
@@ -15656,7 +15654,7 @@
       <c r="W23" s="38"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="67" t="s">
         <v>257</v>
       </c>
@@ -15696,7 +15694,7 @@
       <c r="W24" s="38"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="67" t="s">
         <v>258</v>
       </c>
@@ -15736,7 +15734,7 @@
       <c r="W25" s="38"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="67" t="s">
         <v>259</v>
       </c>
@@ -15776,7 +15774,7 @@
       <c r="W26" s="38"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="67"/>
       <c r="B27" s="65"/>
       <c r="C27" s="68"/>
@@ -15802,7 +15800,7 @@
       <c r="W27" s="38"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="67"/>
       <c r="B28" s="63" t="s">
         <v>62</v>
@@ -15830,7 +15828,7 @@
       <c r="W28" s="38"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="67" t="s">
         <v>260</v>
       </c>
@@ -15870,7 +15868,7 @@
       <c r="W29" s="38"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="67" t="s">
         <v>261</v>
       </c>
@@ -15910,7 +15908,7 @@
       <c r="W30" s="38"/>
       <c r="X30" s="38"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="67" t="s">
         <v>262</v>
       </c>
@@ -15950,7 +15948,7 @@
       <c r="W31" s="38"/>
       <c r="X31" s="38"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="67" t="s">
         <v>263</v>
       </c>
@@ -15990,7 +15988,7 @@
       <c r="W32" s="38"/>
       <c r="X32" s="38"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B33" s="65"/>
       <c r="C33" s="64"/>
       <c r="D33" s="61"/>
@@ -16015,7 +16013,7 @@
       <c r="W33" s="38"/>
       <c r="X33" s="38"/>
     </row>
-    <row r="34" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B34" s="63" t="s">
         <v>39</v>
       </c>
@@ -16042,7 +16040,7 @@
       <c r="W34" s="38"/>
       <c r="X34" s="38"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="67" t="s">
         <v>264</v>
       </c>
@@ -16082,7 +16080,7 @@
       <c r="W35" s="38"/>
       <c r="X35" s="38"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="67" t="s">
         <v>265</v>
       </c>
@@ -16122,7 +16120,7 @@
       <c r="W36" s="38"/>
       <c r="X36" s="38"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B37" s="65"/>
       <c r="C37" s="65"/>
       <c r="D37" s="64"/>
@@ -16147,7 +16145,7 @@
       <c r="W37" s="38"/>
       <c r="X37" s="38"/>
     </row>
-    <row r="38" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B38" s="63" t="s">
         <v>40</v>
       </c>
@@ -16174,7 +16172,7 @@
       <c r="W38" s="38"/>
       <c r="X38" s="38"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="67" t="s">
         <v>442</v>
       </c>
@@ -16214,7 +16212,7 @@
       <c r="W39" s="38"/>
       <c r="X39" s="38"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
       <c r="D40" s="64"/>
@@ -16239,7 +16237,7 @@
       <c r="W40" s="38"/>
       <c r="X40" s="38"/>
     </row>
-    <row r="41" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B41" s="63" t="s">
         <v>41</v>
       </c>
@@ -16266,7 +16264,7 @@
       <c r="W41" s="38"/>
       <c r="X41" s="38"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B42" s="65" t="s">
         <v>203</v>
       </c>
@@ -16293,7 +16291,7 @@
       <c r="W42" s="38"/>
       <c r="X42" s="38"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H43" s="38"/>
       <c r="I43" s="38"/>
       <c r="J43" s="38"/>
@@ -16312,7 +16310,7 @@
       <c r="W43" s="38"/>
       <c r="X43" s="38"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H44" s="38"/>
       <c r="I44" s="38"/>
       <c r="J44" s="38"/>
@@ -16331,7 +16329,7 @@
       <c r="W44" s="38"/>
       <c r="X44" s="38"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
       <c r="J45" s="38"/>
@@ -16350,7 +16348,7 @@
       <c r="W45" s="38"/>
       <c r="X45" s="38"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H46" s="38"/>
       <c r="I46" s="38"/>
       <c r="J46" s="38"/>
@@ -16369,7 +16367,7 @@
       <c r="W46" s="38"/>
       <c r="X46" s="38"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
       <c r="J47" s="38"/>
@@ -16388,7 +16386,7 @@
       <c r="W47" s="38"/>
       <c r="X47" s="38"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H48" s="38"/>
       <c r="I48" s="38"/>
       <c r="J48" s="38"/>
@@ -16407,7 +16405,7 @@
       <c r="W48" s="38"/>
       <c r="X48" s="38"/>
     </row>
-    <row r="49" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
       <c r="J49" s="38"/>
@@ -16426,7 +16424,7 @@
       <c r="W49" s="38"/>
       <c r="X49" s="38"/>
     </row>
-    <row r="50" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H50" s="38"/>
       <c r="I50" s="38"/>
       <c r="J50" s="38"/>
@@ -16445,7 +16443,7 @@
       <c r="W50" s="38"/>
       <c r="X50" s="38"/>
     </row>
-    <row r="51" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
       <c r="J51" s="38"/>
@@ -16464,7 +16462,7 @@
       <c r="W51" s="38"/>
       <c r="X51" s="38"/>
     </row>
-    <row r="52" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H52" s="38"/>
       <c r="I52" s="38"/>
       <c r="J52" s="38"/>
@@ -16483,7 +16481,7 @@
       <c r="W52" s="38"/>
       <c r="X52" s="38"/>
     </row>
-    <row r="53" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
       <c r="J53" s="38"/>
@@ -16502,7 +16500,7 @@
       <c r="W53" s="38"/>
       <c r="X53" s="38"/>
     </row>
-    <row r="54" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
@@ -16521,7 +16519,7 @@
       <c r="W54" s="38"/>
       <c r="X54" s="38"/>
     </row>
-    <row r="55" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H55" s="38"/>
       <c r="I55" s="38"/>
       <c r="J55" s="38"/>
@@ -16540,7 +16538,7 @@
       <c r="W55" s="38"/>
       <c r="X55" s="38"/>
     </row>
-    <row r="56" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="38"/>
@@ -16559,7 +16557,7 @@
       <c r="W56" s="38"/>
       <c r="X56" s="38"/>
     </row>
-    <row r="57" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H57" s="38"/>
       <c r="I57" s="38"/>
       <c r="J57" s="38"/>
@@ -16578,7 +16576,7 @@
       <c r="W57" s="38"/>
       <c r="X57" s="38"/>
     </row>
-    <row r="58" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
       <c r="J58" s="38"/>
@@ -16597,7 +16595,7 @@
       <c r="W58" s="38"/>
       <c r="X58" s="38"/>
     </row>
-    <row r="59" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
@@ -16616,7 +16614,7 @@
       <c r="W59" s="38"/>
       <c r="X59" s="38"/>
     </row>
-    <row r="60" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
       <c r="J60" s="38"/>
@@ -16635,7 +16633,7 @@
       <c r="W60" s="38"/>
       <c r="X60" s="38"/>
     </row>
-    <row r="61" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
       <c r="J61" s="38"/>
@@ -16654,7 +16652,7 @@
       <c r="W61" s="38"/>
       <c r="X61" s="38"/>
     </row>
-    <row r="62" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H62" s="38"/>
       <c r="I62" s="38"/>
       <c r="J62" s="38"/>
@@ -16673,7 +16671,7 @@
       <c r="W62" s="38"/>
       <c r="X62" s="38"/>
     </row>
-    <row r="63" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H63" s="38"/>
       <c r="I63" s="38"/>
       <c r="J63" s="38"/>
@@ -16692,7 +16690,7 @@
       <c r="W63" s="38"/>
       <c r="X63" s="38"/>
     </row>
-    <row r="64" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H64" s="38"/>
       <c r="I64" s="38"/>
       <c r="J64" s="38"/>
@@ -16711,7 +16709,7 @@
       <c r="W64" s="38"/>
       <c r="X64" s="38"/>
     </row>
-    <row r="65" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H65" s="38"/>
       <c r="I65" s="38"/>
       <c r="J65" s="38"/>
@@ -16730,7 +16728,7 @@
       <c r="W65" s="38"/>
       <c r="X65" s="38"/>
     </row>
-    <row r="66" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H66" s="38"/>
       <c r="I66" s="38"/>
       <c r="J66" s="38"/>
@@ -16749,7 +16747,7 @@
       <c r="W66" s="38"/>
       <c r="X66" s="38"/>
     </row>
-    <row r="67" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H67" s="38"/>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
@@ -16768,7 +16766,7 @@
       <c r="W67" s="38"/>
       <c r="X67" s="38"/>
     </row>
-    <row r="68" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H68" s="38"/>
       <c r="I68" s="38"/>
       <c r="J68" s="38"/>
@@ -16787,7 +16785,7 @@
       <c r="W68" s="38"/>
       <c r="X68" s="38"/>
     </row>
-    <row r="69" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
@@ -16806,7 +16804,7 @@
       <c r="W69" s="38"/>
       <c r="X69" s="38"/>
     </row>
-    <row r="70" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H70" s="38"/>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
@@ -16825,7 +16823,7 @@
       <c r="W70" s="38"/>
       <c r="X70" s="38"/>
     </row>
-    <row r="71" spans="8:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="8:24" x14ac:dyDescent="0.25">
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
       <c r="J71" s="38"/>
@@ -16856,15 +16854,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5616AB3-C7B1-4511-93B2-51A6298AD44C}">
   <dimension ref="A5:Q38"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.8984375" customWidth="1"/>
-    <col min="6" max="6" width="13.3984375" customWidth="1"/>
-    <col min="10" max="10" width="17.09765625" customWidth="1"/>
-    <col min="14" max="14" width="16.69921875" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>295</v>
       </c>
@@ -16890,7 +16888,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>296</v>
       </c>
@@ -16922,7 +16920,7 @@
       </c>
       <c r="Q6" s="109"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>297</v>
       </c>
@@ -16954,7 +16952,7 @@
       </c>
       <c r="Q7" s="109"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>298</v>
       </c>
@@ -16986,7 +16984,7 @@
       </c>
       <c r="Q8" s="109"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>299</v>
       </c>
@@ -17018,7 +17016,7 @@
       </c>
       <c r="Q9" s="109"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>300</v>
       </c>
@@ -17050,7 +17048,7 @@
       </c>
       <c r="Q10" s="109"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>301</v>
       </c>
@@ -17082,7 +17080,7 @@
       </c>
       <c r="Q11" s="109"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>302</v>
       </c>
@@ -17114,7 +17112,7 @@
       </c>
       <c r="Q12" s="109"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>303</v>
       </c>
@@ -17146,7 +17144,7 @@
       </c>
       <c r="Q13" s="109"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>304</v>
       </c>
@@ -17178,7 +17176,7 @@
       </c>
       <c r="Q14" s="109"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>305</v>
       </c>
@@ -17210,7 +17208,7 @@
       </c>
       <c r="Q15" s="109"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>306</v>
       </c>
@@ -17242,7 +17240,7 @@
       </c>
       <c r="Q16" s="109"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>307</v>
       </c>
@@ -17274,7 +17272,7 @@
       </c>
       <c r="Q17" s="109"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>308</v>
       </c>
@@ -17306,7 +17304,7 @@
       </c>
       <c r="Q18" s="109"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>309</v>
       </c>
@@ -17338,7 +17336,7 @@
       </c>
       <c r="Q19" s="109"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>310</v>
       </c>
@@ -17370,7 +17368,7 @@
       </c>
       <c r="Q20" s="109"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>311</v>
       </c>
@@ -17402,7 +17400,7 @@
       </c>
       <c r="Q21" s="109"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>312</v>
       </c>
@@ -17434,7 +17432,7 @@
       </c>
       <c r="Q22" s="109"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>313</v>
       </c>
@@ -17466,7 +17464,7 @@
       </c>
       <c r="Q23" s="109"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>314</v>
       </c>
@@ -17498,7 +17496,7 @@
       </c>
       <c r="Q24" s="109"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>315</v>
       </c>
@@ -17530,7 +17528,7 @@
       </c>
       <c r="Q25" s="109"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="78" t="s">
         <v>317</v>
       </c>
@@ -17562,7 +17560,7 @@
       </c>
       <c r="Q26" s="109"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F27" t="s">
         <v>340</v>
       </c>
@@ -17587,7 +17585,7 @@
       </c>
       <c r="Q27" s="109"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F28" t="s">
         <v>341</v>
       </c>
@@ -17612,7 +17610,7 @@
       </c>
       <c r="Q28" s="109"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F29" t="s">
         <v>342</v>
       </c>
@@ -17635,7 +17633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="F30" s="78" t="s">
         <v>317</v>
       </c>
@@ -17658,7 +17656,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="67" t="s">
         <v>423</v>
       </c>

--- a/data/DreamLeague25-26.xlsx
+++ b/data/DreamLeague25-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\80010008\git\dreamleague\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kelloggcompany-my.sharepoint.com/personal/bryn_coombe_kellogg_com/Documents/Desktop/Dream League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF4598B-47B9-4EE7-8DD7-5378FEB61E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1967" documentId="8_{C787F6C9-6D19-48E2-96AB-9D578E0B907B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CB39009-56D2-4792-ADE1-8FF74E4A7A1C}"/>
   <bookViews>
-    <workbookView xWindow="25017" yWindow="-118" windowWidth="25370" windowHeight="13667" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="561">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -1688,6 +1688,39 @@
   </si>
   <si>
     <t>JACK MOYLAN</t>
+  </si>
+  <si>
+    <t>NICO O'REILLY</t>
+  </si>
+  <si>
+    <t>RYAN MANNING</t>
+  </si>
+  <si>
+    <t>ISAAC HUTCHINSON</t>
+  </si>
+  <si>
+    <t>CHELTENHAM</t>
+  </si>
+  <si>
+    <t>ANTHONY GORDON</t>
+  </si>
+  <si>
+    <t>HARVEY BARNES</t>
+  </si>
+  <si>
+    <t>IGOR JESUS</t>
+  </si>
+  <si>
+    <t>LEE BONIS</t>
+  </si>
+  <si>
+    <t>TYRESE SHADE</t>
+  </si>
+  <si>
+    <t>CAULEY WOODROW</t>
+  </si>
+  <si>
+    <t>CHARLES VERNAM</t>
   </si>
 </sst>
 </file>
@@ -3590,30 +3623,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:IX404"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.45" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="77" customWidth="1"/>
+    <col min="1" max="1" width="1.296875" style="77" customWidth="1"/>
     <col min="2" max="2" width="16" style="77" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" style="77" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" style="77" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="77" customWidth="1"/>
+    <col min="3" max="3" width="39.296875" style="77" customWidth="1"/>
+    <col min="4" max="4" width="32.796875" style="77" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" style="77" customWidth="1"/>
     <col min="6" max="6" width="17" style="77" customWidth="1"/>
-    <col min="7" max="8" width="11.28515625" style="77" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" style="77" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" style="77" customWidth="1"/>
-    <col min="11" max="11" width="25.7109375" style="77" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.28515625" style="77" customWidth="1"/>
+    <col min="7" max="8" width="11.296875" style="77" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.69921875" style="77" customWidth="1"/>
+    <col min="10" max="10" width="7.09765625" style="77" customWidth="1"/>
+    <col min="11" max="11" width="25.69921875" style="77" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.296875" style="77" customWidth="1"/>
     <col min="13" max="14" width="12" style="77" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" style="77" customWidth="1"/>
+    <col min="15" max="15" width="10.296875" style="77" customWidth="1"/>
     <col min="16" max="17" width="9" style="77" customWidth="1"/>
-    <col min="18" max="18" width="32.28515625" style="77" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="32.296875" style="77" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="9" style="77" customWidth="1"/>
-    <col min="22" max="22" width="30.140625" style="77" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.09765625" style="77" bestFit="1" customWidth="1"/>
     <col min="23" max="258" width="9" style="77" customWidth="1"/>
     <col min="259" max="16384" width="9" style="78"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3632,7 +3665,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
@@ -3653,7 +3686,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3670,7 +3703,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="79"/>
       <c r="B4" s="6" t="s">
         <v>3</v>
@@ -3712,7 +3745,7 @@
       <c r="U4" s="119"/>
       <c r="V4" s="119"/>
     </row>
-    <row r="5" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="79"/>
       <c r="B5" s="110" t="s">
         <v>13</v>
@@ -3759,7 +3792,7 @@
       <c r="T5" s="101"/>
       <c r="U5" s="102"/>
     </row>
-    <row r="6" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="79"/>
       <c r="B6" s="21" t="s">
         <v>13</v>
@@ -3804,7 +3837,7 @@
       <c r="T6" s="101"/>
       <c r="U6" s="102"/>
     </row>
-    <row r="7" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="79"/>
       <c r="B7" s="21"/>
       <c r="C7" s="21"/>
@@ -3825,21 +3858,21 @@
       </c>
       <c r="M7" s="25">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N7" s="26">
         <f>SUM(F62:F79)</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O7" s="27">
         <f>SUM(F59:F61)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S7" s="102"/>
       <c r="T7" s="101"/>
       <c r="U7" s="102"/>
     </row>
-    <row r="8" spans="1:22" ht="12.45" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="79"/>
       <c r="B8" s="28" t="s">
         <v>14</v>
@@ -3880,7 +3913,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="79"/>
       <c r="B9" s="28" t="s">
         <v>14</v>
@@ -3922,7 +3955,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="79"/>
       <c r="B10" s="106" t="s">
         <v>16</v>
@@ -3973,7 +4006,7 @@
       <c r="U10" s="119"/>
       <c r="V10" s="119"/>
     </row>
-    <row r="11" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="79"/>
       <c r="B11" s="28" t="s">
         <v>16</v>
@@ -4020,7 +4053,7 @@
       <c r="T11" s="101"/>
       <c r="U11" s="102"/>
     </row>
-    <row r="12" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="79"/>
       <c r="B12" s="106" t="s">
         <v>16</v>
@@ -4055,7 +4088,7 @@
       </c>
       <c r="M12" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="N12" s="73">
         <f>SUM(F197:F214)</f>
@@ -4063,10 +4096,10 @@
       </c>
       <c r="O12" s="74">
         <f>SUM(F194:F196)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="79"/>
       <c r="B13" s="28" t="s">
         <v>16</v>
@@ -4099,7 +4132,7 @@
       </c>
       <c r="M13" s="25">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N13" s="73">
         <f>SUM(F224:F241)</f>
@@ -4107,7 +4140,7 @@
       </c>
       <c r="O13" s="74">
         <f>SUM(F221:F223)</f>
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="R13" s="119"/>
       <c r="S13" s="119"/>
@@ -4115,7 +4148,7 @@
       <c r="U13" s="119"/>
       <c r="V13" s="119"/>
     </row>
-    <row r="14" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79"/>
       <c r="B14" s="28" t="s">
         <v>16</v>
@@ -4160,7 +4193,7 @@
       <c r="T14" s="101"/>
       <c r="U14" s="102"/>
     </row>
-    <row r="15" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="79"/>
       <c r="B15" s="106" t="s">
         <v>17</v>
@@ -4195,7 +4228,7 @@
       </c>
       <c r="M15" s="25">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N15" s="26">
         <f>SUM(F278:F295)</f>
@@ -4203,10 +4236,10 @@
       </c>
       <c r="O15" s="27">
         <f>SUM(F275:F277)</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="79"/>
       <c r="B16" s="28" t="s">
         <v>17</v>
@@ -4250,7 +4283,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="79"/>
       <c r="B17" s="28" t="s">
         <v>17</v>
@@ -4297,7 +4330,7 @@
       <c r="U17" s="119"/>
       <c r="V17" s="119"/>
     </row>
-    <row r="18" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="79"/>
       <c r="B18" s="106" t="s">
         <v>17</v>
@@ -4346,7 +4379,7 @@
       <c r="T18" s="101"/>
       <c r="U18" s="102"/>
     </row>
-    <row r="19" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="79"/>
       <c r="B19" s="106" t="s">
         <v>17</v>
@@ -4377,7 +4410,7 @@
       <c r="N19" s="88"/>
       <c r="O19" s="88"/>
     </row>
-    <row r="20" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="79"/>
       <c r="B20" s="28" t="s">
         <v>17</v>
@@ -4411,7 +4444,7 @@
       <c r="U20" s="119"/>
       <c r="V20" s="119"/>
     </row>
-    <row r="21" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="79"/>
       <c r="B21" s="106" t="s">
         <v>17</v>
@@ -4445,7 +4478,7 @@
       <c r="T21" s="101"/>
       <c r="U21" s="102"/>
     </row>
-    <row r="22" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="79"/>
       <c r="B22" s="28" t="s">
         <v>17</v>
@@ -4474,7 +4507,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="79"/>
       <c r="B23" s="106" t="s">
         <v>17</v>
@@ -4505,7 +4538,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="79"/>
       <c r="B24" s="106" t="s">
         <v>17</v>
@@ -4541,7 +4574,7 @@
       <c r="U24" s="119"/>
       <c r="V24" s="119"/>
     </row>
-    <row r="25" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="79"/>
       <c r="B25" s="28" t="s">
         <v>17</v>
@@ -4573,7 +4606,7 @@
       <c r="T25" s="101"/>
       <c r="U25" s="102"/>
     </row>
-    <row r="26" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
@@ -4596,7 +4629,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -4613,7 +4646,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -4635,7 +4668,7 @@
       <c r="U28" s="119"/>
       <c r="V28" s="119"/>
     </row>
-    <row r="29" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
@@ -4656,7 +4689,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -4673,7 +4706,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:22" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="79"/>
       <c r="B31" s="6" t="s">
         <v>3</v>
@@ -4700,7 +4733,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="79"/>
       <c r="B32" s="115" t="s">
         <v>13</v>
@@ -4729,7 +4762,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="79"/>
       <c r="B33" s="115" t="s">
         <v>13</v>
@@ -4758,7 +4791,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="79"/>
       <c r="B34" s="28" t="s">
         <v>13</v>
@@ -4785,7 +4818,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="79"/>
       <c r="B35" s="28" t="s">
         <v>14</v>
@@ -4812,7 +4845,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="79"/>
       <c r="B36" s="28" t="s">
         <v>14</v>
@@ -4839,7 +4872,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="79"/>
       <c r="B37" s="28" t="s">
         <v>16</v>
@@ -4866,7 +4899,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="79"/>
       <c r="B38" s="28" t="s">
         <v>16</v>
@@ -4898,7 +4931,7 @@
       <c r="U38" s="119"/>
       <c r="V38" s="119"/>
     </row>
-    <row r="39" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="79"/>
       <c r="B39" s="28" t="s">
         <v>16</v>
@@ -4925,7 +4958,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="79"/>
       <c r="B40" s="106" t="s">
         <v>17</v>
@@ -4956,7 +4989,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="79"/>
       <c r="B41" s="106" t="s">
         <v>17</v>
@@ -4987,7 +5020,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="79"/>
       <c r="B42" s="106" t="s">
         <v>17</v>
@@ -5002,7 +5035,7 @@
         <v>284</v>
       </c>
       <c r="F42" s="108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="87">
         <v>46051</v>
@@ -5018,7 +5051,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="79"/>
       <c r="B43" s="28" t="s">
         <v>17</v>
@@ -5033,7 +5066,7 @@
         <v>284</v>
       </c>
       <c r="F43" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="87">
         <v>46107</v>
@@ -5047,7 +5080,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="79"/>
       <c r="B44" s="28" t="s">
         <v>17</v>
@@ -5074,7 +5107,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="79"/>
       <c r="B45" s="106" t="s">
         <v>17</v>
@@ -5105,7 +5138,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="79"/>
       <c r="B46" s="106" t="s">
         <v>17</v>
@@ -5136,7 +5169,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="79"/>
       <c r="B47" s="106" t="s">
         <v>17</v>
@@ -5167,7 +5200,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:22" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="79"/>
       <c r="B48" s="28" t="s">
         <v>17</v>
@@ -5196,7 +5229,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="79"/>
       <c r="B49" s="106" t="s">
         <v>17</v>
@@ -5227,7 +5260,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="79"/>
       <c r="B50" s="106" t="s">
         <v>17</v>
@@ -5258,7 +5291,7 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="79"/>
       <c r="B51" s="28" t="s">
         <v>17</v>
@@ -5287,7 +5320,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="79"/>
       <c r="B52" s="28" t="s">
         <v>17</v>
@@ -5314,7 +5347,7 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="B53" s="33"/>
       <c r="C53" s="33"/>
@@ -5337,7 +5370,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -5354,7 +5387,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5371,7 +5404,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
@@ -5392,7 +5425,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -5409,7 +5442,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="79"/>
       <c r="B58" s="6" t="s">
         <v>3</v>
@@ -5436,7 +5469,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="79"/>
       <c r="B59" s="12" t="s">
         <v>13</v>
@@ -5449,7 +5482,7 @@
         <v>4</v>
       </c>
       <c r="F59" s="15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G59" s="80"/>
       <c r="H59" s="92"/>
@@ -5461,7 +5494,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="79"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -5478,7 +5511,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="79"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -5495,7 +5528,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="79"/>
       <c r="B62" s="28" t="s">
         <v>14</v>
@@ -5522,7 +5555,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="79"/>
       <c r="B63" s="28" t="s">
         <v>14</v>
@@ -5549,7 +5582,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="79"/>
       <c r="B64" s="28"/>
       <c r="C64" s="28"/>
@@ -5566,7 +5599,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="79"/>
       <c r="B65" s="28" t="s">
         <v>16</v>
@@ -5593,7 +5626,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="79"/>
       <c r="B66" s="28" t="s">
         <v>16</v>
@@ -5620,7 +5653,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="79"/>
       <c r="B67" s="106" t="s">
         <v>16</v>
@@ -5651,7 +5684,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="79"/>
       <c r="B68" s="28" t="s">
         <v>16</v>
@@ -5680,7 +5713,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="79"/>
       <c r="B69" s="106" t="s">
         <v>17</v>
@@ -5711,7 +5744,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="79"/>
       <c r="B70" s="28" t="s">
         <v>17</v>
@@ -5740,7 +5773,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="79"/>
       <c r="B71" s="106" t="s">
         <v>17</v>
@@ -5771,7 +5804,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="79"/>
       <c r="B72" s="28" t="s">
         <v>17</v>
@@ -5800,7 +5833,7 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="79"/>
       <c r="B73" s="28" t="s">
         <v>17</v>
@@ -5827,7 +5860,7 @@
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
-    <row r="74" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="79"/>
       <c r="B74" s="106" t="s">
         <v>17</v>
@@ -5858,7 +5891,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="79"/>
       <c r="B75" s="106" t="s">
         <v>17</v>
@@ -5889,7 +5922,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="79"/>
       <c r="B76" s="28" t="s">
         <v>17</v>
@@ -5904,7 +5937,7 @@
         <v>284</v>
       </c>
       <c r="F76" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G76" s="87">
         <v>46044</v>
@@ -5918,7 +5951,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
     </row>
-    <row r="77" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="79"/>
       <c r="B77" s="106" t="s">
         <v>17</v>
@@ -5949,7 +5982,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
     </row>
-    <row r="78" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="79"/>
       <c r="B78" s="106" t="s">
         <v>17</v>
@@ -5980,7 +6013,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="79"/>
       <c r="B79" s="28" t="s">
         <v>17</v>
@@ -6009,7 +6042,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1"/>
       <c r="B80" s="33"/>
       <c r="C80" s="33"/>
@@ -6020,7 +6053,7 @@
       </c>
       <c r="F80" s="36">
         <f>SUM(F62:F79)-SUM(F59:F61)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G80" s="80"/>
       <c r="H80" s="92"/>
@@ -6032,7 +6065,7 @@
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6049,7 +6082,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="82" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -6066,7 +6099,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="3" t="s">
@@ -6087,7 +6120,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
     </row>
-    <row r="84" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -6104,7 +6137,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="79"/>
       <c r="B85" s="6" t="s">
         <v>3</v>
@@ -6131,7 +6164,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="79"/>
       <c r="B86" s="12" t="s">
         <v>13</v>
@@ -6156,7 +6189,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
     </row>
-    <row r="87" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="79"/>
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
@@ -6173,7 +6206,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="79"/>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
@@ -6190,7 +6223,7 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="79"/>
       <c r="B89" s="28" t="s">
         <v>14</v>
@@ -6217,7 +6250,7 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="79"/>
       <c r="B90" s="28" t="s">
         <v>14</v>
@@ -6244,7 +6277,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="79"/>
       <c r="B91" s="28" t="s">
         <v>16</v>
@@ -6271,7 +6304,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="79"/>
       <c r="B92" s="106" t="s">
         <v>16</v>
@@ -6302,7 +6335,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
     </row>
-    <row r="93" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="79"/>
       <c r="B93" s="106" t="s">
         <v>16</v>
@@ -6333,7 +6366,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="79"/>
       <c r="B94" s="28" t="s">
         <v>16</v>
@@ -6362,7 +6395,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="79"/>
       <c r="B95" s="28" t="s">
         <v>16</v>
@@ -6389,7 +6422,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="79"/>
       <c r="B96" s="28" t="s">
         <v>17</v>
@@ -6416,7 +6449,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="79"/>
       <c r="B97" s="106" t="s">
         <v>17</v>
@@ -6447,7 +6480,7 @@
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="79"/>
       <c r="B98" s="106" t="s">
         <v>17</v>
@@ -6478,7 +6511,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="79"/>
       <c r="B99" s="28" t="s">
         <v>17</v>
@@ -6507,7 +6540,7 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="79"/>
       <c r="B100" s="106" t="s">
         <v>17</v>
@@ -6538,7 +6571,7 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
-    <row r="101" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="79"/>
       <c r="B101" s="28" t="s">
         <v>17</v>
@@ -6567,7 +6600,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="79"/>
       <c r="B102" s="106" t="s">
         <v>17</v>
@@ -6598,7 +6631,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="79"/>
       <c r="B103" s="28" t="s">
         <v>17</v>
@@ -6627,7 +6660,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
-    <row r="104" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="79"/>
       <c r="B104" s="106" t="s">
         <v>17</v>
@@ -6658,7 +6691,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="79"/>
       <c r="B105" s="106" t="s">
         <v>17</v>
@@ -6689,7 +6722,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="79"/>
       <c r="B106" s="28" t="s">
         <v>17</v>
@@ -6718,7 +6751,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="33"/>
       <c r="C107" s="33"/>
@@ -6741,7 +6774,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
-    <row r="108" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -6758,7 +6791,7 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
-    <row r="109" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -6775,7 +6808,7 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3" t="s">
@@ -6796,7 +6829,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
-    <row r="111" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -6813,7 +6846,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
-    <row r="112" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="79"/>
       <c r="B112" s="6" t="s">
         <v>3</v>
@@ -6840,7 +6873,7 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
-    <row r="113" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="79"/>
       <c r="B113" s="12" t="s">
         <v>13</v>
@@ -6865,7 +6898,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="79"/>
       <c r="B114" s="21"/>
       <c r="C114" s="21"/>
@@ -6882,7 +6915,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="79"/>
       <c r="B115" s="21"/>
       <c r="C115" s="21"/>
@@ -6899,7 +6932,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="79"/>
       <c r="B116" s="28" t="s">
         <v>14</v>
@@ -6926,7 +6959,7 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
-    <row r="117" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="79"/>
       <c r="B117" s="28" t="s">
         <v>14</v>
@@ -6953,7 +6986,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
-    <row r="118" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="79"/>
       <c r="B118" s="106" t="s">
         <v>16</v>
@@ -6984,7 +7017,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
-    <row r="119" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="79"/>
       <c r="B119" s="28" t="s">
         <v>16</v>
@@ -7013,7 +7046,7 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
-    <row r="120" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="79"/>
       <c r="B120" s="28" t="s">
         <v>16</v>
@@ -7040,7 +7073,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
     </row>
-    <row r="121" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="79"/>
       <c r="B121" s="106" t="s">
         <v>16</v>
@@ -7071,7 +7104,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
-    <row r="122" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="79"/>
       <c r="B122" s="28" t="s">
         <v>16</v>
@@ -7100,7 +7133,7 @@
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
-    <row r="123" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="79"/>
       <c r="B123" s="28" t="s">
         <v>17</v>
@@ -7127,7 +7160,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
-    <row r="124" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="79"/>
       <c r="B124" s="106" t="s">
         <v>17</v>
@@ -7158,7 +7191,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
-    <row r="125" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="79"/>
       <c r="B125" s="106" t="s">
         <v>17</v>
@@ -7189,7 +7222,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
-    <row r="126" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="79"/>
       <c r="B126" s="106" t="s">
         <v>17</v>
@@ -7220,7 +7253,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="79"/>
       <c r="B127" s="28" t="s">
         <v>17</v>
@@ -7249,7 +7282,7 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
-    <row r="128" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="79"/>
       <c r="B128" s="106" t="s">
         <v>17</v>
@@ -7280,7 +7313,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
-    <row r="129" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="79"/>
       <c r="B129" s="106" t="s">
         <v>17</v>
@@ -7311,7 +7344,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
-    <row r="130" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="79"/>
       <c r="B130" s="28" t="s">
         <v>17</v>
@@ -7340,7 +7373,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
-    <row r="131" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="79"/>
       <c r="B131" s="28" t="s">
         <v>17</v>
@@ -7367,7 +7400,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
-    <row r="132" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="79"/>
       <c r="B132" s="106" t="s">
         <v>17</v>
@@ -7398,7 +7431,7 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
     </row>
-    <row r="133" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="79"/>
       <c r="B133" s="28" t="s">
         <v>17</v>
@@ -7427,7 +7460,7 @@
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
     </row>
-    <row r="134" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1"/>
       <c r="B134" s="33"/>
       <c r="C134" s="33"/>
@@ -7450,7 +7483,7 @@
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
     </row>
-    <row r="135" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -7467,7 +7500,7 @@
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
     </row>
-    <row r="136" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -7484,7 +7517,7 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
     </row>
-    <row r="137" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="3" t="s">
@@ -7505,7 +7538,7 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
     </row>
-    <row r="138" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -7522,7 +7555,7 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
     </row>
-    <row r="139" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="79"/>
       <c r="B139" s="6" t="s">
         <v>3</v>
@@ -7549,7 +7582,7 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="79"/>
       <c r="B140" s="110" t="s">
         <v>13</v>
@@ -7578,7 +7611,7 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
     </row>
-    <row r="141" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="79"/>
       <c r="B141" s="115" t="s">
         <v>13</v>
@@ -7607,7 +7640,7 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
     </row>
-    <row r="142" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="79"/>
       <c r="B142" s="21" t="s">
         <v>13</v>
@@ -7634,7 +7667,7 @@
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
     </row>
-    <row r="143" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="79"/>
       <c r="B143" s="28" t="s">
         <v>14</v>
@@ -7661,7 +7694,7 @@
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
     </row>
-    <row r="144" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="79"/>
       <c r="B144" s="28" t="s">
         <v>14</v>
@@ -7688,7 +7721,7 @@
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
     </row>
-    <row r="145" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="79"/>
       <c r="B145" s="28" t="s">
         <v>16</v>
@@ -7715,7 +7748,7 @@
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
     </row>
-    <row r="146" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="79"/>
       <c r="B146" s="28" t="s">
         <v>16</v>
@@ -7742,7 +7775,7 @@
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
     </row>
-    <row r="147" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="79"/>
       <c r="B147" s="106" t="s">
         <v>16</v>
@@ -7773,7 +7806,7 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
     </row>
-    <row r="148" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="79"/>
       <c r="B148" s="28" t="s">
         <v>16</v>
@@ -7802,7 +7835,7 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
     </row>
-    <row r="149" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="79"/>
       <c r="B149" s="106" t="s">
         <v>17</v>
@@ -7833,7 +7866,7 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
     </row>
-    <row r="150" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="79"/>
       <c r="B150" s="28" t="s">
         <v>17</v>
@@ -7862,7 +7895,7 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
     </row>
-    <row r="151" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="79"/>
       <c r="B151" s="106" t="s">
         <v>17</v>
@@ -7893,7 +7926,7 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
     </row>
-    <row r="152" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="79"/>
       <c r="B152" s="28" t="s">
         <v>17</v>
@@ -7922,7 +7955,7 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
     </row>
-    <row r="153" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="79"/>
       <c r="B153" s="106" t="s">
         <v>17</v>
@@ -7953,7 +7986,7 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
     </row>
-    <row r="154" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="79"/>
       <c r="B154" s="106" t="s">
         <v>17</v>
@@ -7984,7 +8017,7 @@
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
     </row>
-    <row r="155" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="79"/>
       <c r="B155" s="106" t="s">
         <v>17</v>
@@ -8015,7 +8048,7 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
     </row>
-    <row r="156" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="79"/>
       <c r="B156" s="28" t="s">
         <v>17</v>
@@ -8044,7 +8077,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
     </row>
-    <row r="157" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="79"/>
       <c r="B157" s="28" t="s">
         <v>17</v>
@@ -8071,7 +8104,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
     </row>
-    <row r="158" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="79"/>
       <c r="B158" s="106" t="s">
         <v>17</v>
@@ -8102,7 +8135,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
     </row>
-    <row r="159" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="79"/>
       <c r="B159" s="106" t="s">
         <v>17</v>
@@ -8133,7 +8166,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
     </row>
-    <row r="160" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="79"/>
       <c r="B160" s="28" t="s">
         <v>17</v>
@@ -8162,7 +8195,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
     </row>
-    <row r="161" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1"/>
       <c r="B161" s="33"/>
       <c r="C161" s="33"/>
@@ -8185,7 +8218,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
     </row>
-    <row r="162" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -8202,7 +8235,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
     </row>
-    <row r="163" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -8219,7 +8252,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
     </row>
-    <row r="164" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="3" t="s">
@@ -8240,7 +8273,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
     </row>
-    <row r="165" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="1"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -8257,7 +8290,7 @@
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
     </row>
-    <row r="166" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="79"/>
       <c r="B166" s="6" t="s">
         <v>3</v>
@@ -8284,7 +8317,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
     </row>
-    <row r="167" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="79"/>
       <c r="B167" s="110" t="s">
         <v>13</v>
@@ -8313,7 +8346,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
     </row>
-    <row r="168" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="79"/>
       <c r="B168" s="12" t="s">
         <v>13</v>
@@ -8340,7 +8373,7 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
     </row>
-    <row r="169" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="79"/>
       <c r="B169" s="21"/>
       <c r="C169" s="21"/>
@@ -8357,7 +8390,7 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
     </row>
-    <row r="170" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="79"/>
       <c r="B170" s="28" t="s">
         <v>14</v>
@@ -8384,7 +8417,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
     </row>
-    <row r="171" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="79"/>
       <c r="B171" s="28" t="s">
         <v>14</v>
@@ -8411,7 +8444,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
     </row>
-    <row r="172" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="79"/>
       <c r="B172" s="28"/>
       <c r="C172" s="28"/>
@@ -8428,7 +8461,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
     </row>
-    <row r="173" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="79"/>
       <c r="B173" s="28" t="s">
         <v>16</v>
@@ -8455,7 +8488,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
     </row>
-    <row r="174" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="79"/>
       <c r="B174" s="106" t="s">
         <v>16</v>
@@ -8486,7 +8519,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
     </row>
-    <row r="175" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="79"/>
       <c r="B175" s="106" t="s">
         <v>16</v>
@@ -8517,7 +8550,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
     </row>
-    <row r="176" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="79"/>
       <c r="B176" s="28" t="s">
         <v>16</v>
@@ -8546,7 +8579,7 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
     </row>
-    <row r="177" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="79"/>
       <c r="B177" s="28" t="s">
         <v>16</v>
@@ -8573,7 +8606,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
     </row>
-    <row r="178" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="79"/>
       <c r="B178" s="106" t="s">
         <v>17</v>
@@ -8604,7 +8637,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
     </row>
-    <row r="179" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="79"/>
       <c r="B179" s="106" t="s">
         <v>17</v>
@@ -8635,7 +8668,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
     </row>
-    <row r="180" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="79"/>
       <c r="B180" s="28" t="s">
         <v>17</v>
@@ -8664,7 +8697,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
     </row>
-    <row r="181" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="79"/>
       <c r="B181" s="28" t="s">
         <v>17</v>
@@ -8693,7 +8726,7 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
     </row>
-    <row r="182" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="79"/>
       <c r="B182" s="28" t="s">
         <v>17</v>
@@ -8720,7 +8753,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
     </row>
-    <row r="183" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="79"/>
       <c r="B183" s="106" t="s">
         <v>17</v>
@@ -8751,7 +8784,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
     </row>
-    <row r="184" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="79"/>
       <c r="B184" s="28" t="s">
         <v>17</v>
@@ -8780,7 +8813,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="79"/>
       <c r="B185" s="106" t="s">
         <v>17</v>
@@ -8811,7 +8844,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
     </row>
-    <row r="186" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="79"/>
       <c r="B186" s="106" t="s">
         <v>17</v>
@@ -8842,7 +8875,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
     </row>
-    <row r="187" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="79"/>
       <c r="B187" s="28" t="s">
         <v>17</v>
@@ -8871,7 +8904,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1"/>
       <c r="B188" s="33"/>
       <c r="C188" s="33"/>
@@ -8894,7 +8927,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
     </row>
-    <row r="189" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8911,7 +8944,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
     </row>
-    <row r="190" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8928,7 +8961,7 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="3" t="s">
@@ -8949,7 +8982,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -8966,7 +8999,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="79"/>
       <c r="B193" s="6" t="s">
         <v>3</v>
@@ -8993,7 +9026,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="79"/>
       <c r="B194" s="12" t="s">
         <v>13</v>
@@ -9006,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="15">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G194" s="80"/>
       <c r="H194" s="94"/>
@@ -9018,7 +9051,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="79"/>
       <c r="B195" s="21"/>
       <c r="C195" s="21"/>
@@ -9035,7 +9068,7 @@
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
     </row>
-    <row r="196" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="79"/>
       <c r="B196" s="21"/>
       <c r="C196" s="21"/>
@@ -9052,7 +9085,7 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
     </row>
-    <row r="197" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="79"/>
       <c r="B197" s="28" t="s">
         <v>14</v>
@@ -9079,7 +9112,7 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
     </row>
-    <row r="198" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="79"/>
       <c r="B198" s="28" t="s">
         <v>14</v>
@@ -9106,7 +9139,7 @@
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
     </row>
-    <row r="199" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="79"/>
       <c r="B199" s="28"/>
       <c r="C199" s="28"/>
@@ -9123,7 +9156,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="79"/>
       <c r="B200" s="28" t="s">
         <v>16</v>
@@ -9150,7 +9183,7 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="79"/>
       <c r="B201" s="28" t="s">
         <v>16</v>
@@ -9177,7 +9210,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
     </row>
-    <row r="202" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="79"/>
       <c r="B202" s="28" t="s">
         <v>16</v>
@@ -9204,7 +9237,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
     </row>
-    <row r="203" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="79"/>
       <c r="B203" s="28"/>
       <c r="C203" s="28"/>
@@ -9221,7 +9254,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="79"/>
       <c r="B204" s="28"/>
       <c r="C204" s="28"/>
@@ -9238,7 +9271,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
     </row>
-    <row r="205" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="79"/>
       <c r="B205" s="28"/>
       <c r="C205" s="28"/>
@@ -9255,7 +9288,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
     </row>
-    <row r="206" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="79"/>
       <c r="B206" s="28" t="s">
         <v>17</v>
@@ -9282,7 +9315,7 @@
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
     </row>
-    <row r="207" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="79"/>
       <c r="B207" s="28" t="s">
         <v>17</v>
@@ -9309,7 +9342,7 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
     </row>
-    <row r="208" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="79"/>
       <c r="B208" s="28" t="s">
         <v>17</v>
@@ -9336,7 +9369,7 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
     </row>
-    <row r="209" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="79"/>
       <c r="B209" s="28" t="s">
         <v>17</v>
@@ -9363,7 +9396,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="79"/>
       <c r="B210" s="28" t="s">
         <v>17</v>
@@ -9390,7 +9423,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
     </row>
-    <row r="211" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="79"/>
       <c r="B211" s="28"/>
       <c r="C211" s="28"/>
@@ -9407,7 +9440,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
     </row>
-    <row r="212" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="79"/>
       <c r="B212" s="28"/>
       <c r="C212" s="28"/>
@@ -9424,7 +9457,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
     </row>
-    <row r="213" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="79"/>
       <c r="B213" s="28"/>
       <c r="C213" s="28"/>
@@ -9441,7 +9474,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="79"/>
       <c r="B214" s="28"/>
       <c r="C214" s="28"/>
@@ -9458,7 +9491,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="1"/>
       <c r="B215" s="33"/>
       <c r="C215" s="33"/>
@@ -9469,7 +9502,7 @@
       </c>
       <c r="F215" s="36">
         <f>SUM(F197:F214)-SUM(F194:F196)</f>
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G215" s="80"/>
       <c r="H215" s="92"/>
@@ -9481,7 +9514,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9498,7 +9531,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9515,7 +9548,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="3" t="s">
@@ -9536,7 +9569,7 @@
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="1"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -9553,7 +9586,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="79"/>
       <c r="B220" s="6" t="s">
         <v>3</v>
@@ -9580,7 +9613,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="58"/>
       <c r="B221" s="110" t="s">
         <v>13</v>
@@ -9609,7 +9642,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="79"/>
       <c r="B222" s="115" t="s">
         <v>13</v>
@@ -9638,7 +9671,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
-    <row r="223" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="79"/>
       <c r="B223" s="21" t="s">
         <v>13</v>
@@ -9651,7 +9684,7 @@
         <v>284</v>
       </c>
       <c r="F223" s="21">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G223" s="86">
         <v>46016</v>
@@ -9665,7 +9698,7 @@
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
     </row>
-    <row r="224" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="79"/>
       <c r="B224" s="28" t="s">
         <v>14</v>
@@ -9692,7 +9725,7 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
     </row>
-    <row r="225" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="79"/>
       <c r="B225" s="28" t="s">
         <v>14</v>
@@ -9719,7 +9752,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
     </row>
-    <row r="226" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="79"/>
       <c r="B226" s="28"/>
       <c r="C226" s="28"/>
@@ -9736,7 +9769,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
     </row>
-    <row r="227" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="79"/>
       <c r="B227" s="106" t="s">
         <v>16</v>
@@ -9767,7 +9800,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="79"/>
       <c r="B228" s="28" t="s">
         <v>16</v>
@@ -9796,7 +9829,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
     </row>
-    <row r="229" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="79"/>
       <c r="B229" s="28" t="s">
         <v>16</v>
@@ -9823,7 +9856,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
     </row>
-    <row r="230" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="79"/>
       <c r="B230" s="106" t="s">
         <v>16</v>
@@ -9854,7 +9887,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
-    <row r="231" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="79"/>
       <c r="B231" s="106" t="s">
         <v>16</v>
@@ -9885,7 +9918,7 @@
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
-    <row r="232" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="79"/>
       <c r="B232" s="106" t="s">
         <v>16</v>
@@ -9916,7 +9949,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
-    <row r="233" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="79"/>
       <c r="B233" s="28" t="s">
         <v>16</v>
@@ -9945,7 +9978,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
-    <row r="234" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="79"/>
       <c r="B234" s="28" t="s">
         <v>17</v>
@@ -9972,7 +10005,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
-    <row r="235" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="79"/>
       <c r="B235" s="28" t="s">
         <v>17</v>
@@ -9999,7 +10032,7 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
-    <row r="236" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="79"/>
       <c r="B236" s="28" t="s">
         <v>17</v>
@@ -10026,7 +10059,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
-    <row r="237" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="79"/>
       <c r="B237" s="106" t="s">
         <v>17</v>
@@ -10057,7 +10090,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
-    <row r="238" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="79"/>
       <c r="B238" s="28" t="s">
         <v>17</v>
@@ -10086,7 +10119,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
-    <row r="239" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="79"/>
       <c r="B239" s="106" t="s">
         <v>17</v>
@@ -10117,7 +10150,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
-    <row r="240" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="79"/>
       <c r="B240" s="28" t="s">
         <v>17</v>
@@ -10146,7 +10179,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
-    <row r="241" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="79"/>
       <c r="B241" s="28"/>
       <c r="C241" s="28"/>
@@ -10163,7 +10196,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
-    <row r="242" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="1"/>
       <c r="B242" s="33"/>
       <c r="C242" s="33"/>
@@ -10174,7 +10207,7 @@
       </c>
       <c r="F242" s="36">
         <f>SUM(F224:F241)-SUM(F221:F223)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G242" s="80"/>
       <c r="H242" s="92"/>
@@ -10186,7 +10219,7 @@
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
-    <row r="243" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -10203,7 +10236,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
-    <row r="244" spans="1:15" ht="13.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -10220,7 +10253,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
-    <row r="245" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="3" t="s">
@@ -10241,7 +10274,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
-    <row r="246" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="1"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -10258,7 +10291,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
-    <row r="247" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="79"/>
       <c r="B247" s="6" t="s">
         <v>3</v>
@@ -10277,7 +10310,7 @@
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
-    <row r="248" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="79"/>
       <c r="B248" s="110" t="s">
         <v>13</v>
@@ -10306,7 +10339,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
-    <row r="249" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="79"/>
       <c r="B249" s="115" t="s">
         <v>13</v>
@@ -10335,7 +10368,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
-    <row r="250" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="79"/>
       <c r="B250" s="21" t="s">
         <v>13</v>
@@ -10362,7 +10395,7 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
-    <row r="251" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="79"/>
       <c r="B251" s="28" t="s">
         <v>14</v>
@@ -10389,7 +10422,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
-    <row r="252" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="79"/>
       <c r="B252" s="28" t="s">
         <v>14</v>
@@ -10416,7 +10449,7 @@
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
-    <row r="253" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="79"/>
       <c r="B253" s="28" t="s">
         <v>16</v>
@@ -10443,7 +10476,7 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
-    <row r="254" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="79"/>
       <c r="B254" s="106" t="s">
         <v>16</v>
@@ -10474,7 +10507,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
-    <row r="255" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="79"/>
       <c r="B255" s="106" t="s">
         <v>16</v>
@@ -10505,7 +10538,7 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
     </row>
-    <row r="256" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="79"/>
       <c r="B256" s="28" t="s">
         <v>16</v>
@@ -10534,7 +10567,7 @@
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
     </row>
-    <row r="257" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="79"/>
       <c r="B257" s="28" t="s">
         <v>16</v>
@@ -10561,7 +10594,7 @@
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
     </row>
-    <row r="258" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="79"/>
       <c r="B258" s="106" t="s">
         <v>17</v>
@@ -10592,7 +10625,7 @@
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
     </row>
-    <row r="259" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="79"/>
       <c r="B259" s="28" t="s">
         <v>17</v>
@@ -10621,7 +10654,7 @@
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
     </row>
-    <row r="260" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="79"/>
       <c r="B260" s="28" t="s">
         <v>17</v>
@@ -10648,7 +10681,7 @@
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
     </row>
-    <row r="261" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="79"/>
       <c r="B261" s="106" t="s">
         <v>17</v>
@@ -10679,7 +10712,7 @@
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
     </row>
-    <row r="262" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="79"/>
       <c r="B262" s="28" t="s">
         <v>17</v>
@@ -10708,7 +10741,7 @@
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
     </row>
-    <row r="263" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="79"/>
       <c r="B263" s="106" t="s">
         <v>17</v>
@@ -10739,7 +10772,7 @@
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
     </row>
-    <row r="264" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="79"/>
       <c r="B264" s="28" t="s">
         <v>17</v>
@@ -10768,7 +10801,7 @@
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
     </row>
-    <row r="265" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="79"/>
       <c r="B265" s="106" t="s">
         <v>17</v>
@@ -10799,7 +10832,7 @@
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
     </row>
-    <row r="266" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="79"/>
       <c r="B266" s="106" t="s">
         <v>17</v>
@@ -10830,7 +10863,7 @@
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
     </row>
-    <row r="267" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="79"/>
       <c r="B267" s="106" t="s">
         <v>17</v>
@@ -10861,7 +10894,7 @@
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
     </row>
-    <row r="268" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="79"/>
       <c r="B268" s="28" t="s">
         <v>17</v>
@@ -10890,7 +10923,7 @@
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
     </row>
-    <row r="269" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="1"/>
       <c r="B269" s="33"/>
       <c r="C269" s="33"/>
@@ -10913,7 +10946,7 @@
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
     </row>
-    <row r="270" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -10930,7 +10963,7 @@
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
     </row>
-    <row r="271" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -10947,7 +10980,7 @@
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
     </row>
-    <row r="272" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1" t="s">
@@ -10968,7 +11001,7 @@
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
     </row>
-    <row r="273" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="1"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -10985,7 +11018,7 @@
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
     </row>
-    <row r="274" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="79"/>
       <c r="B274" s="6" t="s">
         <v>3</v>
@@ -11012,7 +11045,7 @@
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
     </row>
-    <row r="275" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="79"/>
       <c r="B275" s="110" t="s">
         <v>13</v>
@@ -11041,7 +11074,7 @@
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
     </row>
-    <row r="276" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="79"/>
       <c r="B276" s="12" t="s">
         <v>13</v>
@@ -11054,7 +11087,7 @@
         <v>284</v>
       </c>
       <c r="F276" s="21">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G276" s="86">
         <v>45974</v>
@@ -11068,7 +11101,7 @@
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
     </row>
-    <row r="277" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="79"/>
       <c r="B277" s="21"/>
       <c r="C277" s="21"/>
@@ -11085,7 +11118,7 @@
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
     </row>
-    <row r="278" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="79"/>
       <c r="B278" s="28" t="s">
         <v>14</v>
@@ -11112,7 +11145,7 @@
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
     </row>
-    <row r="279" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="79"/>
       <c r="B279" s="28" t="s">
         <v>14</v>
@@ -11139,7 +11172,7 @@
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
     </row>
-    <row r="280" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="79"/>
       <c r="B280" s="28"/>
       <c r="C280" s="28"/>
@@ -11156,7 +11189,7 @@
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
     </row>
-    <row r="281" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="79"/>
       <c r="B281" s="28" t="s">
         <v>16</v>
@@ -11183,7 +11216,7 @@
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
     </row>
-    <row r="282" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="79"/>
       <c r="B282" s="28" t="s">
         <v>16</v>
@@ -11210,7 +11243,7 @@
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
     </row>
-    <row r="283" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="79"/>
       <c r="B283" s="106" t="s">
         <v>16</v>
@@ -11241,7 +11274,7 @@
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
     </row>
-    <row r="284" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="79"/>
       <c r="B284" s="28" t="s">
         <v>16</v>
@@ -11270,7 +11303,7 @@
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
     </row>
-    <row r="285" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="79"/>
       <c r="B285" s="28"/>
       <c r="C285" s="28"/>
@@ -11287,7 +11320,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
-    <row r="286" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="79"/>
       <c r="B286" s="28"/>
       <c r="C286" s="28"/>
@@ -11304,7 +11337,7 @@
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
-    <row r="287" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="79"/>
       <c r="B287" s="28" t="s">
         <v>17</v>
@@ -11331,7 +11364,7 @@
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
-    <row r="288" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="79"/>
       <c r="B288" s="28" t="s">
         <v>17</v>
@@ -11358,7 +11391,7 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
-    <row r="289" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="79"/>
       <c r="B289" s="106" t="s">
         <v>17</v>
@@ -11389,7 +11422,7 @@
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
-    <row r="290" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="79"/>
       <c r="B290" s="28" t="s">
         <v>17</v>
@@ -11418,7 +11451,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
-    <row r="291" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="79"/>
       <c r="B291" s="28" t="s">
         <v>17</v>
@@ -11445,7 +11478,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
-    <row r="292" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="79"/>
       <c r="B292" s="28" t="s">
         <v>17</v>
@@ -11472,7 +11505,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
-    <row r="293" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="79"/>
       <c r="B293" s="28"/>
       <c r="C293" s="28"/>
@@ -11489,7 +11522,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
-    <row r="294" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="79"/>
       <c r="B294" s="28"/>
       <c r="C294" s="28"/>
@@ -11506,7 +11539,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
-    <row r="295" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="79"/>
       <c r="B295" s="28"/>
       <c r="C295" s="28"/>
@@ -11523,7 +11556,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
-    <row r="296" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="1"/>
       <c r="B296" s="33"/>
       <c r="C296" s="33"/>
@@ -11534,7 +11567,7 @@
       </c>
       <c r="F296" s="36">
         <f>SUM(F278:F295)-SUM(F275:F276)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G296" s="91"/>
       <c r="H296" s="91"/>
@@ -11546,7 +11579,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
-    <row r="297" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -11563,7 +11596,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
-    <row r="298" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -11580,7 +11613,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
-    <row r="299" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1" t="s">
@@ -11601,7 +11634,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
-    <row r="300" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="1"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -11618,7 +11651,7 @@
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
-    <row r="301" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="79"/>
       <c r="B301" s="6" t="s">
         <v>3</v>
@@ -11645,7 +11678,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="79"/>
       <c r="B302" s="110" t="s">
         <v>13</v>
@@ -11674,7 +11707,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
-    <row r="303" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="79"/>
       <c r="B303" s="115" t="s">
         <v>13</v>
@@ -11703,7 +11736,7 @@
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
-    <row r="304" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="79"/>
       <c r="B304" s="21" t="s">
         <v>13</v>
@@ -11730,7 +11763,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
-    <row r="305" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="79"/>
       <c r="B305" s="28" t="s">
         <v>14</v>
@@ -11757,7 +11790,7 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
-    <row r="306" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="79"/>
       <c r="B306" s="28" t="s">
         <v>14</v>
@@ -11784,7 +11817,7 @@
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
-    <row r="307" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="79"/>
       <c r="B307" s="106" t="s">
         <v>16</v>
@@ -11815,7 +11848,7 @@
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
-    <row r="308" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="79"/>
       <c r="B308" s="28" t="s">
         <v>16</v>
@@ -11844,7 +11877,7 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
-    <row r="309" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="79"/>
       <c r="B309" s="106" t="s">
         <v>16</v>
@@ -11875,7 +11908,7 @@
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
-    <row r="310" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="79"/>
       <c r="B310" s="28" t="s">
         <v>16</v>
@@ -11904,7 +11937,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
-    <row r="311" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="79"/>
       <c r="B311" s="106" t="s">
         <v>16</v>
@@ -11935,7 +11968,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
-    <row r="312" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="79"/>
       <c r="B312" s="28" t="s">
         <v>16</v>
@@ -11964,7 +11997,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
-    <row r="313" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="79"/>
       <c r="B313" s="28" t="s">
         <v>17</v>
@@ -11991,7 +12024,7 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
-    <row r="314" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="79"/>
       <c r="B314" s="106" t="s">
         <v>17</v>
@@ -12022,7 +12055,7 @@
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
-    <row r="315" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="79"/>
       <c r="B315" s="28" t="s">
         <v>17</v>
@@ -12051,7 +12084,7 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
-    <row r="316" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="79"/>
       <c r="B316" s="106" t="s">
         <v>17</v>
@@ -12082,7 +12115,7 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
-    <row r="317" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="79"/>
       <c r="B317" s="28" t="s">
         <v>17</v>
@@ -12111,7 +12144,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
-    <row r="318" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="79"/>
       <c r="B318" s="106" t="s">
         <v>17</v>
@@ -12142,7 +12175,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
-    <row r="319" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="79"/>
       <c r="B319" s="106" t="s">
         <v>17</v>
@@ -12173,7 +12206,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
-    <row r="320" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="79"/>
       <c r="B320" s="28" t="s">
         <v>17</v>
@@ -12202,7 +12235,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
-    <row r="321" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="79"/>
       <c r="B321" s="106" t="s">
         <v>17</v>
@@ -12233,7 +12266,7 @@
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
-    <row r="322" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="79"/>
       <c r="B322" s="28" t="s">
         <v>17</v>
@@ -12262,7 +12295,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
-    <row r="323" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="1"/>
       <c r="B323" s="33"/>
       <c r="C323" s="33"/>
@@ -12285,7 +12318,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
-    <row r="324" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -12302,7 +12335,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
-    <row r="325" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -12319,7 +12352,7 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
-    <row r="326" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1" t="s">
@@ -12340,7 +12373,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
-    <row r="327" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="1"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -12357,7 +12390,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
-    <row r="328" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="79"/>
       <c r="B328" s="6" t="s">
         <v>3</v>
@@ -12384,7 +12417,7 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
-    <row r="329" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="79"/>
       <c r="B329" s="12" t="s">
         <v>13</v>
@@ -12409,7 +12442,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
-    <row r="330" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="79"/>
       <c r="B330" s="21"/>
       <c r="C330" s="21"/>
@@ -12426,7 +12459,7 @@
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
-    <row r="331" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="79"/>
       <c r="B331" s="21"/>
       <c r="C331" s="21"/>
@@ -12443,7 +12476,7 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
-    <row r="332" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="79"/>
       <c r="B332" s="28" t="s">
         <v>14</v>
@@ -12470,7 +12503,7 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
-    <row r="333" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="79"/>
       <c r="B333" s="28" t="s">
         <v>14</v>
@@ -12497,7 +12530,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
-    <row r="334" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="79"/>
       <c r="B334" s="28"/>
       <c r="C334" s="28"/>
@@ -12514,7 +12547,7 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
-    <row r="335" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="79"/>
       <c r="B335" s="106" t="s">
         <v>16</v>
@@ -12545,7 +12578,7 @@
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
-    <row r="336" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="79"/>
       <c r="B336" s="28" t="s">
         <v>16</v>
@@ -12574,7 +12607,7 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
     </row>
-    <row r="337" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="79"/>
       <c r="B337" s="106" t="s">
         <v>16</v>
@@ -12605,7 +12638,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
     </row>
-    <row r="338" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="79"/>
       <c r="B338" s="28" t="s">
         <v>16</v>
@@ -12634,7 +12667,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
     </row>
-    <row r="339" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="79"/>
       <c r="B339" s="28" t="s">
         <v>16</v>
@@ -12658,7 +12691,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
     </row>
-    <row r="340" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="79"/>
       <c r="B340" s="28"/>
       <c r="C340" s="28"/>
@@ -12672,7 +12705,7 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
     </row>
-    <row r="341" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="79"/>
       <c r="B341" s="106" t="s">
         <v>17</v>
@@ -12700,7 +12733,7 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
     </row>
-    <row r="342" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="79"/>
       <c r="B342" s="28" t="s">
         <v>17</v>
@@ -12726,7 +12759,7 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
     </row>
-    <row r="343" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="79"/>
       <c r="B343" s="28" t="s">
         <v>17</v>
@@ -12743,14 +12776,16 @@
       <c r="F343" s="30">
         <v>16</v>
       </c>
-      <c r="G343" s="87"/>
+      <c r="G343" s="87">
+        <v>46072</v>
+      </c>
       <c r="H343" s="91"/>
       <c r="I343" s="90"/>
       <c r="J343" s="1"/>
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
-    <row r="344" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="79"/>
       <c r="B344" s="106" t="s">
         <v>17</v>
@@ -12778,7 +12813,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
     </row>
-    <row r="345" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="79"/>
       <c r="B345" s="28" t="s">
         <v>17</v>
@@ -12804,7 +12839,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
     </row>
-    <row r="346" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="79"/>
       <c r="B346" s="28" t="s">
         <v>17</v>
@@ -12828,7 +12863,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
     </row>
-    <row r="347" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="79"/>
       <c r="B347" s="106" t="s">
         <v>17</v>
@@ -12856,7 +12891,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
     </row>
-    <row r="348" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="79"/>
       <c r="B348" s="28" t="s">
         <v>17</v>
@@ -12882,7 +12917,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
     </row>
-    <row r="349" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="79"/>
       <c r="B349" s="28"/>
       <c r="C349" s="28"/>
@@ -12896,7 +12931,7 @@
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
     </row>
-    <row r="350" spans="1:15" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="1"/>
       <c r="B350" s="33"/>
       <c r="C350" s="33"/>
@@ -12916,7 +12951,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
     </row>
-    <row r="351" spans="1:15" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:15" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -12930,7 +12965,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
     </row>
-    <row r="353" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B353" s="1"/>
       <c r="C353" s="1" t="s">
         <v>245</v>
@@ -12945,7 +12980,7 @@
       <c r="I353" s="1"/>
       <c r="J353" s="1"/>
     </row>
-    <row r="354" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
@@ -12956,7 +12991,7 @@
       <c r="I354" s="1"/>
       <c r="J354" s="1"/>
     </row>
-    <row r="355" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B355" s="6" t="s">
         <v>3</v>
       </c>
@@ -12977,7 +13012,7 @@
       <c r="I355" s="1"/>
       <c r="J355" s="1"/>
     </row>
-    <row r="356" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B356" s="12" t="s">
         <v>13</v>
       </c>
@@ -12996,7 +13031,7 @@
       <c r="I356" s="1"/>
       <c r="J356" s="1"/>
     </row>
-    <row r="357" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B357" s="21"/>
       <c r="C357" s="21"/>
       <c r="D357" s="21"/>
@@ -13007,7 +13042,7 @@
       <c r="I357" s="1"/>
       <c r="J357" s="1"/>
     </row>
-    <row r="358" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B358" s="21"/>
       <c r="C358" s="21"/>
       <c r="D358" s="21"/>
@@ -13018,7 +13053,7 @@
       <c r="I358" s="1"/>
       <c r="J358" s="1"/>
     </row>
-    <row r="359" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B359" s="28" t="s">
         <v>14</v>
       </c>
@@ -13039,7 +13074,7 @@
       <c r="I359" s="1"/>
       <c r="J359" s="1"/>
     </row>
-    <row r="360" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B360" s="28" t="s">
         <v>14</v>
       </c>
@@ -13060,7 +13095,7 @@
       <c r="I360" s="1"/>
       <c r="J360" s="1"/>
     </row>
-    <row r="361" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B361" s="28" t="s">
         <v>16</v>
       </c>
@@ -13081,7 +13116,7 @@
       <c r="I361" s="1"/>
       <c r="J361" s="1"/>
     </row>
-    <row r="362" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B362" s="106" t="s">
         <v>16</v>
       </c>
@@ -13106,7 +13141,7 @@
       <c r="I362" s="1"/>
       <c r="J362" s="1"/>
     </row>
-    <row r="363" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B363" s="106" t="s">
         <v>16</v>
       </c>
@@ -13131,7 +13166,7 @@
       <c r="I363" s="1"/>
       <c r="J363" s="1"/>
     </row>
-    <row r="364" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B364" s="28" t="s">
         <v>16</v>
       </c>
@@ -13154,7 +13189,7 @@
       <c r="I364" s="1"/>
       <c r="J364" s="1"/>
     </row>
-    <row r="365" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B365" s="106" t="s">
         <v>16</v>
       </c>
@@ -13179,7 +13214,7 @@
       <c r="I365" s="1"/>
       <c r="J365" s="1"/>
     </row>
-    <row r="366" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B366" s="28" t="s">
         <v>16</v>
       </c>
@@ -13202,7 +13237,7 @@
       <c r="I366" s="1"/>
       <c r="J366" s="1"/>
     </row>
-    <row r="367" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B367" s="106" t="s">
         <v>17</v>
       </c>
@@ -13227,7 +13262,7 @@
       <c r="I367" s="1"/>
       <c r="J367" s="1"/>
     </row>
-    <row r="368" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B368" s="28" t="s">
         <v>17</v>
       </c>
@@ -13250,7 +13285,7 @@
       <c r="I368" s="1"/>
       <c r="J368" s="1"/>
     </row>
-    <row r="369" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B369" s="28" t="s">
         <v>17</v>
       </c>
@@ -13271,7 +13306,7 @@
       <c r="I369" s="1"/>
       <c r="J369" s="1"/>
     </row>
-    <row r="370" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B370" s="28" t="s">
         <v>17</v>
       </c>
@@ -13292,7 +13327,7 @@
       <c r="I370" s="1"/>
       <c r="J370" s="1"/>
     </row>
-    <row r="371" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B371" s="106" t="s">
         <v>17</v>
       </c>
@@ -13317,7 +13352,7 @@
       <c r="I371" s="1"/>
       <c r="J371" s="1"/>
     </row>
-    <row r="372" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B372" s="106" t="s">
         <v>17</v>
       </c>
@@ -13342,7 +13377,7 @@
       <c r="I372" s="1"/>
       <c r="J372" s="1"/>
     </row>
-    <row r="373" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B373" s="28" t="s">
         <v>17</v>
       </c>
@@ -13365,7 +13400,7 @@
       <c r="I373" s="1"/>
       <c r="J373" s="1"/>
     </row>
-    <row r="374" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B374" s="106" t="s">
         <v>17</v>
       </c>
@@ -13390,7 +13425,7 @@
       <c r="I374" s="1"/>
       <c r="J374" s="1"/>
     </row>
-    <row r="375" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B375" s="106" t="s">
         <v>17</v>
       </c>
@@ -13415,7 +13450,7 @@
       <c r="I375" s="1"/>
       <c r="J375" s="1"/>
     </row>
-    <row r="376" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B376" s="28" t="s">
         <v>17</v>
       </c>
@@ -13438,7 +13473,7 @@
       <c r="I376" s="1"/>
       <c r="J376" s="1"/>
     </row>
-    <row r="377" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B377" s="33"/>
       <c r="C377" s="33"/>
       <c r="D377" s="34"/>
@@ -13455,7 +13490,7 @@
       <c r="I377" s="1"/>
       <c r="J377" s="1"/>
     </row>
-    <row r="380" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B380" s="1"/>
       <c r="C380" s="3" t="s">
         <v>111</v>
@@ -13466,14 +13501,14 @@
       <c r="E380" s="2"/>
       <c r="F380" s="1"/>
     </row>
-    <row r="381" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
       <c r="E381" s="5"/>
       <c r="F381" s="4"/>
     </row>
-    <row r="382" spans="2:10" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:10" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B382" s="6" t="s">
         <v>3</v>
       </c>
@@ -13490,186 +13525,272 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B383" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C383" s="13"/>
-      <c r="D383" s="12"/>
-      <c r="E383" s="14"/>
-      <c r="F383" s="15"/>
-    </row>
-    <row r="384" spans="2:10" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D383" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E383" s="14">
+        <v>1</v>
+      </c>
+      <c r="F383" s="15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="384" spans="2:10" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B384" s="21"/>
       <c r="C384" s="21"/>
       <c r="D384" s="21"/>
       <c r="E384" s="22"/>
       <c r="F384" s="21"/>
     </row>
-    <row r="385" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B385" s="21"/>
       <c r="C385" s="21"/>
       <c r="D385" s="21"/>
       <c r="E385" s="22"/>
       <c r="F385" s="21"/>
     </row>
-    <row r="386" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B386" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C386" s="28"/>
-      <c r="D386" s="28"/>
-      <c r="E386" s="29"/>
-      <c r="F386" s="30"/>
-    </row>
-    <row r="387" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C386" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="D386" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E386" s="29">
+        <v>1</v>
+      </c>
+      <c r="F386" s="30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="387" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B387" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C387" s="28"/>
-      <c r="D387" s="28"/>
-      <c r="E387" s="29"/>
-      <c r="F387" s="30"/>
-    </row>
-    <row r="388" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C387" s="28" t="s">
+        <v>551</v>
+      </c>
+      <c r="D387" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="E387" s="29">
+        <v>1</v>
+      </c>
+      <c r="F387" s="30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="388" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B388" s="28"/>
       <c r="C388" s="28"/>
       <c r="D388" s="28"/>
       <c r="E388" s="29"/>
       <c r="F388" s="30"/>
     </row>
-    <row r="389" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B389" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C389" s="28"/>
-      <c r="D389" s="28"/>
-      <c r="E389" s="29"/>
-      <c r="F389" s="30"/>
-    </row>
-    <row r="390" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C389" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="D389" s="28" t="s">
+        <v>553</v>
+      </c>
+      <c r="E389" s="29">
+        <v>1</v>
+      </c>
+      <c r="F389" s="30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="390" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B390" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C390" s="28"/>
-      <c r="D390" s="28"/>
-      <c r="E390" s="29"/>
-      <c r="F390" s="30"/>
-    </row>
-    <row r="391" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C390" s="28" t="s">
+        <v>554</v>
+      </c>
+      <c r="D390" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E390" s="29">
+        <v>1</v>
+      </c>
+      <c r="F390" s="30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="391" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B391" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C391" s="28"/>
-      <c r="D391" s="28"/>
-      <c r="E391" s="29"/>
-      <c r="F391" s="30"/>
-    </row>
-    <row r="392" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C391" s="28" t="s">
+        <v>555</v>
+      </c>
+      <c r="D391" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E391" s="29">
+        <v>1</v>
+      </c>
+      <c r="F391" s="30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="392" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B392" s="28"/>
       <c r="C392" s="28"/>
       <c r="D392" s="28"/>
       <c r="E392" s="29"/>
       <c r="F392" s="30"/>
     </row>
-    <row r="393" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B393" s="28"/>
       <c r="C393" s="28"/>
       <c r="D393" s="28"/>
       <c r="E393" s="29"/>
       <c r="F393" s="30"/>
     </row>
-    <row r="394" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B394" s="28"/>
       <c r="C394" s="28"/>
       <c r="D394" s="28"/>
       <c r="E394" s="29"/>
       <c r="F394" s="30"/>
     </row>
-    <row r="395" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B395" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C395" s="28"/>
-      <c r="D395" s="28"/>
-      <c r="E395" s="29"/>
-      <c r="F395" s="30"/>
-    </row>
-    <row r="396" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C395" s="28" t="s">
+        <v>556</v>
+      </c>
+      <c r="D395" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="E395" s="29">
+        <v>1</v>
+      </c>
+      <c r="F395" s="30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="396" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B396" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C396" s="28"/>
-      <c r="D396" s="28"/>
-      <c r="E396" s="29"/>
-      <c r="F396" s="30"/>
-    </row>
-    <row r="397" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C396" s="28" t="s">
+        <v>557</v>
+      </c>
+      <c r="D396" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="E396" s="29">
+        <v>1</v>
+      </c>
+      <c r="F396" s="30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="397" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B397" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C397" s="28"/>
-      <c r="D397" s="28"/>
-      <c r="E397" s="29"/>
-      <c r="F397" s="30"/>
-    </row>
-    <row r="398" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C397" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="D397" s="28" t="s">
+        <v>530</v>
+      </c>
+      <c r="E397" s="29">
+        <v>1</v>
+      </c>
+      <c r="F397" s="30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="398" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B398" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C398" s="28"/>
-      <c r="D398" s="28"/>
-      <c r="E398" s="29"/>
-      <c r="F398" s="30"/>
-    </row>
-    <row r="399" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C398" s="28" t="s">
+        <v>559</v>
+      </c>
+      <c r="D398" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E398" s="29">
+        <v>1</v>
+      </c>
+      <c r="F398" s="30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="399" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B399" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C399" s="28"/>
-      <c r="D399" s="28"/>
-      <c r="E399" s="29"/>
-      <c r="F399" s="30"/>
-    </row>
-    <row r="400" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C399" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="D399" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E399" s="29">
+        <v>1</v>
+      </c>
+      <c r="F399" s="30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="400" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B400" s="28"/>
       <c r="C400" s="28"/>
       <c r="D400" s="28"/>
       <c r="E400" s="29"/>
       <c r="F400" s="30"/>
     </row>
-    <row r="401" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B401" s="28"/>
       <c r="C401" s="28"/>
       <c r="D401" s="28"/>
       <c r="E401" s="29"/>
       <c r="F401" s="30"/>
     </row>
-    <row r="402" spans="2:6" ht="13.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="2:6" ht="13.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B402" s="28"/>
       <c r="C402" s="28"/>
       <c r="D402" s="28"/>
       <c r="E402" s="29"/>
       <c r="F402" s="30"/>
     </row>
-    <row r="403" spans="2:6" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B403" s="28"/>
       <c r="C403" s="28"/>
       <c r="D403" s="28"/>
       <c r="E403" s="29"/>
       <c r="F403" s="30"/>
     </row>
-    <row r="404" spans="2:6" ht="13.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" ht="13.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B404" s="33"/>
       <c r="C404" s="33"/>
       <c r="D404" s="34"/>
       <c r="E404" s="35">
         <f>SUM(E383:E403)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F404" s="36">
         <f>SUM(F386:F403)-SUM(F383:F385)</f>
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -13702,18 +13823,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IV22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.8" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="38" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="38" customWidth="1"/>
+    <col min="1" max="1" width="1.296875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="11.796875" style="38" customWidth="1"/>
     <col min="3" max="3" width="31" style="38" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" style="38" customWidth="1"/>
+    <col min="4" max="4" width="35.296875" style="38" customWidth="1"/>
     <col min="5" max="6" width="9" style="38" customWidth="1"/>
     <col min="7" max="7" width="11" style="38" customWidth="1"/>
     <col min="8" max="256" width="9" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -13730,7 +13851,7 @@
       </c>
       <c r="K1" s="41"/>
     </row>
-    <row r="2" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40"/>
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
@@ -13745,7 +13866,7 @@
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
     </row>
-    <row r="3" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -13758,7 +13879,7 @@
       <c r="J3" s="41"/>
       <c r="K3" s="41"/>
     </row>
-    <row r="4" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="40"/>
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
@@ -13773,7 +13894,7 @@
       <c r="J4" s="41"/>
       <c r="K4" s="41"/>
     </row>
-    <row r="5" spans="1:11" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40"/>
       <c r="B5" s="45"/>
       <c r="C5" s="45"/>
@@ -13786,7 +13907,7 @@
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
     </row>
-    <row r="6" spans="1:11" ht="14.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="14.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="47"/>
       <c r="B6" s="48" t="s">
         <v>3</v>
@@ -13811,7 +13932,7 @@
       <c r="J6" s="41"/>
       <c r="K6" s="41"/>
     </row>
-    <row r="7" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="47"/>
       <c r="B7" s="54">
         <v>1</v>
@@ -13825,10 +13946,10 @@
       <c r="E7" s="25">
         <v>57</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="26">
         <v>123</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="27">
         <v>66</v>
       </c>
       <c r="H7" s="117"/>
@@ -13836,7 +13957,7 @@
       <c r="J7" s="41"/>
       <c r="K7" s="41"/>
     </row>
-    <row r="8" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47"/>
       <c r="B8" s="54">
         <v>2</v>
@@ -13844,16 +13965,16 @@
       <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="55" t="s">
         <v>203</v>
       </c>
       <c r="E8" s="25">
         <v>42</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="56">
         <v>95</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="57">
         <v>53</v>
       </c>
       <c r="H8" s="52"/>
@@ -13861,7 +13982,7 @@
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
     </row>
-    <row r="9" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47"/>
       <c r="B9" s="54">
         <v>3</v>
@@ -13869,7 +13990,7 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="55" t="s">
         <v>188</v>
       </c>
       <c r="E9" s="25">
@@ -13886,7 +14007,7 @@
       <c r="J9" s="41"/>
       <c r="K9" s="41"/>
     </row>
-    <row r="10" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47"/>
       <c r="B10" s="54">
         <v>4</v>
@@ -13911,7 +14032,7 @@
       <c r="J10" s="41"/>
       <c r="K10" s="53"/>
     </row>
-    <row r="11" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="47"/>
       <c r="B11" s="54">
         <v>5</v>
@@ -13919,7 +14040,7 @@
       <c r="C11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="24" t="s">
         <v>1</v>
       </c>
       <c r="E11" s="25">
@@ -13936,7 +14057,7 @@
       <c r="J11" s="41"/>
       <c r="K11" s="41"/>
     </row>
-    <row r="12" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="47"/>
       <c r="B12" s="54">
         <v>6</v>
@@ -13961,7 +14082,7 @@
       <c r="J12" s="41"/>
       <c r="K12" s="41"/>
     </row>
-    <row r="13" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="47"/>
       <c r="B13" s="54">
         <v>7</v>
@@ -13986,7 +14107,7 @@
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
     </row>
-    <row r="14" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="47"/>
       <c r="B14" s="54">
         <v>8</v>
@@ -13994,24 +14115,24 @@
       <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="24" t="s">
         <v>198</v>
       </c>
       <c r="E14" s="25">
-        <v>33</v>
-      </c>
-      <c r="F14" s="56">
-        <v>84</v>
-      </c>
-      <c r="G14" s="57">
-        <v>51</v>
+        <v>32</v>
+      </c>
+      <c r="F14" s="26">
+        <v>85</v>
+      </c>
+      <c r="G14" s="27">
+        <v>53</v>
       </c>
       <c r="H14" s="117"/>
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
       <c r="K14" s="41"/>
     </row>
-    <row r="15" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="47"/>
       <c r="B15" s="54">
         <v>9</v>
@@ -14023,20 +14144,20 @@
         <v>267</v>
       </c>
       <c r="E15" s="25">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F15" s="26">
         <v>97</v>
       </c>
       <c r="G15" s="27">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H15" s="117"/>
       <c r="I15" s="41"/>
       <c r="J15" s="41"/>
       <c r="K15" s="41"/>
     </row>
-    <row r="16" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="47"/>
       <c r="B16" s="54">
         <v>10</v>
@@ -14061,7 +14182,7 @@
       <c r="J16" s="41"/>
       <c r="K16" s="41"/>
     </row>
-    <row r="17" spans="1:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="47"/>
       <c r="B17" s="54">
         <v>11</v>
@@ -14075,10 +14196,10 @@
       <c r="E17" s="25">
         <v>17</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="56">
         <v>69</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="57">
         <v>52</v>
       </c>
       <c r="H17" s="52"/>
@@ -14086,7 +14207,7 @@
       <c r="J17" s="41"/>
       <c r="K17" s="41"/>
     </row>
-    <row r="18" spans="1:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47"/>
       <c r="B18" s="54">
         <v>11</v>
@@ -14098,20 +14219,20 @@
         <v>140</v>
       </c>
       <c r="E18" s="25">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="26">
         <v>78</v>
       </c>
       <c r="G18" s="27">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
       <c r="K18" s="41"/>
     </row>
-    <row r="19" spans="1:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="47"/>
       <c r="B19" s="54">
         <v>13</v>
@@ -14136,7 +14257,7 @@
       <c r="J19" s="41"/>
       <c r="K19" s="41"/>
     </row>
-    <row r="20" spans="1:11" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="14.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="47"/>
       <c r="B20" s="54">
         <v>14</v>
@@ -14148,20 +14269,20 @@
         <v>53</v>
       </c>
       <c r="E20" s="25">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F20" s="26">
         <v>68</v>
       </c>
       <c r="G20" s="27">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H20" s="117"/>
       <c r="I20" s="41"/>
       <c r="J20" s="41"/>
       <c r="K20" s="41"/>
     </row>
-    <row r="21" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
       <c r="B21" s="59"/>
       <c r="C21" s="59"/>
@@ -14174,7 +14295,7 @@
       <c r="J21" s="41"/>
       <c r="K21" s="41"/>
     </row>
-    <row r="22" spans="1:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="40"/>
       <c r="B22" s="40"/>
       <c r="C22" s="40"/>
@@ -14208,17 +14329,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:IW34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.8" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="33.28515625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="38" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" style="38" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" style="38" customWidth="1"/>
-    <col min="6" max="7" width="9.28515625" style="38" customWidth="1"/>
-    <col min="8" max="257" width="8.85546875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="33.296875" style="38" customWidth="1"/>
+    <col min="3" max="3" width="10.09765625" style="38" customWidth="1"/>
+    <col min="4" max="4" width="9.296875" style="38" customWidth="1"/>
+    <col min="5" max="5" width="31.296875" style="38" customWidth="1"/>
+    <col min="6" max="7" width="9.296875" style="38" customWidth="1"/>
+    <col min="8" max="257" width="8.796875" style="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
         <v>253</v>
       </c>
@@ -14228,7 +14349,7 @@
       <c r="F1" s="40"/>
       <c r="G1" s="40"/>
     </row>
-    <row r="2" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -14236,7 +14357,7 @@
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
     </row>
-    <row r="3" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="63" t="s">
         <v>38</v>
       </c>
@@ -14246,7 +14367,7 @@
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
     </row>
-    <row r="4" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
         <v>42</v>
       </c>
@@ -14275,7 +14396,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
         <v>43</v>
       </c>
@@ -14304,7 +14425,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>44</v>
       </c>
@@ -14333,7 +14454,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="67" t="s">
         <v>45</v>
       </c>
@@ -14362,7 +14483,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="67" t="s">
         <v>46</v>
       </c>
@@ -14385,7 +14506,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
         <v>47</v>
       </c>
@@ -14411,7 +14532,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="67"/>
       <c r="B10" s="65"/>
       <c r="C10" s="65"/>
@@ -14423,7 +14544,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="67"/>
       <c r="B11" s="63" t="s">
         <v>525</v>
@@ -14437,7 +14558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="67" t="s">
         <v>48</v>
       </c>
@@ -14460,7 +14581,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="67"/>
       <c r="B13" s="65"/>
       <c r="C13" s="68"/>
@@ -14469,7 +14590,7 @@
       <c r="F13" s="68"/>
       <c r="G13" s="64"/>
     </row>
-    <row r="14" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="67"/>
       <c r="B14" s="63" t="s">
         <v>62</v>
@@ -14480,7 +14601,7 @@
       <c r="F14" s="69"/>
       <c r="G14" s="100"/>
     </row>
-    <row r="15" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="67" t="s">
         <v>49</v>
       </c>
@@ -14503,7 +14624,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
         <v>50</v>
       </c>
@@ -14526,7 +14647,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>63</v>
       </c>
@@ -14549,7 +14670,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="67" t="s">
         <v>76</v>
       </c>
@@ -14572,7 +14693,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="63"/>
       <c r="C19" s="64"/>
       <c r="D19" s="64"/>
@@ -14580,7 +14701,7 @@
       <c r="F19" s="66"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="67"/>
       <c r="B20" s="63" t="s">
         <v>535</v>
@@ -14591,7 +14712,7 @@
       <c r="F20" s="68"/>
       <c r="G20" s="64"/>
     </row>
-    <row r="21" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
         <v>77</v>
       </c>
@@ -14614,7 +14735,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="65"/>
       <c r="C22" s="64"/>
       <c r="D22" s="61"/>
@@ -14622,7 +14743,7 @@
       <c r="F22" s="66"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="63" t="s">
         <v>39</v>
       </c>
@@ -14632,7 +14753,7 @@
       <c r="F23" s="66"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
         <v>78</v>
       </c>
@@ -14655,7 +14776,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
         <v>110</v>
       </c>
@@ -14678,7 +14799,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="67"/>
       <c r="B26" s="65"/>
       <c r="C26" s="68"/>
@@ -14687,7 +14808,7 @@
       <c r="F26" s="69"/>
       <c r="G26" s="100"/>
     </row>
-    <row r="27" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="67"/>
       <c r="B27" s="63" t="s">
         <v>543</v>
@@ -14698,7 +14819,7 @@
       <c r="F27" s="68"/>
       <c r="G27" s="64"/>
     </row>
-    <row r="28" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
         <v>255</v>
       </c>
@@ -14721,7 +14842,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
       <c r="D29" s="64"/>
@@ -14729,7 +14850,7 @@
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="63" t="s">
         <v>40</v>
       </c>
@@ -14739,7 +14860,7 @@
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
         <v>256</v>
       </c>
@@ -14762,7 +14883,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="40"/>
       <c r="C32" s="40"/>
       <c r="D32" s="64"/>
@@ -14770,7 +14891,7 @@
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="2:11" ht="13.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="63" t="s">
         <v>41</v>
       </c>
@@ -14781,7 +14902,7 @@
       <c r="G33" s="40"/>
       <c r="K33" s="98"/>
     </row>
-    <row r="34" spans="2:11" ht="12.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="65" t="s">
         <v>222</v>
       </c>
@@ -14807,13 +14928,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA85496-96FC-4E57-B88C-D037E5ADD8C6}">
   <dimension ref="A1:X71"/>
-  <sheetFormatPr defaultRowHeight="13.1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.69921875" customWidth="1"/>
+    <col min="5" max="5" width="35.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" s="62" t="s">
         <v>282</v>
       </c>
@@ -14840,7 +14961,7 @@
       <c r="W1" s="38"/>
       <c r="X1" s="38"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B2" s="40"/>
       <c r="C2" s="40"/>
       <c r="D2" s="40"/>
@@ -14865,7 +14986,7 @@
       <c r="W2" s="38"/>
       <c r="X2" s="38"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B3" s="63" t="s">
         <v>38</v>
       </c>
@@ -14892,7 +15013,7 @@
       <c r="W3" s="38"/>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
         <v>42</v>
       </c>
@@ -14934,7 +15055,7 @@
       <c r="W4" s="38"/>
       <c r="X4" s="38"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="67" t="s">
         <v>43</v>
       </c>
@@ -14976,7 +15097,7 @@
       <c r="W5" s="38"/>
       <c r="X5" s="38"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="67" t="s">
         <v>44</v>
       </c>
@@ -15018,7 +15139,7 @@
       <c r="W6" s="38"/>
       <c r="X6" s="38"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="67" t="s">
         <v>45</v>
       </c>
@@ -15060,7 +15181,7 @@
       <c r="W7" s="38"/>
       <c r="X7" s="38"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="67" t="s">
         <v>46</v>
       </c>
@@ -15102,7 +15223,7 @@
       <c r="W8" s="38"/>
       <c r="X8" s="38"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
         <v>47</v>
       </c>
@@ -15144,7 +15265,7 @@
       <c r="W9" s="38"/>
       <c r="X9" s="38"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="67" t="s">
         <v>48</v>
       </c>
@@ -15186,7 +15307,7 @@
       <c r="W10" s="38"/>
       <c r="X10" s="38"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="67" t="s">
         <v>49</v>
       </c>
@@ -15226,7 +15347,7 @@
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="67" t="s">
         <v>50</v>
       </c>
@@ -15266,7 +15387,7 @@
       <c r="W12" s="38"/>
       <c r="X12" s="38"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="67" t="s">
         <v>63</v>
       </c>
@@ -15306,7 +15427,7 @@
       <c r="W13" s="38"/>
       <c r="X13" s="38"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="67"/>
       <c r="B14" s="68"/>
       <c r="C14" s="64"/>
@@ -15332,7 +15453,7 @@
       <c r="W14" s="38"/>
       <c r="X14" s="38"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A15" s="67"/>
       <c r="B15" s="63" t="s">
         <v>441</v>
@@ -15360,7 +15481,7 @@
       <c r="W15" s="38"/>
       <c r="X15" s="38"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="67" t="s">
         <v>76</v>
       </c>
@@ -15400,7 +15521,7 @@
       <c r="W16" s="38"/>
       <c r="X16" s="38"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="67"/>
       <c r="B17" s="65"/>
       <c r="C17" s="65"/>
@@ -15426,7 +15547,7 @@
       <c r="W17" s="38"/>
       <c r="X17" s="38"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A18" s="67"/>
       <c r="B18" s="63" t="s">
         <v>254</v>
@@ -15454,7 +15575,7 @@
       <c r="W18" s="38"/>
       <c r="X18" s="38"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="67" t="s">
         <v>77</v>
       </c>
@@ -15494,7 +15615,7 @@
       <c r="W19" s="38"/>
       <c r="X19" s="38"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="67" t="s">
         <v>78</v>
       </c>
@@ -15534,7 +15655,7 @@
       <c r="W20" s="38"/>
       <c r="X20" s="38"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="67" t="s">
         <v>110</v>
       </c>
@@ -15574,7 +15695,7 @@
       <c r="W21" s="38"/>
       <c r="X21" s="38"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="67" t="s">
         <v>255</v>
       </c>
@@ -15614,7 +15735,7 @@
       <c r="W22" s="38"/>
       <c r="X22" s="38"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="67" t="s">
         <v>256</v>
       </c>
@@ -15654,7 +15775,7 @@
       <c r="W23" s="38"/>
       <c r="X23" s="38"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="67" t="s">
         <v>257</v>
       </c>
@@ -15694,7 +15815,7 @@
       <c r="W24" s="38"/>
       <c r="X24" s="38"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="67" t="s">
         <v>258</v>
       </c>
@@ -15734,7 +15855,7 @@
       <c r="W25" s="38"/>
       <c r="X25" s="38"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="67" t="s">
         <v>259</v>
       </c>
@@ -15774,7 +15895,7 @@
       <c r="W26" s="38"/>
       <c r="X26" s="38"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="67"/>
       <c r="B27" s="65"/>
       <c r="C27" s="68"/>
@@ -15800,7 +15921,7 @@
       <c r="W27" s="38"/>
       <c r="X27" s="38"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="A28" s="67"/>
       <c r="B28" s="63" t="s">
         <v>62</v>
@@ -15828,7 +15949,7 @@
       <c r="W28" s="38"/>
       <c r="X28" s="38"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="67" t="s">
         <v>260</v>
       </c>
@@ -15868,7 +15989,7 @@
       <c r="W29" s="38"/>
       <c r="X29" s="38"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="67" t="s">
         <v>261</v>
       </c>
@@ -15908,7 +16029,7 @@
       <c r="W30" s="38"/>
       <c r="X30" s="38"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="67" t="s">
         <v>262</v>
       </c>
@@ -15948,7 +16069,7 @@
       <c r="W31" s="38"/>
       <c r="X31" s="38"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="67" t="s">
         <v>263</v>
       </c>
@@ -15988,7 +16109,7 @@
       <c r="W32" s="38"/>
       <c r="X32" s="38"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B33" s="65"/>
       <c r="C33" s="64"/>
       <c r="D33" s="61"/>
@@ -16013,7 +16134,7 @@
       <c r="W33" s="38"/>
       <c r="X33" s="38"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B34" s="63" t="s">
         <v>39</v>
       </c>
@@ -16040,7 +16161,7 @@
       <c r="W34" s="38"/>
       <c r="X34" s="38"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="67" t="s">
         <v>264</v>
       </c>
@@ -16080,7 +16201,7 @@
       <c r="W35" s="38"/>
       <c r="X35" s="38"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="67" t="s">
         <v>265</v>
       </c>
@@ -16120,7 +16241,7 @@
       <c r="W36" s="38"/>
       <c r="X36" s="38"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B37" s="65"/>
       <c r="C37" s="65"/>
       <c r="D37" s="64"/>
@@ -16145,7 +16266,7 @@
       <c r="W37" s="38"/>
       <c r="X37" s="38"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B38" s="63" t="s">
         <v>40</v>
       </c>
@@ -16172,7 +16293,7 @@
       <c r="W38" s="38"/>
       <c r="X38" s="38"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="67" t="s">
         <v>442</v>
       </c>
@@ -16212,7 +16333,7 @@
       <c r="W39" s="38"/>
       <c r="X39" s="38"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B40" s="40"/>
       <c r="C40" s="40"/>
       <c r="D40" s="64"/>
@@ -16237,7 +16358,7 @@
       <c r="W40" s="38"/>
       <c r="X40" s="38"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="13.5" x14ac:dyDescent="0.35">
       <c r="B41" s="63" t="s">
         <v>41</v>
       </c>
@@ -16264,7 +16385,7 @@
       <c r="W41" s="38"/>
       <c r="X41" s="38"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B42" s="65" t="s">
         <v>203</v>
       </c>
@@ -16291,7 +16412,7 @@
       <c r="W42" s="38"/>
       <c r="X42" s="38"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H43" s="38"/>
       <c r="I43" s="38"/>
       <c r="J43" s="38"/>
@@ -16310,7 +16431,7 @@
       <c r="W43" s="38"/>
       <c r="X43" s="38"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H44" s="38"/>
       <c r="I44" s="38"/>
       <c r="J44" s="38"/>
@@ -16329,7 +16450,7 @@
       <c r="W44" s="38"/>
       <c r="X44" s="38"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H45" s="38"/>
       <c r="I45" s="38"/>
       <c r="J45" s="38"/>
@@ -16348,7 +16469,7 @@
       <c r="W45" s="38"/>
       <c r="X45" s="38"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H46" s="38"/>
       <c r="I46" s="38"/>
       <c r="J46" s="38"/>
@@ -16367,7 +16488,7 @@
       <c r="W46" s="38"/>
       <c r="X46" s="38"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
       <c r="J47" s="38"/>
@@ -16386,7 +16507,7 @@
       <c r="W47" s="38"/>
       <c r="X47" s="38"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="H48" s="38"/>
       <c r="I48" s="38"/>
       <c r="J48" s="38"/>
@@ -16405,7 +16526,7 @@
       <c r="W48" s="38"/>
       <c r="X48" s="38"/>
     </row>
-    <row r="49" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
       <c r="J49" s="38"/>
@@ -16424,7 +16545,7 @@
       <c r="W49" s="38"/>
       <c r="X49" s="38"/>
     </row>
-    <row r="50" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H50" s="38"/>
       <c r="I50" s="38"/>
       <c r="J50" s="38"/>
@@ -16443,7 +16564,7 @@
       <c r="W50" s="38"/>
       <c r="X50" s="38"/>
     </row>
-    <row r="51" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
       <c r="J51" s="38"/>
@@ -16462,7 +16583,7 @@
       <c r="W51" s="38"/>
       <c r="X51" s="38"/>
     </row>
-    <row r="52" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H52" s="38"/>
       <c r="I52" s="38"/>
       <c r="J52" s="38"/>
@@ -16481,7 +16602,7 @@
       <c r="W52" s="38"/>
       <c r="X52" s="38"/>
     </row>
-    <row r="53" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H53" s="38"/>
       <c r="I53" s="38"/>
       <c r="J53" s="38"/>
@@ -16500,7 +16621,7 @@
       <c r="W53" s="38"/>
       <c r="X53" s="38"/>
     </row>
-    <row r="54" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H54" s="38"/>
       <c r="I54" s="38"/>
       <c r="J54" s="38"/>
@@ -16519,7 +16640,7 @@
       <c r="W54" s="38"/>
       <c r="X54" s="38"/>
     </row>
-    <row r="55" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H55" s="38"/>
       <c r="I55" s="38"/>
       <c r="J55" s="38"/>
@@ -16538,7 +16659,7 @@
       <c r="W55" s="38"/>
       <c r="X55" s="38"/>
     </row>
-    <row r="56" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="38"/>
@@ -16557,7 +16678,7 @@
       <c r="W56" s="38"/>
       <c r="X56" s="38"/>
     </row>
-    <row r="57" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H57" s="38"/>
       <c r="I57" s="38"/>
       <c r="J57" s="38"/>
@@ -16576,7 +16697,7 @@
       <c r="W57" s="38"/>
       <c r="X57" s="38"/>
     </row>
-    <row r="58" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
       <c r="J58" s="38"/>
@@ -16595,7 +16716,7 @@
       <c r="W58" s="38"/>
       <c r="X58" s="38"/>
     </row>
-    <row r="59" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H59" s="38"/>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
@@ -16614,7 +16735,7 @@
       <c r="W59" s="38"/>
       <c r="X59" s="38"/>
     </row>
-    <row r="60" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H60" s="38"/>
       <c r="I60" s="38"/>
       <c r="J60" s="38"/>
@@ -16633,7 +16754,7 @@
       <c r="W60" s="38"/>
       <c r="X60" s="38"/>
     </row>
-    <row r="61" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
       <c r="J61" s="38"/>
@@ -16652,7 +16773,7 @@
       <c r="W61" s="38"/>
       <c r="X61" s="38"/>
     </row>
-    <row r="62" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H62" s="38"/>
       <c r="I62" s="38"/>
       <c r="J62" s="38"/>
@@ -16671,7 +16792,7 @@
       <c r="W62" s="38"/>
       <c r="X62" s="38"/>
     </row>
-    <row r="63" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H63" s="38"/>
       <c r="I63" s="38"/>
       <c r="J63" s="38"/>
@@ -16690,7 +16811,7 @@
       <c r="W63" s="38"/>
       <c r="X63" s="38"/>
     </row>
-    <row r="64" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H64" s="38"/>
       <c r="I64" s="38"/>
       <c r="J64" s="38"/>
@@ -16709,7 +16830,7 @@
       <c r="W64" s="38"/>
       <c r="X64" s="38"/>
     </row>
-    <row r="65" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H65" s="38"/>
       <c r="I65" s="38"/>
       <c r="J65" s="38"/>
@@ -16728,7 +16849,7 @@
       <c r="W65" s="38"/>
       <c r="X65" s="38"/>
     </row>
-    <row r="66" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H66" s="38"/>
       <c r="I66" s="38"/>
       <c r="J66" s="38"/>
@@ -16747,7 +16868,7 @@
       <c r="W66" s="38"/>
       <c r="X66" s="38"/>
     </row>
-    <row r="67" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H67" s="38"/>
       <c r="I67" s="38"/>
       <c r="J67" s="38"/>
@@ -16766,7 +16887,7 @@
       <c r="W67" s="38"/>
       <c r="X67" s="38"/>
     </row>
-    <row r="68" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H68" s="38"/>
       <c r="I68" s="38"/>
       <c r="J68" s="38"/>
@@ -16785,7 +16906,7 @@
       <c r="W68" s="38"/>
       <c r="X68" s="38"/>
     </row>
-    <row r="69" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
       <c r="J69" s="38"/>
@@ -16804,7 +16925,7 @@
       <c r="W69" s="38"/>
       <c r="X69" s="38"/>
     </row>
-    <row r="70" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H70" s="38"/>
       <c r="I70" s="38"/>
       <c r="J70" s="38"/>
@@ -16823,7 +16944,7 @@
       <c r="W70" s="38"/>
       <c r="X70" s="38"/>
     </row>
-    <row r="71" spans="8:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="8:24" x14ac:dyDescent="0.3">
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
       <c r="J71" s="38"/>
@@ -16854,15 +16975,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5616AB3-C7B1-4511-93B2-51A6298AD44C}">
   <dimension ref="A5:Q38"/>
-  <sheetFormatPr defaultRowHeight="13.1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.8984375" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" customWidth="1"/>
+    <col min="10" max="10" width="17.09765625" customWidth="1"/>
+    <col min="14" max="14" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>295</v>
       </c>
@@ -16888,7 +17009,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>296</v>
       </c>
@@ -16920,7 +17041,7 @@
       </c>
       <c r="Q6" s="109"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>297</v>
       </c>
@@ -16952,7 +17073,7 @@
       </c>
       <c r="Q7" s="109"/>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>298</v>
       </c>
@@ -16984,7 +17105,7 @@
       </c>
       <c r="Q8" s="109"/>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>299</v>
       </c>
@@ -17016,7 +17137,7 @@
       </c>
       <c r="Q9" s="109"/>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>300</v>
       </c>
@@ -17048,7 +17169,7 @@
       </c>
       <c r="Q10" s="109"/>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>301</v>
       </c>
@@ -17068,7 +17189,7 @@
       </c>
       <c r="K11">
         <f>COUNTIF(Stats!D:D,'Player Count'!J11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" s="109"/>
       <c r="N11" s="67" t="s">
@@ -17080,7 +17201,7 @@
       </c>
       <c r="Q11" s="109"/>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>302</v>
       </c>
@@ -17108,11 +17229,11 @@
       </c>
       <c r="O12">
         <f>COUNTIF(Stats!D:D,'Player Count'!N12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="109"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>303</v>
       </c>
@@ -17140,11 +17261,11 @@
       </c>
       <c r="O13">
         <f>COUNTIF(Stats!D:D,'Player Count'!N13)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="109"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>304</v>
       </c>
@@ -17176,7 +17297,7 @@
       </c>
       <c r="Q14" s="109"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>305</v>
       </c>
@@ -17208,7 +17329,7 @@
       </c>
       <c r="Q15" s="109"/>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>306</v>
       </c>
@@ -17240,7 +17361,7 @@
       </c>
       <c r="Q16" s="109"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>307</v>
       </c>
@@ -17272,13 +17393,13 @@
       </c>
       <c r="Q17" s="109"/>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>308</v>
       </c>
       <c r="C18">
         <f>COUNTIF(Stats!D:D,'Player Count'!B18)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
         <v>331</v>
@@ -17304,7 +17425,7 @@
       </c>
       <c r="Q18" s="109"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>309</v>
       </c>
@@ -17332,17 +17453,17 @@
       </c>
       <c r="O19">
         <f>COUNTIF(Stats!D:D,'Player Count'!N19)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="109"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>310</v>
       </c>
       <c r="C20">
         <f>COUNTIF(Stats!D:D,'Player Count'!B20)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>333</v>
@@ -17368,13 +17489,13 @@
       </c>
       <c r="Q20" s="109"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>311</v>
       </c>
       <c r="C21">
         <f>COUNTIF(Stats!D:D,'Player Count'!B21)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
         <v>334</v>
@@ -17400,7 +17521,7 @@
       </c>
       <c r="Q21" s="109"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>312</v>
       </c>
@@ -17432,7 +17553,7 @@
       </c>
       <c r="Q22" s="109"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>313</v>
       </c>
@@ -17464,7 +17585,7 @@
       </c>
       <c r="Q23" s="109"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>314</v>
       </c>
@@ -17477,7 +17598,7 @@
       </c>
       <c r="G24">
         <f>COUNTIF(Stats!D:D,'Player Count'!F24)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="s">
         <v>358</v>
@@ -17492,11 +17613,11 @@
       </c>
       <c r="O24">
         <f>COUNTIF(Stats!D:D,'Player Count'!N24)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="109"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>315</v>
       </c>
@@ -17528,13 +17649,13 @@
       </c>
       <c r="Q25" s="109"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="78" t="s">
         <v>317</v>
       </c>
       <c r="C26" s="78">
         <f>SUM(C6:C25)</f>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F26" t="s">
         <v>339</v>
@@ -17560,7 +17681,7 @@
       </c>
       <c r="Q26" s="109"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F27" t="s">
         <v>340</v>
       </c>
@@ -17585,7 +17706,7 @@
       </c>
       <c r="Q27" s="109"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F28" t="s">
         <v>341</v>
       </c>
@@ -17610,7 +17731,7 @@
       </c>
       <c r="Q28" s="109"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
         <v>342</v>
       </c>
@@ -17623,7 +17744,7 @@
       </c>
       <c r="K29">
         <f>COUNTIF(Stats!D:D,'Player Count'!J29)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29" t="s">
         <v>390</v>
@@ -17633,57 +17754,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="G30" s="78">
         <f>SUM(G6:G29)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="K30" s="78">
         <f>SUM(K6:K29)</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N30" s="78" t="s">
         <v>317</v>
       </c>
       <c r="O30" s="78">
         <f>SUM(O6:O29)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="67" t="s">
         <v>423</v>
       </c>
       <c r="C38" s="114">
         <f>C26/SUM(C26,G30,K30,O30)</f>
-        <v>0.3588709677419355</v>
+        <v>0.35907335907335908</v>
       </c>
       <c r="D38" s="114"/>
       <c r="E38" s="114"/>
       <c r="F38" s="114"/>
       <c r="G38" s="114">
         <f>G30/SUM(C26,G30,K30,O30)</f>
-        <v>0.26209677419354838</v>
+        <v>0.25482625482625482</v>
       </c>
       <c r="H38" s="114"/>
       <c r="I38" s="114"/>
       <c r="J38" s="114"/>
       <c r="K38" s="114">
         <f>K30/SUM(C26,G30,K30,O30)</f>
-        <v>0.21774193548387097</v>
+        <v>0.21621621621621623</v>
       </c>
       <c r="L38" s="114"/>
       <c r="M38" s="114"/>
       <c r="N38" s="114"/>
       <c r="O38" s="114">
         <f>O30/SUM(C26,G30,K30,O30)</f>
-        <v>0.16129032258064516</v>
+        <v>0.16988416988416988</v>
       </c>
     </row>
   </sheetData>
